--- a/output/OUTREACH_100.xlsx
+++ b/output/OUTREACH_100.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$Z$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$AA$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,7 @@
     <col width="50" customWidth="1" min="24" max="24"/>
     <col width="50" customWidth="1" min="25" max="25"/>
     <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="50" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,6 +599,11 @@
           <t>Why this angle</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Check before sending</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -682,12 +688,52 @@
           <t>mobile performance score below 60: PSI mobile performance 37</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for MJ Kitchen &amp; Bath</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt,
+Congrats on the new showroom on Ann Arbor Road. One small thing I spotted: on mj-kitchens.com the phone number is plain text in the header and footer, so a visitor on a phone can't tap it to call. Google's PageSpeed test also gives the mobile homepage a 37 out of 100.
+I built MJ a free homepage concept out of your own project photos and Google reviews. It puts tap-to-call in the header and hero, your 4.8 rating from 79 reviews up top, and the $50,000 same-layout starting price from your cost guide.
+https://mj-kitchens.thecreativezohaib.com/
+It's private: not indexed and not on your domain. Open to a quick 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, a second thing I noticed. Your reviews page opens with an off-topic comment about a truck driver before the project reviews. The concept skips that widget and shows three Google reviews instead, including Rebecca A., who brought your team back for two bathrooms after her kitchen. Here it is again:
+https://mj-kitchens.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, last note from me. The Plymouth concept stays up as a private preview if you want to look later:
+https://mj-kitchens.thecreativezohaib.com/
+If it's useful, just reply and I can walk you through it. Either way, good luck with the new showroom.</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt! I made a free homepage concept for MJ Kitchen &amp; Bath from your own photos and reviews, with tap-to-call up top and your 4.8 Google rating front and center. Private preview: https://mj-kitchens.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Phone is plain text with no tap-to-call on all crawled pages, plus PSI mobile 37 (conversion_notes.current_site_defects, pagespeed_mobile); showroom opener from outreach_hook. Note: listed email asimkins@ is from the careers page, not Matt's.</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>The only email is asimkins@, an assistant's address found on the careers page; the email greets Matt. Consider calling the showroom or using the contact form first. This email was found on their careers page and may reach staff, not the owner.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -780,12 +826,52 @@
           <t>mobile performance score below 60: PSI mobile performance 51</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>A Sterling Heights homepage for Majestic</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zayne,
+Your Google listing shows 42886 Mound Rd in Sterling Heights, but your website never shows that street address. The footer and contact page list only "Sterling Heights, MI 48314", and the copy describes Majestic as a Rochester Hills area contractor.
+So I made a free homepage concept using your own photos and Google reviews. Sterling Heights leads the headline, the full Mound Rd address matches Google, and your 4.8 from 49 reviews sits under it. Your kitchen packages ($35,000 to $55,000) and the 18-month labor warranty are right there too.
+https://majestichomesolutions.thecreativezohaib.com/
+This is a private preview only: not indexed and not on your domain. Happy to talk it through if you reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zayne, a quick follow-up. The footer badge on your site says 5.0 stars from 46 reviews, while Google now shows 4.8 from 49. The concept shows the Google figure exactly, so a homeowner who checks sees the same number. It also explains the Design Agreement in plain words.
+https://majestichomesolutions.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zayne, I won't keep filling your inbox. The Majestic concept will stay up as a private link in case it's useful down the road:
+https://majestichomesolutions.thecreativezohaib.com/
+Thanks for reading, and all the best this season.</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zayne, I built a free homepage concept for Majestic Home Solutions from your own photos and reviews. It shows your Mound Rd address, Sterling Heights up top and your 4.8 Google rating. Private preview: https://majestichomesolutions.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>No street address on the site while Google lists 42886 Mound Rd, plus Rochester Hills wording (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>This email was found on their careers page and may reach staff, not the owner.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -878,12 +964,48 @@
           <t>gallery images over 1MB each: https://acremodeling.com/__l5e/assets-v1/cec1c1be-5157-48df-b349-155f0b442312/design-build-3d-reality.png = 2,228,323 bytes; https://acremodeling.com/__l5e/assets-v1/b48af857-a78e-4e8d-8947-a0f856348d24/fuller-6.png = 1,407,800 bytes; https://acremodeling.com/__l5e/assets-v1/636377d5-1bda-47c8-b48b-de1e8bcc4601/team-carolina-white2.jpg = 5,716,609 bytes; https://acremodeling.com/__l5e/assets-v1/63ffdb06-0cef-4586-9d2e-469baf50f911/team-melissa-white2.jpg = 4,270,096 bytes | re-measured 2026-10-17 (full download): c1be-5157-48df-b349-155f0b442312/design-build-3d-reality.png = 2,228,323 bytes (browser Accept) / 2,228,323 bytes (curl); /assets-v1/b48af857-a78e-4e8d-8947-a0f856348d24/fuller-6.png = 1,407,800 bytes (browser Accept) / 1,407,800 bytes (curl); 36377d5-1bda-47c8-b48b-de1e8bcc4601/team-carolina-white2.jpg = 5,716,609 bytes (browser Accept) / 5,716,609 bytes (curl); 63ffdb06-0cef-4586-9d2e-469baf50f911/team-melissa-white2.jpg = 4,270,096 bytes (browser Accept) / 4,270,096 bytes (curl)</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for AC Remodeling</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex,
+Your reviews page still says 47 Google reviews, but your Google profile now shows 55. I also measured the team photo of Carolina at about 5.7MB, which is heavy on a phone.
+I put together a free concept for your homepage, built only from AC Remodeling's own photos and Google reviews. It opens with "Design-Build Remodeling in Gaithersburg, MD, Run by the Owners", shows 5.0 from 55 reviews, and puts your MHIC license and 17 Best of Houzz awards in the first screen. The FAQ also explains the no-free-estimate policy up front.
+https://acremodeling.thecreativezohaib.com/
+It is a private preview, not indexed and not live on your domain. Would a 10-minute call this week work?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex, here's another angle. Right now a visitor learns you don't offer free estimates only after filling in your contact form. The concept answers that in the FAQ, along with how the design retainer is credited toward the build, so the people who reach out already know how you work.
+https://acremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex, this is my last note on the concept. It stays up as a private preview if you or Carolina want to look later:
+https://acremodeling.thecreativezohaib.com/
+Just reply anytime if it's helpful.</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex, I made a free homepage concept for AC Remodeling using your own photos and Google reviews. It leads with you and Carolina running every job and your 5.0 rating from 55 reviews. Private preview: https://acremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>Reviews page says 47 Google reviews vs 55 on Google, plus measured 5,716,609-byte team photo (conversion_notes.current_site_defects, measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -979,12 +1101,48 @@
           <t>mobile performance score below 60: PSI mobile performance 58</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>JDI homepage idea, one phone number</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Hi Arthur,
+I noticed your Google profile lists (360) 844-3985, but the call button on your website dials (360) 844-3234. Your Vancouver bathroom remodeling page also returned a 502 error when I checked it.
+I mocked up a free homepage concept built from your own before and after photos and Google reviews. It uses the Google number as tap-to-call in the header and hero, shows the 4.9 rating from 211 reviews on your Vancouver profile, and puts the 5-year written warranty above the fold.
+https://jdiconstruction.thecreativezohaib.com/
+To be clear, it's a private preview. It isn't indexed and isn't live on your domain. If you'd like a walkthrough, just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Hi Arthur, following up with one detail. Your current homepage FAQ shows the questions, but the answers didn't come through in the page text. In the concept every answer is written out, including what your 5-year warranty covers and the starting prices from your cost calculator.
+https://jdiconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Hi Arthur, I don't want to crowd your inbox, so this is my last email. If the JDI concept is ever useful, it will still be at this private link:
+https://jdiconstruction.thecreativezohaib.com/
+Thanks for your time, and congrats on 211 reviews.</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Hi Arthur, I put together a free homepage concept for JDI Construction from your own photos and reviews. One phone number everywhere, your 4.9 rating from 211 reviews and the 5-year warranty up top: https://jdiconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Phone mismatch (Google 844-3985 vs site 844-3234) and 502 on the Vancouver bathroom page (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1077,12 +1235,48 @@
           <t>mobile performance score below 60: PSI mobile performance 38</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Idea for 3 Day Cabinet Pros' homepage</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Liam,
+Quick heads-up: Google's PageSpeed test scored your homepage 38 out of 100 on mobile, and your 5.0 rating from 130 Google reviews isn't shown anywhere on the site.
+I built a free homepage concept from your own kitchen photos and Google reviews. Your 130 reviews sit right under the headline, three real ones from Glen, Valerie and Lou follow, and it names the Stateline towns you cover in Illinois and Wisconsin.
+https://3daycabinetprosandmore.thecreativezohaib.com/
+It's only a private preview, not indexed and not on your domain. Would you be open to a short call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Liam, one more thought. Your current homepage hero uses a stock-style picture, while your portfolio has strong before and after kitchens. The concept swaps in your own finished kitchens and adds a "1 to 2 days for most cabinet installs" badge, which says what your name promises.
+https://3daycabinetprosandmore.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Liam, last message from me on this. The concept is still at the private link below if you ever want a look:
+https://3daycabinetprosandmore.thecreativezohaib.com/
+Thanks, and keep up the great reviews.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Liam! I made a free homepage concept for 3 Day Cabinet Pros using your own kitchens and reviews. Your 5.0 rating from 130 Google reviews is right up top. Private preview here: https://3daycabinetprosandmore.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>Counters render as '1 Average Employee Tenure' and '0 Not 3 weeks' and the 5.0/130 rating is not shown (conversion_notes.current_site_defects). | Revised: counter claims removed after a browser check showed they were animation or crawl artifacts.</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1178,12 +1372,48 @@
           <t>mobile performance score below 60: PSI mobile performance 58</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Westlake Village homepage for All Exclusive</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jacob,
+Your homepage says "5 Star Rated with 80+ Reviews", while your Google profile shows 27. The title and headline also target Santa Clarita, even though your Google address is in Westlake Village.
+So I drafted a free homepage concept with your own project photos and Google reviews. It leads with bathroom remodeling in Westlake Village, shows 5.0 from 27 exactly as Google does, and puts your CA license number and 24-hour reply in the first screen. Leobardo's review about comparing three bids is featured too.
+https://allexclusivepro.thecreativezohaib.com/
+It's a private preview: not indexed, not on your domain. If it looks useful, reply and we can find 10 minutes.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jacob, following up with a phone detail. On the concept, the number in the header is a tap-to-call link, and the FAQ answers what homeowners ask before they call: bathroom cost, tub-to-shower conversions, HOA approval and permits in Westlake Village. Same link:
+https://allexclusivepro.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jacob, I'll close the loop here. The All Exclusive concept stays up privately if you want it later, whether for ideas or a full rebuild:
+https://allexclusivepro.thecreativezohaib.com/
+Appreciate you reading, and if it's not a fit, no worries.</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jacob, I built a free homepage concept for All Exclusive Construction from your own photos and reviews. It focuses on Westlake Village bathrooms and shows your Google rating as it is. Private link: https://allexclusivepro.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>Homepage claims 80+ reviews vs 27 on Google, and Santa Clarita targeting vs Westlake Village GBP (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1264,12 +1494,48 @@
           <t>gallery images over 1MB each: https://annarborremodelingllc.com/wp-content/uploads/2023/09/3-print-DJI_0783-scaled.jpg = 1,558,929 bytes; https://annarborremodelingllc.com/wp-content/uploads/2023/09/Devonshire-MCM-Remodel-Labra-Photos-2023-08-29-04.jpg = 1,911,628 bytes; https://annarborremodelingllc.com/wp-content/uploads/2023/09/Devonshire-MCM-Remodel-Labra-Photos-2023-08-29-13.jpg = 2,085,123 bytes | re-measured 2026-10-14 (full download): c.com/wp-content/uploads/2023/09/3-print-DJI_0783-scaled.jpg = 1,558,929 bytes (browser Accept) / 1,558,929 bytes (curl); 023/09/Devonshire-MCM-Remodel-Labra-Photos-2023-08-29-04.jpg = 1,911,628 bytes (browser Accept) / 1,911,628 bytes (curl); 023/09/Devonshire-MCM-Remodel-Labra-Photos-2023-08-29-13.jpg = 2,085,123 bytes (browser Accept) / 2,085,123 bytes (curl)</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Ann Arbor Remodeling</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin,
+Your portfolio photos are excellent, but three of them weigh between 1.5MB and 2MB each, which slows the site on phones. The footer also still reads 2020, and the phone number is plain text with no tap-to-call.
+I made a free homepage concept from your own photos and Google reviews. It leads with design-build remodeling in Ann Arbor and transparent pricing, adds tap-to-call at the top and bottom, and shows your 4.9 rating from 86 reviews. The FAQ explains why you show your actual costs and what a lead carpenter does.
+https://annarborremodelingllc.thecreativezohaib.com/
+This is just a private preview. It's not indexed and not live on your domain. Want to hop on a quick call?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, something else worth a look. Your Google reviews mention you and Nolan by name, and Lauren R. talks about her attic becoming a home office. Right now none of that appears on your homepage. The concept shows three of those reviews with the 4.9 rating.
+https://annarborremodelingllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, final note. If transparent pricing ever becomes the focus of a site refresh, the concept will be waiting at this private link:
+https://annarborremodelingllc.thecreativezohaib.com/
+A short reply is all it takes if you want to talk.</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, I made a free homepage concept for Ann Arbor Remodeling using your own photos and reviews. It leads with your transparent pricing and lead carpenter system, with tap-to-call up top: https://annarborremodelingllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>Measured gallery photos of 1,558,929 to 2,085,123 bytes, footer dated 2020, no tap-to-call (measured_defects, conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1367,12 +1633,48 @@
           <t>mobile performance score below 60: PSI mobile performance 48</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Condo-first homepage for Assembly Squad</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor,
+On your homepage, the Wicker Park before and after slider requests a Before photo that returns a 404. Google's PageSpeed test also scored the mobile page 48 on the day I checked.
+I built a free concept from your own project photos and Google reviews that leads with condo remodeling in Chicago. Your 300+ pre-approved buildings appear in the first screen, the 4.9 rating from 87 reviews sits under the headline, and the reviews feature Lakeview East and Gold Coast condo owners.
+https://assemblyserviceil.thecreativezohaib.com/
+It's a private preview, so it isn't indexed or live on your domain. Would a 10-minute call this week be worth it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, quick follow-up. The concept's FAQ opens with the question condo buyers worry about most: who deals with the board and building management. It also covers cost, timing and seeing materials at the Lincoln Park studio, all in plain text. Have a look:
+https://assemblyserviceil.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, I'll stop here so I'm not a pest. The condo concept will stay available at this private link:
+https://assemblyserviceil.thecreativezohaib.com/
+Thanks, and best of luck with the next round of Chicago projects.</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, I made a free condo-first homepage concept for Assembly Squad from your own photos and reviews: 300+ pre-approved buildings and your 4.9 Google rating up top. Private preview: https://assemblyserviceil.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>Wicker Park slider Before image returns HTTP 404, plus PSI mobile 48 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1468,12 +1770,48 @@
           <t>mobile performance score below 60: PSI mobile performance 45; gallery images over 1MB each: https://crafthomeremodel.com/api/media/file/Devilbiss-Complete-Home-Remodel-4.png = 2,362,621 bytes; https://crafthomeremodel.com/api/media/file/modern-kitchen-island-skylights-and-patio-access.jpeg = 1,641,262 bytes | re-measured 2026-10-14 (full download): del.com/api/media/file/Devilbiss-Complete-Home-Remodel-4.png = 2,362,621 bytes (browser Accept) / 2,362,621 bytes (curl); a/file/modern-kitchen-island-skylights-and-patio-access.jpeg = 1,641,262 bytes (browser Accept) / 1,641,262 bytes (curl)</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Craft Home Remodeling</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey,
+Your home and about pages say "Call Us Today 858-351-0320", but your Google profile and footer use (858) 888-9139. One project photo on your projects page also loads at about 2.4MB.
+I made a free homepage concept for Craft, pulling only from your own projects and Google reviews. It uses one tap-to-call number, the one on Google, and opens with "Bathroom Remodeling in San Diego, Designed With the Owner". Your 5.0 rating and Best of Houzz Service 2026 sit up top, and Bonita's review about getting a designer space follows.
+https://crafthomeremodel.thecreativezohaib.com/
+The link is a private preview; search engines won't index it and it isn't on your domain. Interested in a quick chat?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey, adding one point. On the bathroom and kitchen pages of your current site there is no main headline at all. The concept puts a clear one at the top, labels each photo with its real neighborhood, and answers whether people need a separate designer.
+https://crafthomeremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey, last message on this from my side. The Craft concept stays up as a private preview whenever you want to come back to it:
+https://crafthomeremodel.thecreativezohaib.com/
+Thanks for reading, and congrats on Best of Houzz.</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey! I built a free homepage concept for Craft Home Remodeling using your own projects and reviews. One phone number, your 5.0 rating and the owner-led design angle up top: https://crafthomeremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>Two phone numbers (858-351-0320 on site vs Google 888-9139) and a 2,362,621-byte gallery image (conversion_notes.current_site_defects, measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1571,12 +1909,48 @@
           <t>mobile performance score below 60: PSI mobile performance 38</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Forward Design Build: homepage concept</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jef,
+Your NARI Contractor of the Year awards and 5.0 rating from 66 Google reviews never show on your homepage. There's also no phone number in the header, and Google's PageSpeed test scores the mobile page 38.
+As a free sample, I put together a homepage concept with Forward's own project photos and Google reviews. The headline targets kitchen remodeling in Ann Arbor, the 5.0 rating and NARI awards sit just below it, and tap-to-call is in the header. The FAQ also covers your published price ranges and the Terra Knoll rental home.
+https://planforward.thecreativezohaib.com/
+It's only a private preview, not indexed and not live on your domain. Open to a short call?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jef, circling back with an idea. Your current homepage still mentions working "in a safe and controlled environment", which reads like pandemic-era copy. The concept replaces it with your three concepts at three price points, so a homeowner sees how planning works before they call.
+https://planforward.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jef, I'll leave this with you. The Forward concept stays at this private link for whenever the timing is right:
+https://planforward.thecreativezohaib.com/
+If it's ever helpful, just reply and we can set up a call.</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jef, I made a free homepage concept for Forward Design Build using your own photos and reviews. It leads with Ann Arbor kitchens, your NARI awards and the 5.0 Google rating. Private preview: https://planforward.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>NARI awards and 5.0/66 rating missing from homepage, no header phone, PSI 38 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1667,12 +2041,48 @@
           <t>mobile performance score below 60: PSI mobile performance 55; gallery images over 1MB each: https://sdwuaksbmiflgmpqozge.supabase.co/storage/v1/object/public/website-photos/5E%20Hackensack-Kitchen-polished%20after%202.JPEG = 5,820,755 bytes; https://sdwuaksbmiflgmpqozge.supabase.co/storage/v1/object/public/website-photos/5E%20Hackensack-kitchen-polished%20after.JPEG = 4,976,917 bytes; https://sdwuaksbmiflgmpqozge.supabase.co/storage/v1/object/public/website-photos/5E%20Hackensack-Kitchen-polished%20after%202.JPEG = 5,820,755 bytes; https://sdwuaksbmiflgmpqozge.supabase.co/storage/v1/object/public/website-photos/5E%20Hackensack-kitchen-polished%20after.JPEG = 4,976,917 bytes | re-measured 2026-10-18 (full download): ite-photos/5E%20Hackensack-Kitchen-polished%20after%202.JPEG = 5,820,755 bytes (browser Accept) / 5,820,755 bytes (curl); website-photos/5E%20Hackensack-kitchen-polished%20after.JPEG = 4,976,917 bytes (browser Accept) / 4,976,917 bytes (curl); ite-photos/5E%20Hackensack-Kitchen-polished%20after%202.JPEG = 5,820,755 bytes (browser Accept) / 5,820,755 bytes (curl); website-photos/5E%20Hackensack-kitchen-polished%20after.JPEG = 4,976,917 bytes (browser Accept) / 4,976,917 bytes (curl); ct/public/website-photos/Glen%20Rock%20Deck%20after%209.JPEG = 1,266,149 bytes (browser Accept) / 1,266,149 bytes (curl); ct/public/website-photos/North%20haledon%20deck%20after.JPEG = 1,469,701 bytes (browser Accept) / 1,469,701 bytes (curl); v1/object/public/website-photos/Westwood%20deck%20after.JPEG = 1,230,555 bytes (browser Accept) / 1,230,555 bytes (curl); /object/public/website-photos/Morristown%20deck%20after.JPEG = 1,248,986 bytes (browser Accept) / 1,248,986 bytes (curl); website-photos/Hawthorne%20Metro%20vista%20Deck%20After.JPEG = 1,134,304 bytes (browser Accept) / 1,134,304 bytes (curl); ct/public/website-photos/Glen%20Rock%20deck%20after%208.JPEG = 1,227,252 bytes (browser Accept) / 1,227,252 bytes (curl); website-photos/Commercial-chip%20and%20birdies-%20after.JPEG = 1,192,857 bytes (browser Accept) / 1,192,857 bytes (curl)</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr"/>
-      <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Hamlett Renovations</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Devin,
+Your site already does a lot right: published prices, a named service area and your license up front. One thing stands out, though. The two Hackensack kitchen photos weigh about 5.8MB and 5.0MB, almost 11MB together, and Google scores the mobile site 55.
+I built a free homepage concept for Hamlett out of your own project photos and Google reviews. It puts "kitchen remodeling in Wayne, NJ" in the headline, shows 5.0 from 56 reviews, and lists ranges like $12,000 to $40,000 for bathrooms.
+https://hamlettrenovations.thecreativezohaib.com/
+It's a private, unindexed preview and it isn't on your domain. Happy to talk if you reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Devin, another small idea. Most FAQ answers on your current site sit in collapsed sections, so only the cost answer came through in the page text. The concept writes out answers on timelines, the first meeting, licensing and working from existing architect plans.
+https://hamlettrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Devin, wrapping up on my end. The Wayne concept is still at the private link below if you'd like to compare it with your current site later:
+https://hamlettrenovations.thecreativezohaib.com/
+Thanks, and congrats on the 5.0 rating.</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Devin, I made a free homepage concept for Hamlett Renovations from your own photos and reviews. Lighter images, Wayne, NJ up top and your 5.0 Google rating from 56 reviews: https://hamlettrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>Measured Hackensack kitchen photos of 5,820,755 and 4,976,917 bytes, PSI 55 (measured_defects, outreach_hook).</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1770,12 +2180,48 @@
           <t>mobile performance score below 60: PSI mobile performance 41</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr"/>
-      <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>McDonald Remodeling homepage concept</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris,
+Your phone number shows up only as plain text in the footer, "651.554.1234". None of the 16 pages I checked has it in the header or as a tap-to-call link, and the mobile homepage scores 41 on Google's speed test.
+Here's a free homepage concept I made with McDonald's own project photos and Google reviews. Tap-to-call sits in the header and hero, and the first screen shows your 4.9 rating from 50 reviews, the 2026 Regional Chrysalis Award and your MN license. Your day-by-day scheduling is explained up front.
+https://mcdonaldremodeling.thecreativezohaib.com/
+The preview is private, not indexed, and not connected to your domain. Could we find 10 minutes this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, following up on accessibility. Karla F. wrote that you remodeled her bathroom to be more accessible as she ages. The concept features her review and answers the accessibility question in the FAQ, since many homeowners search for exactly that.
+https://mcdonaldremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I'll wrap up here. The McDonald concept stays up privately, so feel free to share it with Amy or the team:
+https://mcdonaldremodeling.thecreativezohaib.com/
+Thanks for your time, and congrats on the Chrysalis award.</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I built a free homepage concept for McDonald Remodeling from your own photos and reviews: tap-to-call up top, your 4.9 Google rating and the 2026 Chrysalis award. Private link: https://mcdonaldremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>Phone only as plain footer text with no tap-to-call on 16 crawled pages, PSI 41 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1875,12 +2321,48 @@
           <t>mobile performance score below 60: PSI mobile performance 38</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr"/>
-      <c r="X14" s="2" t="inlineStr"/>
-      <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for ALL Renovation</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amos,
+Google's PageSpeed test gives your mobile site a 38 out of 100, and some gallery photos are close to 1MB each. Your 10-year workmanship guarantee, your strongest promise, sits halfway down the About page.
+I made a free homepage concept from the photos and Google reviews you already have. It leads with what's solid: workmanship guaranteed up to 10 years, your 4.9 rating from 63 reviews and the 2006 founding. The second button books your free discovery call.
+https://allrd.thecreativezohaib.com/
+This is a private preview, not indexed and not live on your domain. Would a quick call work for you?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amos, a follow-up note. Liz H. wrote that this was her fourth project with your team. The concept puts that review on the homepage and lists the towns you serve, from Manheim and Lititz to Hershey and Lebanon, which your current homepage doesn't name.
+https://allrd.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amos, my final message about this. The ALL concept will stay at this private link in case it helps when you next look at the site:
+https://allrd.thecreativezohaib.com/
+Best wishes to you and the crew.</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>Hi Amos, I made a free homepage concept for ALL Renovation &amp; Design using your own photos and reviews. It leads with your 10-year workmanship guarantee and 4.9 Google rating. Private preview: https://allrd.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Conflicting counters (50+ on About vs 148+ on kitchen page) and PSI 38 (conversion_notes.current_site_defects, pagespeed_mobile). | Revised: counter claims removed after a browser check showed they were animation or crawl artifacts.</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1975,12 +2457,52 @@
           <t>mobile performance score below 60: PSI mobile performance 35; gallery images over 1MB each: https://bossdesigncenter.com/wp-content/uploads/2025/07/kitchen-renovation-in-French-Style-4-1.jpg = 1,503,931 bytes; https://bossdesigncenter.com/wp-content/uploads/2025/10/Reno-Maryland-9854-Kentsdale-Dr-Potomac-Photos-4-of-20.jpg = 1,188,836 bytes | re-measured 2026-10-14 (full download): t/uploads/2025/07/kitchen-renovation-in-French-Style-4-1.jpg = 1,503,931 bytes (browser Accept) / 1,503,931 bytes (curl); 0/Reno-Maryland-9854-Kentsdale-Dr-Potomac-Photos-4-of-20.jpg = 1,188,836 bytes (browser Accept) / 1,188,836 bytes (curl)</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
-      <c r="X15" s="2" t="inlineStr"/>
-      <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>Boss Design Center homepage idea</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taha,
+Your 5.0 rating from 145 Google reviews is a standout, yet it doesn't appear anywhere on your site. Both showroom numbers are also plain text, with no tap-to-call link in the header or elsewhere.
+So I built a free concept for the homepage using your real project photos and Google reviews. The header and hero have tap-to-call, the first screen leads with 145 reviews rated 5.0, and the 5-year structural warranty follows. Three named Google reviews replace the anonymous quotes.
+https://bossdesigncenter.thecreativezohaib.com/
+It stays private, unindexed and off your live domain. Would you have 10 minutes this week to look at it together?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taha, a note on mobile speed. A few of your portfolio photos load at 1.2MB to 1.5MB, and Google's mobile speed score is 35. The concept keeps your real project photography but is built to load lighter on phones, with Bethesda in the headline to match your Google profile.
+https://bossdesigncenter.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taha, closing out my notes on this. The Boss Design Center concept remains at this private link if you'd like to review it with your team:
+https://bossdesigncenter.thecreativezohaib.com/
+Just reply if you'd like to talk.</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taha, I made a free homepage concept for Boss Design Center from your own photos and reviews. Your 5.0 rating from 145 Google reviews is front and center, with tap-to-call up top: https://bossdesigncenter.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>5.0/145 rating not shown and no tap-to-call anywhere (conversion_notes.current_site_defects). Email is talha@ and reviews say 'Talha' while owner field says Taha; confirm the name.</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>Owner name: the record says Taha, but the email (talha@) and reviews say Talha. Confirm the spelling.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2080,12 +2602,52 @@
           <t>mobile performance score below 60: PSI mobile performance 54</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="2" t="inlineStr"/>
-      <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Degnan</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hi Abe,
+On your site the phone number lives only in the footer, and the contact email is spelled out as "[at]" and "[dot]", so a phone visitor can't tap either one. Your 5.0 rating from 26 Google reviews isn't on the homepage yet.
+I designed a free homepage concept for Degnan with your own photos and Google reviews. It has tap-to-call in the header and hero, a kitchen remodeling Madison headline, and badges for the 5.0 rating, the 1981 founding and your 14th year as a Guildmaster. The free ballpark estimate is spelled out too.
+https://degnandesignbuildremodel.thecreativezohaib.com/
+It's a private preview, so it isn't indexed and doesn't touch your live domain. Up for a short call?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Hi Abe, a thought on your reviews. Patricia H. and Betsy B. both wrote warm reviews about big projects, including a second floor in a 100-year-old home. The concept puts three of those reviews on the homepage along with the Dane County towns you serve.
+https://degnandesignbuildremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Hi Abe, final note from me. The Degnan concept stays up as a private preview if you, Amy or the team want a look:
+https://degnandesignbuildremodel.thecreativezohaib.com/
+Thanks for reading, and congrats on 14 years as a Guildmaster.</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>Hi Abe, I built a free homepage concept for Degnan Design-Build-Remodel using your own photos and reviews: tap-to-call, your 5.0 Google rating and the free ballpark call up top. https://degnandesignbuildremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>Phone only in footer and email written as [at]/[dot] (conversion_notes.current_site_defects). Email goes to amy@, not Abe directly.</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>The email goes to amy@ but greets Abe; Amy is likely office staff. Fine to send, or reach Abe by phone.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2180,12 +2742,52 @@
           <t>mobile performance score below 60: PSI mobile performance 45</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="2" t="inlineStr"/>
-      <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>KBF homepage idea and a phone mismatch</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ashley,
+Every call button on your site dials 407-499-8694, but your Google Business Profile lists 407-337-8609. It may be intentional for tracking, but it's worth checking. Google also scores the mobile homepage 45, likely due in part to the scroll film and map animations.
+I built a free concept for a lighter homepage, using KBF's own project photos and Google reviews. It focuses on kitchen remodeling in Maitland, with your 4.8 rating, the 2003 founding and your 5-year warranty in the first screen. It uses the Google number for now; your team would pick which to keep.
+https://kbfdesigngallery.thecreativezohaib.com/
+It's a private preview, not indexed and not live on your domain. Glad to chat if useful.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ashley, one follow-up. The FAQ answers on your Maitland page sit in collapsed sections, so only the questions show in the page text. The concept answers them in the open, including load-bearing walls and permits in Maitland. Have a look here:
+https://kbfdesigngallery.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ashley, last note on this one. I know you have marketing help in-house, so treat the concept as ideas to borrow. It stays at the private link:
+https://kbfdesigngallery.thecreativezohaib.com/
+Thanks for reading.</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ashley, I put together a free, lighter homepage concept for KBF Design Gallery from your own photos and reviews, focused on Maitland kitchens with your 4.8 Google rating up top: https://kbfdesigngallery.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>NAP phone conflict (site 407-499-8694 vs Google 407-337-8609), PSI 45 (conversion_notes.current_site_defects). Research note flags a weak fit: in-house marketing staff.</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>Weaker fit: the firm has in-house marketing staff. Its site phone differs from Google; it may be a call-tracking number on purpose.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2276,12 +2878,52 @@
           <t>mobile performance score below 60: PSI mobile performance 29</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr"/>
-      <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Nip Tuck homepage concept</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Hi April,
+Your homepage hero still has a button inviting people to the October 17 Remodeling Showcase, which has now passed. Google also scores the mobile homepage 29 out of 100.
+With your own project photos and Google reviews, I made a free homepage concept for Nip Tuck. It replaces the event button with evergreen copy and leads with what sets you apart: about 2% average cost variance, 50+ awards and your 4.9 rating from 49 reviews. Tap-to-call sits in the header and hero.
+https://niptuckremodel.thecreativezohaib.com/
+It's a private preview only, not indexed and not on your domain. If you're curious, reply and we can set up a 10-minute call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Hi April, a follow-up idea. Your current FAQ shows only the first answer in the page text. The concept answers each question in full, including how close the final cost lands to the estimate and when Nip Tuck isn't the right fit, which builds trust with careful planners.
+https://niptuckremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Hi April, I'll stop here. The Nip Tuck concept stays at this private preview link, and you're welcome to pass it along to your team:
+https://niptuckremodel.thecreativezohaib.com/
+Thanks for reading, and congrats on the 4.9 rating.</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>Hi April, I made a free homepage concept for Nip Tuck Remodeling from your own photos and reviews. It leads with your 2% cost variance, 50+ awards and 4.9 Google rating: https://niptuckremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>Hero button still promotes the past October 17 showcase, PSI 29 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>The email mentions their October 17 showcase still promoted on the home page. Check it is still there before sending.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2332,11 +2974,7 @@
           <t>info@sfcustomremodeling.com</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>admin@sfrestoration.com</t>
-        </is>
-      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>https://sfcustomremodeling.com/contact/</t>
@@ -2385,12 +3023,48 @@
           <t>mobile performance score below 60: PSI mobile performance 59; gallery images over 1MB each: https://sfcustomremodeling.com/wp-content/uploads/2025/03/Image-47-scaled.jpg = 1,172,592 bytes; https://sfcustomremodeling.com/wp-content/uploads/2025/03/Image-5-3-scaled.jpg = 1,271,825 bytes; https://sfcustomremodeling.com/wp-content/uploads/2025/03/Image-7-2-scaled.jpg = 1,776,368 bytes; https://sfcustomremodeling.com/wp-content/uploads/2025/03/Image-49-1-scaled.jpg = 1,018,686 bytes | re-measured 2026-10-14 (full download): emodeling.com/wp-content/uploads/2025/03/Image-47-scaled.jpg = 1,132,976 bytes (browser Accept) / 1,132,976 bytes (curl); modeling.com/wp-content/uploads/2025/03/Image-5-3-scaled.jpg = 1,231,998 bytes (browser Accept) / 1,231,998 bytes (curl); modeling.com/wp-content/uploads/2025/03/Image-7-2-scaled.jpg = 1,729,114 bytes (browser Accept) / 1,729,114 bytes (curl); odeling.com/wp-content/uploads/2025/03/Image-49-1-scaled.jpg = 979,090 bytes (browser Accept) / 979,090 bytes (curl)</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="2" t="inlineStr"/>
-      <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Semper Fi homepage concept</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jay,
+Your pricing page answers the budget question better than most sites I've seen. On the homepage, though, the header shows two phone numbers side by side, AVL and GVL, while Google lists only (828) 279-6703. Some gallery photos also weigh up to 1.7MB each.
+I put together a free Semper Fi homepage concept from your own project photos and Google reviews. It has one tap-to-call number, leads with two Marine veterans running the team, and shows your published ranges, like $80k to $120k for a same-layout kitchen.
+https://sfcustomremodeling.thecreativezohaib.com/
+Only you can see it: a private preview, not indexed and not live on your domain. Want to talk it over for 10 minutes?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jay, a quick note on reviews. Your site's review widget says 120 reviews from mixed sources, while Google shows 4.9 from 89. The concept states the Google figure once and features three Google reviews, including the one about a mountain home remodel in 9 months.
+https://sfcustomremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jay, this is my last note. The Semper Fi concept will stay up privately if you want to come back to it after a busy season:
+https://sfcustomremodeling.thecreativezohaib.com/
+Thanks for your time, and Semper Fi.</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jay, I built a free homepage concept for Semper Fi Custom Remodeling from your own photos and reviews: one phone number, your published prices and your 4.9 Google rating up top. https://sfcustomremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>Two header phone numbers vs one on Google, gallery JPEG at 1,729,114 bytes (conversion_notes.current_site_defects, measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2486,12 +3160,48 @@
           <t>mobile performance score below 60: PSI mobile performance 40</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="2" t="inlineStr"/>
-      <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Sweeney Design Remodel homepage idea</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tim,
+Your site gives the company's age three ways: "60 years of experience" on the homepage, "over six decades" on the warranty page and "more than 70 years" on the kitchen page. Founded in 1954, you're at 72. The homepage also has no main heading.
+I made a free concept for your homepage, drawing on your own project photos and Google reviews. It uses 1954 everywhere, puts your nine NARI Contractor of the Year awards and the 4.7 Google rating in the first screen, and explains the trade walk-through on the homepage.
+https://sweeneydesign.thecreativezohaib.com/
+The page is private and unindexed, and it's not on your domain. Would you be open to a short call?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tim, one idea I keep coming back to. The way you bring plumbers, electricians and HVAC partners through a home before pricing is a strong reason to choose you, but it only appears on the Design + Build page. In the concept it's one of the first things a visitor reads.
+https://sweeneydesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tim, signing off on this thread. The Sweeney concept stays available at this private link if you'd like to show it around the office:
+https://sweeneydesign.thecreativezohaib.com/
+Congrats on 72 years in Madison.</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tim, I put together a free homepage concept for Sweeney Design Remodel from your own photos and reviews, leading with 1954, nine NARI awards and your trade walk-through: https://sweeneydesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>Company age stated three ways (60, six decades, 70+) vs 1954 founding, no H1 (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2588,12 +3298,52 @@
           <t>mobile performance score below 60: PSI mobile performance 34; gallery images over 1MB each: https://wadedesigninc.com/wp-content/uploads/2025/07/Pawnee_Bath_Wade_Design_Ryan_Hainey_Photography_005_web.jpg = 1,697,303 bytes (HTTP Content-Length); https://wadedesigninc.com/wp-content/uploads/2021/03/River_Road_Kitchen_Wade_Design_Ryan_Hainey_Photography_001_web.jpg = 1,258,344 bytes (HTTP Content-Length); https://wadedesigninc.com/wp-content/uploads/2025/06/Stratford_Wade_Design_Ryan_Hainey_Photography_001_web.jpg = 1,037,260 bytes (HTTP Content-Length); https://wadedesigninc.com/wp-content/uploads/2025/06/Americana_2_Wade_Design_Ryan_Hainey_Photography_004_web.jpg = 1,443,014 bytes (HTTP Content-Length) | re-measured 2026-10-14 (full download): /Pawnee_Bath_Wade_Design_Ryan_Hainey_Photography_005_web.jpg = 1,697,303 bytes (browser Accept) / 1,697,303 bytes (curl); Road_Kitchen_Wade_Design_Ryan_Hainey_Photography_001_web.jpg = 1,258,344 bytes (browser Accept) / 1,258,344 bytes (curl); 06/Stratford_Wade_Design_Ryan_Hainey_Photography_001_web.jpg = 1,037,260 bytes (browser Accept) / 1,037,260 bytes (curl); /Americana_2_Wade_Design_Ryan_Hainey_Photography_004_web.jpg = 1,443,014 bytes (browser Accept) / 1,443,014 bytes (curl)</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="2" t="inlineStr"/>
-      <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Mequon homepage concept for Wade Design</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael,
+Your contact page lists the office at 5200 W Parkview Drive, while your footer and Google profile say 6510 W Mequon Road. That can confuse visitors and search engines. Your 5.0 rating from 35 Google reviews also isn't shown anywhere on the site.
+Using Wade's own project photos and Google reviews, I built a free homepage concept. It leads with kitchen and bath remodeling in Mequon, uses only the Mequon Road address, and puts the 5.0 rating, your 2025 Chrysalis bath award and 11 years of Best of Houzz Service in the first screen.
+https://wadedesigninc.thecreativezohaib.com/
+It's a private preview that isn't indexed or connected to your domain. Reply if you'd like a quick walkthrough.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, a mobile detail. On phones, your current header shows only a LET'S CHAT button, and the number appears further down. The concept puts tap-to-call (262) 512-1799 in the header and hero, with a consultation request as the second option.
+https://wadedesigninc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I'll leave it here. The Wade concept stays at this private link if you'd like to look later or share it with the team:
+https://wadedesigninc.thecreativezohaib.com/
+Thanks for reading, and congrats on the Chrysalis award.</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I made a free homepage concept for Wade Design &amp; Construction from your own photos and reviews: Mequon up top, your 5.0 Google rating and the 2025 Chrysalis award. https://wadedesigninc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>Address conflict (5200 W Parkview Dr on contact page vs 6510 W Mequon Rd on Google) and 5.0/35 not shown (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>This email was found on their careers page and may reach staff, not the owner.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2685,12 +3435,48 @@
           <t>mobile performance score below 60: PSI mobile performance 51</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr"/>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="2" t="inlineStr"/>
-      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Wood Contracting Chicago</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dillon,
+On woodcontractingchicago.com the header only offers "Schedule Your Consultation," and (312) 405-5837 first shows up in the footer. Google's PageSpeed test also gave the mobile home page a 51.
+I built a free homepage concept from your own project photos and Google reviews. Your number is tap-to-call in the header and hero, the 4.9 rating from 27 reviews and license TGC105501 sit up top, and 15 Chicago neighborhoods share one list. Google can't index it and it isn't on your domain; it's a private preview for you:
+https://woodcontractingchicago.thecreativezohaib.com/
+If any of it is useful, a reply is all it takes. I'm also glad to walk you through it on a 10-minute call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dillon, one more detail on the concept. Your Google reviewers bring up tile work more than anything else, so the page opens on condo and vintage-home bathrooms and quotes three of those reviews word for word. There's also a 3-step estimate form asking for the project, town and start date.
+https://woodcontractingchicago.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dillon, this is my last note on the concept. It stays up as a private preview if you ever want to look at it with Sarah or the crew:
+https://woodcontractingchicago.thecreativezohaib.com/
+If the timing is wrong, no problem at all.</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dillon! I made a free homepage concept for Wood Contracting from your own photos and Google reviews, with tap-to-call right in the header. Private preview, not live anywhere: https://woodcontractingchicago.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>Phone only in the footer, not the header (conversion_notes.current_site_defects) plus PSI mobile 51 (measured_defects); features from what_this_homepage_fixes, checked on the live concept.</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2775,12 +3561,48 @@
           <t>mobile performance score below 60: PSI mobile performance 45</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr"/>
-      <c r="X23" s="2" t="inlineStr"/>
-      <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>A Roseville kitchen homepage for Anani</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Daniel,
+You have ten 5-star Google reviews, but none of them appear on ananiremodeling.com. The home page shows two unsourced testimonials instead, and Google's mobile speed test scored it 45.
+So I put together a free sample homepage using your project photos and those reviews. It leads with kitchen remodeling in Roseville, puts your published planning ranges and permit answers right on the page, and has tap-to-call (916) 404-4780 at the top. Search engines can't see it and it isn't on your domain; think of it as a private draft.
+https://ananiremodeling.thecreativezohaib.com/
+Would you be open to a quick 10-minute call this week to hear your take?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Daniel, circling back with something I think you'll like. Natalie K.'s review about upfront pricing and finishing ahead of schedule is one of three Google reviews quoted on the concept, right under your kitchen work. On phones, the header keeps your number one tap away the whole time.
+https://ananiremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Daniel, I won't keep filling your inbox. The Roseville kitchen concept is still online as a private preview whenever you have a free minute to look:
+https://ananiremodeling.thecreativezohaib.com/
+Thanks either way, and good luck with the fall projects.</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>Hi Daniel, I built a free homepage concept for Anani Remodeling that finally shows your ten 5-star Google reviews, plus your own project photos. It's private, just for you: https://ananiremodeling.thecreativezohaib.com/ Curious what you think!</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Ten 5-star Google reviews absent from the site (conversion_notes.current_site_defects) plus PSI mobile 45 (measured_defects); price ranges and review checked on the live concept.</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2874,12 +3696,52 @@
           <t>mobile performance score below 60: PSI mobile performance 58; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 385px, i.e. 10px wider than the screen; elements past the right edge: ['DIV.swiper-slide right=520', 'FIGURE.swiper-slide-inner right=520', 'IMG.swiper-slide-image right=520']</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>Your before-and-after slider on phones</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Hi Don,
+I opened betterremodels.com at iPhone width (375px) and the page measured 385px wide. The before-and-after slider runs past the right edge, so the page drifts sideways when someone scrolls.
+Working from your gallery photos and Google reviews, I made a free concept homepage that fits the screen. It has one clear headline on kitchen remodeling in Orange County, your 40 town-labeled projects, three real reviews that mention you by name, and a tap-to-call button for (949) 508-0300. The preview is private: unindexed and not connected to your domain.
+https://betterremodels.thecreativezohaib.com/
+Reply if you'd like to talk it over. Ten minutes on the phone is plenty.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Hi Don, wanted to point out one part of the concept. It lists Orange and 39 more Orange County communities in a single service-area section, and the FAQ answers the walk-in tub and referral questions in plain text, so phone visitors don't have to open anything.
+https://betterremodels.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>Hi Don, one final message. If a new homepage ever moves up your list, the Orange County concept will still be waiting at the same private link:
+https://betterremodels.thecreativezohaib.com/
+All the best with the projects ahead.</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>Hey Don, I put together a free homepage concept for Better Remodels using your before-and-after gallery and Google reviews. It fits iPhone screens with no sideways scroll. Private link: https://betterremodels.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>375px overflow from the before-and-after slider (measured_defects); greeted as Don because the Google reviews and outreach_hook use that name for Donald Garcia.</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>Greeting uses Don (Donald in the record), as in his Google reviews.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2980,12 +3842,48 @@
           <t>mobile performance score below 60: PSI mobile performance 47; gallery images over 1MB each: https://static1.squarespace.com/static/6637e400a65dba341668e469/t/68c98059087f14378e341b74/1758036071094/KC+Outdoor+Living+Final.jpg = 2,048,349 bytes; https://static1.squarespace.com/static/6637e400a65dba341668e469/t/69c68a6d2f55616873bd84ad/1774619246372/Five+Fold+Solutions+KC+Bathroom+2.jpg = 1,190,881 bytes; https://static1.squarespace.com/static/6637e400a65dba341668e469/t/69c6fc7f564c0f29d57d8af1/1774648448920/FIVEFOLD-2.jpg = 2,764,049 bytes; https://static1.squarespace.com/static/6637e400a65dba341668e469/t/69c6aa288b48ea2c6f017fb1/1774627374558/KSP-FFS-DearbornHouseKitchenRemodel%284of5%29.JPG = 12,294,835 bytes | re-measured 2026-10-14 (full download): 469/t/68c98059087f14378e341b74/1758036071094/KC+Outdoor+Livi = 2,048,349 bytes (browser Accept) / 2,048,349 bytes (curl); 469/t/69c68a6d2f55616873bd84ad/1774619246372/Five+Fold+Solut = 1,190,881 bytes (browser Accept) / 1,190,881 bytes (curl); e469/t/69c6fc7f564c0f29d57d8af1/1774648448920/FIVEFOLD-2.jpg = 2,764,049 bytes (browser Accept) / 2,764,049 bytes (curl); 469/t/69c6aa288b48ea2c6f017fb1/1774627374558/KSP-FFS-Dearbor = 12,294,835 bytes (browser Accept) / 12,294,835 bytes (curl)</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr"/>
-      <c r="X25" s="2" t="inlineStr"/>
-      <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>A 12MB kitchen photo on fivefoldkc.com</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Max,
+One photo on your site, the Dearborn House kitchen, downloads at 12,294,835 bytes, about 12.3MB. Google's mobile test gave the home page a 47.
+Five Fold's new homepage concept is ready, and it's free: every image is one of your own photos, and the quotes are your Google reviews. It centers on bathroom remodeling in Overland Park, shows 5.0 stars from 8 Google reviews in the first screen, and writes out the FAQ answers on the free consultation, tub-to-shower and permits in plain text. It's a private link only you have, not indexed and not on your domain.
+https://fivefoldkc.thecreativezohaib.com/
+Worth a look? A reply works, or we can do a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Max, one more thought. Your 10 to 15 minute first call is a great low-pressure offer, so the concept makes it the closing headline. The Johnson County towns, from Leawood to Bonner Springs, now sit together in one list instead of being split between the bathroom page and the footer.
+https://fivefoldkc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Max, closing the loop on my end. You and Jason are welcome to look at the Overland Park bathroom concept anytime, and it stays private:
+https://fivefoldkc.thecreativezohaib.com/
+Thanks for your time, and congrats on 120+ projects.</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Max! I rebuilt the Five Fold homepage as a free concept around Overland Park bathrooms, using your own photos and the 5.0 Google reviews. Have a look (private link): https://fivefoldkc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>12,294,835-byte Dearborn House kitchen photo and PSI mobile 47 (measured_defects); 10 to 15 minute call from best_conversion_angle and the live concept.</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -3087,12 +3985,48 @@
           <t>mobile performance score below 60: PSI mobile performance 43</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="inlineStr"/>
-      <c r="X26" s="2" t="inlineStr"/>
-      <c r="Y26" s="2" t="inlineStr"/>
-      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>Two phone numbers on keselmangroup.com</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zakhar,
+Your header and footer show (216) 677-9562, while your Google profile and your own site schema list (216) 208-6365. Callers and search engines can end up with two different numbers for the same business.
+I made a free homepage concept from your project photos and Google reviews that uses one number, (216) 208-6365, as tap-to-call at the top and bottom. The hero also carries the eight first-place 2025 Cleveland Choice Awards and 4.9 stars from 220 reviews. It sits on a private link that Google doesn't index, separate from your domain.
+https://keselmangroup.thecreativezohaib.com/
+If you have 10 minutes this week, I'd be glad to show you around it.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zakhar, a small detail I enjoyed building. Reviewers name your project managers Ivan and Sergiy, so the concept mentions them by name. The service area runs from Solon to Lakewood with Pepper Pike and Shaker Heights included, and the FAQ spells out the free consultation and financing.
+https://keselmangroup.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zakhar, I'll leave it here for now. The Cleveland kitchen concept remains a private preview if your team wants to look later:
+https://keselmangroup.thecreativezohaib.com/
+Congratulations again on the eight 2025 first places.</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Zakhar, I made a free homepage concept for Keselman with one phone number, your 220 Google reviews and the 2025 Cleveland Choice wins up top, built from your own photos. Preview: https://keselmangroup.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>Header/footer phone (216) 677-9562 vs Google and schema (216) 208-6365 (conversion_notes.current_site_defects); awards and reviews from what_this_homepage_fixes and the live concept.</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -3139,11 +4073,7 @@
           <t>info@kitchenbarn.net</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>info@kitchenbarn.net%c2%a0</t>
-        </is>
-      </c>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t>https://www.kitchenbarn.net/contact-us/</t>
@@ -3189,12 +4119,48 @@
           <t>mobile performance score below 60: PSI mobile performance 51</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr"/>
-      <c r="X27" s="2" t="inlineStr"/>
-      <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Kitchen Barn hero video on mobile</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mathew,
+When I crawled kitchenbarn.net, the hero video returned "Media error: Format(s) not supported or source(s) not found" where the kitchen footage should play. The page also measured 51 for mobile performance.
+As a free sample, I mocked up a new homepage with your kitchen photos and the words of your Google reviewers. A still photo of your work replaces the video, the Poway showroom is in the headline, and the Express Kitchen and Bath track gets its own section on the home page. Think of it as a sketch: private, not indexed and not live on your domain.
+https://kitchenbarn.thecreativezohaib.com/
+Any thoughts? Just hit reply, or pick a time for a short call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mathew, something else worth a look. Reviewers praise David, Kyle and Angel for design help, so those reviews sit right below the showroom section. The concept also states your 5.0 rating from 14 Google reviews, matching the profile, where the current site widget says 16.
+https://kitchenbarn.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mathew, wrapping up from my side. The Poway showroom concept is still up as a private preview for you and David to look through together:
+https://kitchenbarn.thecreativezohaib.com/
+No reply needed if it's not a fit right now.</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mathew, I built a free homepage concept for Kitchen Barn from your own kitchens and Google reviews. It swaps the hero video for a fast photo and features your Express track. Private: https://kitchenbarn.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>Hero video media error in the crawl (conversion_notes.current_site_defects) plus PSI mobile 51 (measured_defects); Express track from best_conversion_angle and the live concept.</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -3294,12 +4260,48 @@
           <t>horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 1800px, i.e. 1425px wider than the screen; elements past the right edge: ['IMG.bg.attachment- right=1536', 'IMG.bg.attachment- right=1800', 'IMG.bg.attachment-original right=1800']</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
-      <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="2" t="inlineStr"/>
-      <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>ARIID home page on an iPhone screen</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ariana,
+On an iPhone-width screen (375px), the ARIID home page renders 1,800px wide because the full-width background images run past the edge. Visitors end up scrolling sideways.
+I built a free concept homepage from your project photos and Google reviews that fits a phone screen. It opens with your story of starting a build company to protect your designs, shows Est. 2006 and the 2021 and 2024 NKBA awards up top, and uses one set of kitchen prices from your kitchen page. It's a private mockup, unindexed and separate from ariidbuild.com.
+https://ariidbuild.thecreativezohaib.com/
+I'd love your reaction. A quick reply or a 10-minute call, whichever is easier.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ariana, here's another piece of the concept. The service area focuses on Kirkland and the Eastside, from Bellevue to Sammamish, instead of out-of-state markets. The permit and move-out questions are answered in open text, and every photo is your own project work.
+https://ariidbuild.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ariana, last message on this, I promise. If you'd like to revisit the Kirkland design-build concept, it stays private at this link:
+https://ariidbuild.thecreativezohaib.com/
+Wishing you and the team a great season.</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ariana! I made a free homepage concept for ARIID that fits iPhone screens and leads with your designer-led story, built from your own projects and reviews. Private preview: https://ariidbuild.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Home page renders 1,800px wide at 375px (measured_defects); story and NKBA awards from best_conversion_angle and the live concept.</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -3395,12 +4397,52 @@
           <t>mobile performance score below 60: PSI mobile performance 45</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
-      <c r="V29" s="2" t="inlineStr"/>
-      <c r="W29" s="2" t="inlineStr"/>
-      <c r="X29" s="2" t="inlineStr"/>
-      <c r="Y29" s="2" t="inlineStr"/>
-      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Gayler Design Build</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris,
+Gayler's phone number isn't in the site header right now. It sits in the footer and body copy, so a phone visitor has to scroll to find a way to call. Your mobile PageSpeed score is 45 as well.
+Using your photos and Google reviews, I built a free homepage concept. Tap-to-call (925) 820-0185 sits in the header and hero, the headline names kitchen remodeling in Danville, and the 5-year warranty and Guildmaster award show as plain text. It's a private preview for you alone, kept out of search and off gaylerdesignbuild.com.
+https://gaylerdesignbuild.thecreativezohaib.com/
+Happy to hear what you think by reply or on a short call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, adding one thing. The concept tells the family story from your grandfather's 1961 start to today, and lists the Tri-Valley and Lamorinda towns, Alamo through Moraga, in one place. Also worth a quick fix on the current site: the home page seminar block still references Thursday, October 15.
+https://gaylerdesignbuild.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I'll stop here. The Danville kitchen concept remains a private preview, so feel free to share the link with your designers:
+https://gaylerdesignbuild.thecreativezohaib.com/
+Thanks for considering it, and best to the family.</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I made a free homepage concept for Gayler Design Build from your own photos and reviews, with tap-to-call in the header and your 5-year warranty up front. Private link: https://gaylerdesignbuild.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>No phone in the header (conversion_notes.current_site_defects) plus PSI mobile 45 (measured_defects); follow-up notes the passed October 15 seminar block from current_site_defects.</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>Follow-up 1 mentions a seminar block dated October 15 on their home page. Re-check before sending it.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -3493,12 +4535,48 @@
           <t>mobile performance score below 60: PSI mobile performance 35; gallery images over 1MB each: https://images.squarespace-cdn.com/content/6388c54f85a4e044606b9c69/b13482e1-4ec4-4300-9bd7-ec77cc58bedd/Norman+Ln+LoRes+%2858+of+77%29.jpg?content-type=image%2Fjpeg = 1,202,921 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/6388c54f85a4e044606b9c69/662f1ee1-0c23-4202-9ee4-5f87ee373dfb/DSC06114.jpg?content-type=image%2Fjpeg = 1,019,161 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/6388c54f85a4e044606b9c69/1734638511088-NGDQGUJ8PFXE27S9CW06/01+-+Deck.jpg?format=2500w = 1,135,850 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/6388c54f85a4e044606b9c69/1727201344342-91LZ130QX6M6CNTL3CMG/1.png?format=2500w = 1,991,562 bytes (HTTP Content-Length) | re-measured 2026-10-14 (full download): 06b9c69/b13482e1-4ec4-4300-9bd7-ec77cc58bedd/Norman+Ln+LoRes = 962,156 bytes (browser Accept) / 962,156 bytes (curl); 06b9c69/662f1ee1-0c23-4202-9ee4-5f87ee373dfb/DSC06114.jpg?co = 547,290 bytes (browser Accept) / 547,290 bytes (curl); 44606b9c69/1734638511088-NGDQGUJ8PFXE27S9CW06/01+-+Deck.jpg? = 1,012,400 bytes (browser Accept) / 1,012,400 bytes (curl); 44606b9c69/1727201344342-91LZ130QX6M6CNTL3CMG/1.png?format=2 = 1,341,078 bytes (browser Accept) / 1,341,078 bytes (curl)</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="inlineStr"/>
-      <c r="X30" s="2" t="inlineStr"/>
-      <c r="Y30" s="2" t="inlineStr"/>
-      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Two broken links on kellowconstruction.com</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kiel,
+The About Us and Our Process links in your footer both land on a "We couldn't find the page" screen, as does the Addition Construction page. The footer lists a P.O. Box while Google shows 310 E Micheltorena St.
+Your own project photos and Google reviews became the raw material for a free homepage concept I put together. It leads with the fixed-price contract, shows 5.0 stars from 15 reviews and License #1070520, uses the Micheltorena address and links only to working pages. The link is private: search engines can't see it, and nothing changes on your domain.
+https://kellowconstruction.thecreativezohaib.com/
+Could I get 10 minutes this week to walk you through it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kiel, another part you may like. The concept names Santa Barbara, Montecito, Goleta, Carpinteria and Hope Ranch in a service-area block, and your weekday hours appear beside the closing call button. Separately, the Facebook link on your current site points to a placeholder URL rather than your page.
+https://kellowconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kiel, just a short goodbye note. The kitchen concept for Kellow will stay private and available if you want to come back to it later:
+https://kellowconstruction.thecreativezohaib.com/
+Take care, and thanks for reading.</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kiel, I built a free homepage concept for Kellow Construction around your fixed-price contract, using your own projects and 5.0 Google reviews. Only you have the link: https://kellowconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>About and Our Process footer links returning page-not-found, plus P.O. Box vs Google street address (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -3623,12 +4701,48 @@
           <t>mobile performance score below 60: PSI mobile performance 28; gallery images over 1MB each: https://rikb.com/wp-content/uploads/2024/05/Portsmouth-RIKB-Kitchen-Remodel-1500x1247.png = 2,302,537 bytes; https://rikb.com/wp-content/uploads/2024/05/coffee-bar.png = 2,741,172 bytes; https://rikb.com/wp-content/uploads/2024/05/RIKB-Design-Build-Kitchen-Bristol.png = 2,166,256 bytes; https://rikb.com/wp-content/uploads/2024/05/East-Greenwich-master-bathroom-remodel-1500x1000.png = 1,820,211 bytes | re-measured 2026-10-14 (full download): ploads/2024/05/Portsmouth-RIKB-Kitchen-Remodel-1500x1247.png = 2,302,537 bytes (browser Accept) / 2,302,537 bytes (curl); https://rikb.com/wp-content/uploads/2024/05/coffee-bar.png = 2,741,172 bytes (browser Accept) / 2,741,172 bytes (curl); ontent/uploads/2024/05/RIKB-Design-Build-Kitchen-Bristol.png = 2,166,256 bytes (browser Accept) / 2,166,256 bytes (curl); 2024/05/East-Greenwich-master-bathroom-remodel-1500x1000.png = 1,820,211 bytes (browser Accept) / 1,820,211 bytes (curl)</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr"/>
-      <c r="V31" s="2" t="inlineStr"/>
-      <c r="W31" s="2" t="inlineStr"/>
-      <c r="X31" s="2" t="inlineStr"/>
-      <c r="Y31" s="2" t="inlineStr"/>
-      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>RIKB photos and mobile load time</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tanya,
+Your coffee bar photo on rikb.com is a 2.7MB PNG, and the Bristol kitchen is another 2.2MB. Google measured the mobile home page at 28.
+Free, no strings: I designed a sample homepage for RIKB with your real project photography and quotes from Google reviewers. It names kitchen and bath remodeling in Warwick in the headline, puts the 1989 founding, five-year workmanship warranty and CKD and CAPS designers near the top, and lists the towns your photos come from, Bristol to Glocester. The page is a private, unlisted preview and has nothing to do with your live site.
+https://rikb.thecreativezohaib.com/
+If you're curious, reply here or let's book a 10-minute call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tanya, a detail from the reviews section. Your clients name Kelly May and Jamie, so those reviews are quoted on the concept with first names and initials. The closing section invites people to walk the Jefferson Boulevard design center before they plan anything.
+https://rikb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tanya, this will be my final email about it. If you ever want a second look at the Warwick concept, it's private and still here:
+https://rikb.thecreativezohaib.com/
+Thank you for reading, and best to the team.</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tanya! I made a free homepage concept for RIKB from your own project photos and Google reviews, putting 1989, your warranty and the design center up top. Private preview: https://rikb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>coffee-bar.png 2,741,172 bytes and Bristol PNG 2,166,256 bytes, PSI mobile 28 (measured_defects); reviewer names from the live concept.</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -3723,12 +4837,48 @@
           <t>mobile performance score below 60: PSI mobile performance 56; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/5ba3e4b211f7845683218892/1759105337806-81ZDLTUOIHH4W43IAVO9/IMG_5694.JPG = 1,430,048 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/5ba3e4b211f7845683218892/1759105341019-6AV04NPIC502MCZIRH5N/IMG_5695.JPG = 1,608,637 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/5ba3e4b211f7845683218892/1759105434625-L55E9QBKD36NGDA242V9/IMG_5678.JPG = 1,626,226 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/5ba3e4b211f7845683218892/1759105435917-8UOA1S6EWQEQ13XJUEVJ/IMG_5680.JPG = 1,526,478 bytes (HTTP Content-Length) | re-measured 2026-10-14 (full download): 845683218892/1759105337806-81ZDLTUOIHH4W43IAVO9/IMG_5694.JPG = 1,099,090 bytes (browser Accept) / 1,099,090 bytes (curl); 845683218892/1759105341019-6AV04NPIC502MCZIRH5N/IMG_5695.JPG = 1,295,552 bytes (browser Accept) / 1,295,552 bytes (curl); 845683218892/1759105434625-L55E9QBKD36NGDA242V9/IMG_5678.JPG = 1,412,220 bytes (browser Accept) / 1,412,220 bytes (curl); 845683218892/1759105435917-8UOA1S6EWQEQ13XJUEVJ/IMG_5680.JPG = 1,261,276 bytes (browser Accept) / 1,261,276 bytes (curl)</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr"/>
-      <c r="X32" s="2" t="inlineStr"/>
-      <c r="Y32" s="2" t="inlineStr"/>
-      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>Your 42 Google reviews, on your homepage</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg,
+Google shows A+ at 5.0 from 42 reviews, but the Reviews page on buildwithaplus.com is empty. Your phone number is also not a tap-to-call link anywhere I checked.
+So I built you a free homepage concept where those reviews finally get a home, alongside your own project photos. Call or text (401) 225-7875 is one tap in the header and hero, three reviews are quoted word for word, and your price calculator is pitched as the easy first step. It's a private preview you're the only one to see: no indexing, not live on your site.
+https://buildwithaplus.thecreativezohaib.com/
+Tell me what you think by reply, or we can talk for 10 minutes.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, wanted to share one more change. The concept expands your one-line About page into the real story: commercial work in Boston, then A+ in January 2018 with an in-house crew. Seekonk, Rehoboth and East Providence are named in the service area, too.
+https://buildwithaplus.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, I'll leave this with you. The Seekonk bathroom concept stays up privately in case it turns out to be useful down the road:
+https://buildwithaplus.thecreativezohaib.com/
+Thanks, and good luck this fall.</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>Hey Greg, I made a free homepage concept for A+ that shows your 5.0 Google reviews and makes your number tap-to-call, using your own project photos. Private link: https://buildwithaplus.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>Empty Reviews page vs 5.0 from 42 Google reviews and no tap-to-call link (conversion_notes.current_site_defects); founder story from the live concept.</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3826,12 +4976,48 @@
           <t>gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/5d66eeced4a70b000157052f/1784648103278-159ZOCK7BX8VYGPGU015/image-asset.png?format=1500w = 1,018,340 bytes; https://images.squarespace-cdn.com/content/v1/5d66eeced4a70b000157052f/1784648236038-AN3RAKL8R6BW4SM6Z5SG/AZNB-097_PhotoEnhancing_Image3_After.png?format=1500w = 1,091,848 bytes; https://images.squarespace-cdn.com/content/v1/5d66eeced4a70b000157052f/1784648843332-L15LWRPCL5A7ZCFMSIEA/image+%2811%29.png?format=1500w = 2,691,432 bytes; https://images.squarespace-cdn.com/content/v1/5d66eeced4a70b000157052f/1784648854386-HZZ99KIEBARYVB63NAEM/image+%2812%29.png?format=1500w = 3,043,238 bytes | re-measured 2026-10-18 (full download): 000157052f/1789411333735-RYSVLW6ACYYCBSLEVXSW/IMG_0953%2B2.p = 1,083,958 bytes (browser Accept) / 2,874,520 bytes (curl); 000157052f/1782151711855-FD1S90C2K6XLBZXD9C51/AZNewBathAugus = 1,006,970 bytes (browser Accept) / 1,006,970 bytes (curl); 000157052f/1781130165343-BCOHQK2OQIPZ3PUE6YIM/Shower%2BRemod = 781,668 bytes (browser Accept) / 781,668 bytes (curl)</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
-      <c r="V33" s="2" t="inlineStr"/>
-      <c r="W33" s="2" t="inlineStr"/>
-      <c r="X33" s="2" t="inlineStr"/>
-      <c r="Y33" s="2" t="inlineStr"/>
-      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>One phone number for AZ New Bath</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan,
+Your Google profile lists (623) 281-3691, but aznewbath.com uses others: 623-745-2568 in the header, 623-439-8607 on the quote page, and 623-404-8720 and 602-803-1574 elsewhere. That mix can confuse callers and search engines.
+The free concept I made for you runs on your own bathroom photos and Google reviews. It uses the Google number as tap-to-call at the top and bottom, and the hero shows 1 to 2 day showers, the lifetime warranty, ROC #264481 and 4.7 stars from 89 reviews. It's tucked away privately, not indexed and not on your domain.
+https://aznewbath.thecreativezohaib.com/
+Open to a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, checking back with one more point. The concept answers the question most homeowners worry about, whether they'll lose a working bathroom, right in the intro. It also lists the Valley and Prescott-area towns you cover in a single section, with the free in-home quote as the next step.
+https://aznewbath.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, last one from me on this. The Peoria bathroom concept is still available as a private preview for you and Jeremy to look over:
+https://aznewbath.thecreativezohaib.com/
+Appreciate your time either way.</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, I built a free homepage concept for AZ New Bath with one phone number, your lifetime warranty and 4.7 Google rating up top, from your own photos. Private preview: https://aznewbath.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>Several site phone numbers, none matching Google's (623) 281-3691 (conversion_notes.current_site_defects); greeted by first name Jonathan from the owner field.</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3930,12 +5116,48 @@
           <t>gallery images over 1MB each: https://www.bayshoreremodels.com/wp-content/uploads/2026/08/wp_img_homepage-brand-01-bayshore-van-on-site-coastal-street.jpg = 2,681,554 bytes; https://www.bayshoreremodels.com/wp-content/uploads/2026/08/03-gulf-blvd-living-room-normalized.png = 6,564,456 bytes; https://www.bayshoreremodels.com/wp-content/uploads/2026/08/wholehome-01-bath-closet-transition-corrected.png?v=portfolio-reconciled-20260814 = 5,199,282 bytes; https://www.bayshoreremodels.com/wp-content/uploads/2026/08/wholehome-06-open-kitchen-great-room-corrected.png?v=portfolio-reconciled-20260814 = 5,255,766 bytes | re-measured 2026-10-17 (full download): wp_img_homepage-brand-01-bayshore-van-on-site-coastal-street = 142,188 bytes (browser Accept) / 142,188 bytes (curl); tent/uploads/2026/08/03-gulf-blvd-living-room-normalized.png = 6,564,456 bytes (browser Accept) / 6,564,456 bytes (curl); wholehome-01-bath-closet-transition-corrected.png?v=portfoli = 5,199,282 bytes (browser Accept) / 5,199,282 bytes (curl); wholehome-06-open-kitchen-great-room-corrected.png?v=portfol = 5,255,766 bytes (browser Accept) / 5,255,766 bytes (curl)</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
-      <c r="V34" s="2" t="inlineStr"/>
-      <c r="W34" s="2" t="inlineStr"/>
-      <c r="X34" s="2" t="inlineStr"/>
-      <c r="Y34" s="2" t="inlineStr"/>
-      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>A 6.6MB image on the Bayshore home page</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin,
+Your pricing is refreshingly clear, but the home page loads a living-room PNG (03-gulf-blvd-living-room-normalized.png) that weighs 6,564,456 bytes. On a phone, that's a heavy download before anyone reaches a price.
+I rebuilt the top of your home page as a free concept, using only your photos and your Google reviews. It opens on a real Largo kitchen, keeps the $28,000 starting price and the 5.0 rating from 87 reviews, and has tap-to-call (813) 489-1552 at the top and bottom. It lives on a private preview link, hidden from search and away from bayshoreremodels.com.
+https://bayshoreremodels.thecreativezohaib.com/
+Reply if it's worth a closer look, or grab 10 minutes with me this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, one more angle. The concept keeps your "burned before" message and turns the prices and written warranty into short badges and service cards. Laura D.'s master bath review is quoted too. Internal links are clean, with no tracking parameters, so each page is crawled under one address.
+https://bayshoreremodels.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, this is the end of my follow-ups. The Largo kitchen concept will stay private if you'd like to look it over when things slow down:
+https://bayshoreremodels.thecreativezohaib.com/
+Best of luck with the busy season.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>Hi Justin, I made a free homepage concept for Bayshore that leads with a real Largo kitchen and your posted prices, built from your own photos and Google reviews. Private: https://bayshoreremodels.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>6,564,456-byte living-room PNG on the home page (measured_defects); prices and rating from what_this_homepage_fixes and the live concept.</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -4028,12 +5250,48 @@
           <t>mobile performance score below 60: PSI mobile performance 39; gallery images over 1MB each: https://cdn.prod.website-files.com/6962d53f17d6448d5360b9c6/6a8844bc153347b239a648ba_6965df3e81ac01b449eecef4_Creative_Ideas_for_Blending_Old_and_New_in_a_Home_Addition_638947323240597196.png = 1,837,517 bytes; https://cdn.prod.website-files.com/6962d53f17d6448d5360b9c6/6a8844bad0f0052fead8adcf_6965dd04168d6f67371bd7f8_Signs_Its_Time_to_Remodel_Your_Bathroom_638932574518778251.png = 1,061,516 bytes; https://cdn.prod.website-files.com/6962d53f17d6448d5360b9c6/6ace62fed3b0407c399ddede_Crain-10.png = 1,512,526 bytes; https://cdn.prod.website-files.com/6962d53f17d6448d5360b9c6/6ac591a29890f17bc32052dc_6980e0bd6c9f70a3a6a3c411_DSC_0474-HDR.jpeg = 3,921,120 bytes</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
-      <c r="V35" s="2" t="inlineStr"/>
-      <c r="W35" s="2" t="inlineStr"/>
-      <c r="X35" s="2" t="inlineStr"/>
-      <c r="Y35" s="2" t="inlineStr"/>
-      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Phone numbers on cs-enterprises.net</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Scott,
+Your site footer shows 210-998-6289 and the About page shows 210-338-2676, while Google lists (210) 485-5424. None of the site numbers match the Google profile.
+To show what one number looks like, I made C&amp;S a free homepage concept with your own project photos and Google reviewer quotes. It uses the Google number as tap-to-call in the header and hero, leads with bathroom remodeling in San Antonio, and puts your free 3D renderings, 2015 founding and veteran- and woman-owned status up top. Nothing about it is public yet: it's a private preview that search engines skip, and your domain is untouched.
+https://cs-enterprises.thecreativezohaib.com/
+Would you and Carol like a quick 10-minute walkthrough this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Scott, a quick add. Google reviewers mention bathroom remodels more than any other job, so the concept shows your bathroom price ranges and timelines in the FAQ. Boerne, Helotes and the other Hill Country towns are listed too, and Carol's design role gets its own mention.
+https://cs-enterprises.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Scott, this is my final follow-up. The San Antonio bathroom concept remains private, so feel free to open it whenever it suits you:
+https://cs-enterprises.thecreativezohaib.com/
+Thanks to you and Carol for your time.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Scott! I made a free homepage concept for C&amp;S Remodeling with one phone number and your free 3D renderings up front, using your own photos and reviews. Private preview: https://cs-enterprises.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Site numbers 210-998-6289 and 210-338-2676 vs Google (210) 485-5424 (conversion_notes.current_site_defects); review topics from current_site_defects.</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -4132,12 +5390,52 @@
           <t>mobile performance score below 60: PSI mobile performance 57</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
-      <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="inlineStr"/>
-      <c r="X36" s="2" t="inlineStr"/>
-      <c r="Y36" s="2" t="inlineStr"/>
-      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>A leftover link on your Who We Are page</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bill,
+The team cards on your Who We Are page link to facebook.com/SidneyMBuckley and twitter.com/SidneyMBuckley, which look like placeholders left over from the theme. Your 4.8 rating from 38 Google reviews also isn't shown on the site.
+There's a free homepage concept waiting for you, made with Craftsman's own project photos and Google reviews. It leads with kitchen remodeling for Portland's older homes, shows the 2025 NARI award, CCB number and Google rating in the first screen, and lists neighborhoods from Laurelhurst to Sellwood. It's a private draft that search engines can't reach, apart from your domain.
+https://craftsmandesign.thecreativezohaib.com/
+Can I show you around on a 10-minute call?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bill, sharing a favorite part. The 1902 Northwest Portland kitchen, with its v-groove wainscot and leaded glass transoms, is featured in the intro, since it shows your old-house work better than any slogan could. The concept FAQ also states the $150,000 to $250,000 kitchen range from your FAQ page.
+https://craftsmandesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bill, one last note. If you'd like to revisit the Portland old-house concept, it's still private and online at the same address:
+https://craftsmandesign.thecreativezohaib.com/
+Thanks for reading, and enjoy the rest of the fall.</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bill, I made a free homepage concept for Craftsman Design that puts your 2025 NARI award and Google rating up top, built from your own projects and reviews. Private preview: https://craftsmandesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>Placeholder SidneyMBuckley social links on the team page (conversion_notes.current_site_defects); NARI award and 1902 kitchen from the live concept.</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>This email was found on their careers page and may reach staff, not the owner.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -4237,12 +5535,52 @@
           <t>mobile performance score below 60: PSI mobile performance 20; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/684edac861644d6e021b9a6c/ef6290ab-b6fe-48eb-88fb-4cd510bfd8e6/Portfolio+Website+Story+3.png = 1,062,088 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/684edac861644d6e021b9a6c/a455b416-6197-45c5-842d-8390e134dcd5/Portfolio+Website+Images.png = 1,849,292 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/684edac861644d6e021b9a6c/1777490639423-F35NG58W3BUM8PIWO4RD/3.png = 1,062,465 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/684edac861644d6e021b9a6c/1777490635753-MQS4KJ42ZP5KNMRATWF3/1.png = 1,262,189 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
-      <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr"/>
-      <c r="X37" s="2" t="inlineStr"/>
-      <c r="Y37" s="2" t="inlineStr"/>
-      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Giveaway dates on remodelsbyelite.com</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jerry,
+Quick heads-up: your site banner says the last day to enter the giveaway is November 4, but the official rules say entries close November 1, 2026. Separately, the home page scores 20 on Google's mobile PageSpeed test.
+Here's a free concept homepage I designed around ELITE's own photography and Google reviews. It puts 4.9 stars from 165 reviews, the 5-year craftsmanship warranty and the Las Positas design center above the fold, and explains REFRESH by ELITE next to full remodels. Consider it a private look only, kept out of Google and off your domain.
+https://remodelsbyelite.thecreativezohaib.com/
+If it's helpful, reply and I can walk you through it in 10 minutes.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jerry, a follow-up thought. The embedded videos on your current pages showed a "not available" error in my crawl, so the concept uses written Google reviews from Jing H., Kristi T. and Adam L. instead. Your Carpinteria to Solvang service area is spelled out as well.
+https://remodelsbyelite.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jerry, my last message on this. Your concept page is staying online, private as before, for whenever ELITE wants it:
+https://remodelsbyelite.thecreativezohaib.com/
+Good luck with the giveaway, and thanks for your time.</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jerry! Free homepage concept for ELITE Remodels, built from your own photos and your 165 Google reviews, with the 5-year warranty up top. Private preview: https://remodelsbyelite.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>Giveaway banner November 4 vs rules November 1, 2026, and PSI mobile 20 (conversion_notes.current_site_defects, measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>The email points out the giveaway banner says November 4 while the rules close entries November 1, 2026. Send before November 1 or remove that line.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -4338,12 +5676,48 @@
           <t>mobile performance score below 60: PSI mobile performance 51</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
-      <c r="V38" s="2" t="inlineStr"/>
-      <c r="W38" s="2" t="inlineStr"/>
-      <c r="X38" s="2" t="inlineStr"/>
-      <c r="Y38" s="2" t="inlineStr"/>
-      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>Your NAHB award on the ELM homepage</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Elliott,
+The 2023 NAHB Remodeler of the Year award sits on your About and How We Work pages, not the home page, and the header has no phone number. Kitchen pricing also differs: $100,000 in the services FAQ and "starting at $125,000" in the budgeting guide.
+Free of charge, I drafted an ELM homepage from your project photos and client reviews on Google. The award, two-year warranty and 5.0 rating from 52 reviews are hero badges, (205) 273-2773 is tap-to-call, and the FAQ uses the $125,000 starting point. It is a private preview, not indexed and not on elmbuilds.com.
+https://elmbuilds.thecreativezohaib.com/
+Worth 10 minutes on the phone this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Elliott, one addition. The concept puts the guaranteed fixed price front and center, and Hank P.'s note about staying on schedule and on budget backs it up. Vestavia Hills, Mountain Brook and Hoover appear in the service area, with the four-step process laid out cleanly.
+https://elmbuilds.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Elliott, I'll close this out. The Homewood kitchen concept is private and still online if you or LeArden want to see it:
+https://elmbuilds.thecreativezohaib.com/
+Thanks, and congratulations again on the NAHB award.</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Elliott, I built a free homepage concept for ELM that leads with your 2023 NAHB award and 5.0 Google rating, using your own projects and reviews. Private preview: https://elmbuilds.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>NAHB award buried, no header phone, and the $100,000 vs $125,000 kitchen price conflict (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -4439,12 +5813,52 @@
           <t>mobile performance score below 60: PSI mobile performance 53</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="inlineStr"/>
-      <c r="X39" s="2" t="inlineStr"/>
-      <c r="Y39" s="2" t="inlineStr"/>
-      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Elite Kitchen &amp; Bath</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Hi David,
+On elitekb.com, the phone number isn't in the home page header; in the page text it first appears near the footer. The 4.8 Google rating isn't on the home page either.
+From your own project photos and Google reviews, I created a free homepage concept. Tap-to-call (516) 365-0595 is at the top and bottom, and the hero shows the 1984 founding, the 9 NARI Contractor of the Year awards and the 6,500 sq ft showroom on Northern Blvd. Only you have the private link; it isn't indexed and isn't on your domain.
+https://elitekb.thecreativezohaib.com/
+Would a short reply or a 10-minute call work for you?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Hi David, pointing out one more feature. Every gallery photo on the concept carries alt text naming the room, material and town, such as the Glen Head kitchen and the Great Neck master bath. On your current site, 77 of 133 content images have none.
+https://elitekb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Hi David, last follow-up from me. The Manhasset concept stays up privately in case you'd like to show it to your father or the design team:
+https://elitekb.thecreativezohaib.com/
+All the best to everyone at Elite.</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>Hi David, I made a free homepage concept for Elite Kitchen &amp; Bath that puts your NARI wins, showroom and phone up top, from your own photos and Google reviews. Private: https://elitekb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>Phone not in header, first near footer (conversion_notes.current_site_defects). Owner field is founder Yeheskel Sharbani; greeted David, who the concept and outreach_hook name as current president.</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>Greeting is to David, the current president; the record lists founder Yeheskel Sharbani as owner.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -4534,12 +5948,48 @@
           <t>mobile performance score below 60: PSI mobile performance 34</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
-      <c r="V40" s="2" t="inlineStr"/>
-      <c r="W40" s="2" t="inlineStr"/>
-      <c r="X40" s="2" t="inlineStr"/>
-      <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Your tile showers, front and center</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anthony,
+The Golden Era home page mixes Unsplash stock photos with your real work, while your best tile showers sit on the gallery page with file names like IMG_5835.jpeg as alt text. Its mobile PageSpeed score is 34.
+I built a free homepage concept using only your own shower and vanity photos and your Google reviews. It shows 4.9 stars from 91 reviews once in the hero, offers call or text (469) 586-6478 at the top and bottom, and names Mansfield as your base. Right now it's a private preview, not on Google and not on goldeneraremodel.com.
+https://goldeneraremodel.thecreativezohaib.com/
+Reply if you'd like to talk, or I can call for 10 minutes.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anthony, there's one more thing I want to flag. The concept explains your Schluter waterproofing and real cement or epoxy grout, which sets you apart from snap-in acrylic panels. Garrett M.'s review about the redone shower is quoted too, right beside your photos.
+https://goldeneraremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anthony, I'll stop following up after this. The DFW bathroom concept is private and available anytime you want to look:
+https://goldeneraremodel.thecreativezohaib.com/
+Thanks, and keep up the great tile work.</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>Hey Anthony, I made a free homepage concept for Golden Era that leads with your own tile showers instead of stock photos, plus your 91 Google reviews. Private preview: https://goldeneraremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>Stock Unsplash photos on the home page while real showers sit in the gallery as IMG_5835.jpeg, PSI mobile 34 (conversion_notes.current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -4625,12 +6075,48 @@
           <t>mobile performance score below 60: PSI mobile performance 51; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/63f43239870bcc1e6e5a8642/1709176361640-K43OA4LW1QPPG3ST2JY9/tempImage1nhmgE.gif?format=1500w = 1,634,684 bytes; https://images.squarespace-cdn.com/content/v1/63f43239870bcc1e6e5a8642/1709176446903-1LNIS40DXE23OR82HCVV/tempImaged5hAs6.gif?format=1500w = 1,959,606 bytes; https://images.squarespace-cdn.com/content/v1/63f43239870bcc1e6e5a8642/1678600747058-4K0SHC1WOJBFNYFVMXS8/Light+Blue+White+Clean+Grid+Family+Photo+Collage+%288%29.png?format=1500w = 1,538,834 bytes; https://images.squarespace-cdn.com/content/v1/63f43239870bcc1e6e5a8642/1709176543025-1GCBICGOD2DJ11PRIMCA/tempImagevOMbRy.gif?format=1500w = 1,357,141 bytes | re-measured 2026-10-14 (full download): 1e6e5a8642/1709176361640-K43OA4LW1QPPG3ST2JY9/tempImage1nhmg = 4,548,280 bytes (browser Accept) / 4,548,280 bytes (curl); 1e6e5a8642/1709176446903-1LNIS40DXE23OR82HCVV/tempImaged5hAs = 5,538,633 bytes (browser Accept) / 5,538,633 bytes (curl); 1e6e5a8642/1678600747058-4K0SHC1WOJBFNYFVMXS8/Light+Blue+Whi = 2,196,110 bytes (browser Accept) / 2,196,110 bytes (curl); 1e6e5a8642/1709176543025-1GCBICGOD2DJ11PRIMCA/tempImagevOMbR = 3,886,622 bytes (browser Accept) / 3,886,622 bytes (curl)</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
-      <c r="V41" s="2" t="inlineStr"/>
-      <c r="W41" s="2" t="inlineStr"/>
-      <c r="X41" s="2" t="inlineStr"/>
-      <c r="Y41" s="2" t="inlineStr"/>
-      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>GIF tiles on the Goldsmith services page</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe,
+Your service tiles are animated GIFs: Kitchens is 4,548,280 bytes, Basements 5,538,633 and Bathrooms 3,886,622. The home page also comes in at 51 on mobile PageSpeed.
+From your project photos and Google reviews, I built a free homepage concept that swaps the GIFs for still photos. It shows 5.0 stars from 77 reviews and License #BC805216 up top, has a "Call Joe" tap-to-call button, and explains the free estimate and 3D design. It's private for now, with no search indexing and no link from your domain.
+https://goldsmithremodelanddesign.thecreativezohaib.com/
+Let me know what you think. A reply or a quick 10-minute call both work.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe, I wanted to follow up on one section. The concept introduces you, Lexie and Broc, and makes it clear the person who quotes the kitchen is the one who builds it. Rochester, Eyota and Lanesboro are named in the service area, and the FAQ covers payments.
+https://goldsmithremodelanddesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe, a final word from me. The Rochester kitchen concept is still private and online if you'd like to look later with Lexie and Broc:
+https://goldsmithremodelanddesign.thecreativezohaib.com/
+Enjoy the rest of October, Joe.</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe! I built a free homepage concept for Goldsmith Remodel and Design with your 77 five-star Google reviews and a Call Joe button, using your own photos. Private preview: https://goldsmithremodelanddesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>Animated GIF tiles of 4,548,280, 5,538,633 and 3,886,622 bytes plus PSI mobile 51 (measured_defects, current_site_defects).</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -4719,12 +6205,45 @@
           <t>mobile performance score below 60: PSI mobile performance 49</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
-      <c r="V42" s="2" t="inlineStr"/>
-      <c r="W42" s="2" t="inlineStr"/>
-      <c r="X42" s="2" t="inlineStr"/>
-      <c r="Y42" s="2" t="inlineStr"/>
-      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for H&amp;H Signature Renovations</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tristan,
+Quick thing I spotted on hhsrenovations.com: every call button dials (561) 269-9658, but your Google profile lists (561) 888-4488. Someone who finds you on Maps and then visits the site sees two different numbers.
+I built a free homepage concept for H&amp;H using your own project photos and Google reviews. It uses the 888-4488 number in every tap-to-call button, shows your 5.0 rating from 101 reviews under the headline, and writes out full FAQ answers on permits and historic districts. It is a private preview, not indexed and not on your domain.
+https://hhsrenovations.thecreativezohaib.com/
+If it's useful, reply and I can walk you through it on a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tristan, one more detail on the H&amp;H concept. The Lake Worth Beach page your Google profile links to scored 49 on Google's mobile PageSpeed test. On the concept, the phone number sits in the header as a tap-to-call link and the free estimate form takes three short steps. https://hhsrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tristan, last note from me. The H&amp;H homepage concept is still up as a private preview if you ever want it: https://hhsrenovations.thecreativezohaib.com/ Happy to hand it over or answer questions.</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tristan, I made a free homepage concept for H&amp;H from your own photos and 101 Google reviews. Every call button uses your 888-4488 number. Private preview: https://hhsrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>Phone mismatch (call buttons dial 269-9658, Google lists 888-4488) from conversion_notes.current_site_defects / outreach_hook; PSI 49 from measured_defects used in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -4818,12 +6337,45 @@
           <t>mobile performance score below 60: PSI mobile performance 41</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
-      <c r="V43" s="2" t="inlineStr"/>
-      <c r="W43" s="2" t="inlineStr"/>
-      <c r="X43" s="2" t="inlineStr"/>
-      <c r="Y43" s="2" t="inlineStr"/>
-      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>A homepage concept for HDR Remodeling</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris,
+I was looking at hdrremodeling.com and noticed the footer lists 5677 Horton Ave., while your Google Business Profile says 5677 Horton St. Small detail, but Google likes the two to match.
+So I put together a free homepage concept for HDR, built from your own project photos and Google reviews. The address matches Google everywhere, (510) 845-6100 is tap-to-call at the top, and your 4.8 rating and 2023 NARI kitchen and bath award sit right under the headline. It's a private preview only: not indexed, not on your domain.
+https://hdrremodeling.thecreativezohaib.com/
+Would you be open to a 10-minute call this week to look at it together?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, a follow-up on the HDR concept. Your current home page headline reads 'Bay Area Design Build' and doesn't mention kitchens or a city. The concept opens with 'Kitchen Remodeling in Berkeley and the East Bay Since 1987' and your rule that work starts only once every material is on site. https://hdrremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>Chris, this is my last note. The HDR concept stays up as a private link if it's ever useful to you or your team: https://hdrremodeling.thecreativezohaib.com/ Congrats on the NARI wins.</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I built a free homepage concept for HDR Remodeling from your own photos and reviews, with your 4.8 rating and NARI awards up top. Private preview here: https://hdrremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>NAP mismatch (footer '5677 Horton Ave.' vs Google '5677 Horton St') from conversion_notes.current_site_defects; H1 'Bay Area Design Build' defect used in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -4918,12 +6470,45 @@
           <t>mobile performance score below 60: PSI mobile performance 44</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="inlineStr"/>
-      <c r="X44" s="2" t="inlineStr"/>
-      <c r="Y44" s="2" t="inlineStr"/>
-      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>Lee's Summit homepage idea for Haven Reno KC</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lorna,
+On havenrenokc.com, the home page has no H1 heading. 'Lee's Summit Remodeling &amp; Design' is set as an H3, so search engines get a weaker signal about what you do.
+I made a free homepage concept for Haven Reno KC from your own photos and Google reviews. It opens with a real H1, 'Bathroom Remodeling in Lee's Summit, Designed by the Owners', puts (816) 607-4099 in the header as a tap-to-call link, and shows your 5.0 rating as readable text. The link is private, search engines can't index it, and nothing touches your live site.
+https://havenrenokc.thecreativezohaib.com/
+Want to talk it through? Reply, or take 10 minutes with me this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lorna, one more idea from the Haven concept. Right now towns only show up as tags under testimonials. The concept adds a named service-area section built from the towns your clients list, plus separate blocks for baths, kitchens, basements, laundry and offices. https://havenrenokc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lorna, I won't keep filling your inbox. If you and Mel want to look at the concept later, the link will still work: https://havenrenokc.thecreativezohaib.com/ Wishing you a good fall.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lorna! I designed a free homepage concept for Haven Reno KC using your own bathroom photos and Google reviews. Tap-to-call up top and a real Lee's Summit headline: https://havenrenokc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>Missing H1 (main heading is an H3) from conversion_notes.current_site_defects / outreach_hook; no service-area list defect used in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4976,7 +6561,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>jamie@jbjbuildersincmi.com%20, jbjbuilder@sbcglobal.net</t>
+          <t>jbjbuilder@sbcglobal.net</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5021,12 +6606,45 @@
           <t>mobile performance score below 60: PSI mobile performance 57; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 389px, i.e. 14px wider than the screen; elements past the right edge: ['DIV.ti-review-item.source-Google right=714', 'DIV.ti-inner right=706', 'DIV.ti-review-content right=686']</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
-      <c r="V45" s="2" t="inlineStr"/>
-      <c r="W45" s="2" t="inlineStr"/>
-      <c r="X45" s="2" t="inlineStr"/>
-      <c r="Y45" s="2" t="inlineStr"/>
-      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for JBJ Building &amp; Remodeling</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jamie,
+I opened jbjbuildersincmi.com on an iPhone-sized screen and the home page scrolls sideways. The Google review slider runs 14px past the right edge, so the whole page shifts when someone swipes.
+I built a free homepage concept for JBJ from your own bath and kitchen photos and your Google reviews. Reviews appear as plain text, so nothing pushes the page wider than the phone. It also uses one number, 616-862-8778, to match Google, and leads with the tile work your reviewers praise. Nobody else can find it: the page is not indexed and is not on your domain.
+https://jbjbuildersincmi.thecreativezohaib.com/
+A quick reply or a 10-minute call this week both work.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jamie, following up on the JBJ homepage concept. Your current contact form asks for a budget right away, with no steps explained first. The concept adds a short four-step process, from free consultation to a walkthrough with you, so that question feels less abrupt. https://jbjbuildersincmi.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Jamie, one last note and then I'll leave you be. The JBJ concept link stays live as a private preview: https://jbjbuildersincmi.thecreativezohaib.com/ If you ever want it, or have questions, just say so.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jamie, I made a free homepage concept for JBJ using your own tile and bath photos plus your 4.9 Google rating, with reviews as plain text instead of a slider. Here it is: https://jbjbuildersincmi.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>Measured horizontal overflow at 375px (review slider 14px too wide) from measured_defects; budget-first form defect from current_site_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -5121,12 +6739,45 @@
           <t>mobile performance score below 60: PSI mobile performance 51; gallery images over 1MB each: https://premierkitchenandbath.com/wp-content/uploads/2026/03/2024-07-30.webp = 1,543,232 bytes; https://premierkitchenandbath.com/wp-content/uploads/2026/03/2024-07-30-11.webp = 1,453,454 bytes; https://premierkitchenandbath.com/wp-content/uploads/2026/03/2024-07-30-8.webp = 1,521,658 bytes; https://premierkitchenandbath.com/wp-content/uploads/2026/03/2024-07-30-7.webp = 1,825,808 bytes | re-measured 2026-10-14 (full download): itchenandbath.com/wp-content/uploads/2026/03/2024-07-30.webp = 1,543,232 bytes (browser Accept) / 1,543,232 bytes (curl); henandbath.com/wp-content/uploads/2026/03/2024-07-30-11.webp = 1,453,454 bytes (browser Accept) / 1,453,454 bytes (curl); chenandbath.com/wp-content/uploads/2026/03/2024-07-30-8.webp = 1,521,658 bytes (browser Accept) / 1,521,658 bytes (curl); chenandbath.com/wp-content/uploads/2026/03/2024-07-30-7.webp = 1,825,808 bytes (browser Accept) / 1,825,808 bytes (curl)</t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
-      <c r="V46" s="2" t="inlineStr"/>
-      <c r="W46" s="2" t="inlineStr"/>
-      <c r="X46" s="2" t="inlineStr"/>
-      <c r="Y46" s="2" t="inlineStr"/>
-      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>Scottsdale homepage concept for Premier</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg,
+While looking at the Scottsdale side of premierkitchenandbath.com, I saw the site lists (480) 969-4700 and (480) 933-7199, but your Google profile uses (480) 573-7182. That mix makes it harder for Google to tie the listing to the site.
+I created a free homepage concept for Premier using your own project photos and Google reviews. It runs one number, the Google one, as tap-to-call, and opens with 'Kitchen Remodeling in Scottsdale, AZ', your 4.9 rating and the 10-year labor warranty. It sits on a private preview link that isn't indexed and isn't on your domain.
+https://premierkitchenandbath.thecreativezohaib.com/
+Could I get 10 minutes with you this week to show you around it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, a quick follow-up. The Scottsdale showroom gallery currently serves photos between 1.45 MB and 1.83 MB each, which is heavy on a phone. The concept uses a lighter, curated gallery of Valley projects and quotes three Google reviews that name Rachel and Chris. https://premierkitchenandbath.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, last note from my side. The Premier concept is still at this private link whenever you have a minute: https://premierkitchenandbath.thecreativezohaib.com/ Thanks for considering it. If any detail on the page is wrong, tell me and I'll fix it.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, I built a free homepage concept for Premier from your own projects and Google reviews: one phone number matching Google, plus your 4.9 rating and 10-year labor warranty up top. https://premierkitchenandbath.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>Phone mismatch (site 969-4700 and 933-7199 vs Google 573-7182) from current_site_defects; gallery images 1.45 to 1.83 MB from measured_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -5220,12 +6871,45 @@
           <t>mobile performance score below 60: PSI mobile performance 59</t>
         </is>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
-      <c r="V47" s="2" t="inlineStr"/>
-      <c r="W47" s="2" t="inlineStr"/>
-      <c r="X47" s="2" t="inlineStr"/>
-      <c r="Y47" s="2" t="inlineStr"/>
-      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Red Fox homepage concept (private preview)</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Hi Denny,
+On redfoxremodeling.com, your phone number isn't in the visible text of the home page. It is only there as a tel: link, and the main buttons go to a form. Your 5.0 Google rating doesn't appear either.
+I put together a free homepage concept for Red Fox from your own St. Paul project photos and Google reviews. It shows (612) 208-2794 as tap-to-call in the header, your 5.0 rating from 37 reviews under the headline, and the starting prices you already publish for each service. It's private: not indexed, and not on your domain.
+https://redfoxremodeling.thecreativezohaib.com/
+Worth a reply? I'm also glad to do a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Hi Denny, one more thing about the Red Fox concept. Your current title tag and H1 don't mention kitchens or Minneapolis. The concept's headline reads 'Kitchen Remodeling Minneapolis Families Can Budget For', with your license number and NARI award as badges. https://redfoxremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Denny, I'll leave it here. If the Red Fox concept is ever useful, it is waiting at this private link: https://redfoxremodeling.thecreativezohaib.com/ Thanks for taking a look. You can share it with your team as is.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>Hi Denny! Free homepage concept for Red Fox, made from your own St. Paul projects and reviews. Tap-to-call up top, your 5.0 rating and your posted starting prices: https://redfoxremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>Phone not in visible home page text and 5.0 rating not shown, from current_site_defects / outreach_hook; title and H1 defect in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -5306,12 +6990,49 @@
           <t>mobile performance score below 60: PSI mobile performance 59</t>
         </is>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
-      <c r="V48" s="2" t="inlineStr"/>
-      <c r="W48" s="2" t="inlineStr"/>
-      <c r="X48" s="2" t="inlineStr"/>
-      <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Remont Remodeling</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor,
+Every page of remontremodel.com shows 425-230-3723, while your Google profile lists (425) 600-1957. Someone who calls from Maps and someone who calls from the site may reach different lines.
+I made a free homepage concept for Remont from your own bathroom photos and Google reviews. It uses (425) 600-1957 for every tap-to-call button, states your rating once as 5.0 from 50 reviews, and adds a gallery of seven of your bathrooms in place of the stock images. This is only a preview at a private address; search engines don't index it and it isn't on your domain.
+https://remontremodel.thecreativezohaib.com/
+If you want a quick walkthrough, reply and we can do 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, a follow-up on the Remont concept. Your current home page shows '122 reviews' in one badge and '5.0 37 reviews' in another. The concept shows one figure, matching Google, and lists warranty terms once per service so pages no longer disagree. https://remontremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, final note from me. The concept for Remont stays available here as a private preview: https://remontremodel.thecreativezohaib.com/ No pressure at all. If anything should change, like the photos or the wording, a short reply is enough.</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Viktor, I built a free homepage concept for Remont Remodeling with your own bathroom photos, a gallery of seven jobs and your Google number on every call button. See it here: https://remontremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>NAP phone mismatch (site 425-230-3723 vs Google 600-1957) from current_site_defects / outreach_hook; conflicting review badges in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>The only email is ihor@ but the owner is Viktor; reviews mention Ihor or Igor, who may be family or a partner. Confirm who reads it.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -5407,12 +7128,49 @@
           <t>mobile performance score below 60: PSI mobile performance 38</t>
         </is>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
-      <c r="V49" s="2" t="inlineStr"/>
-      <c r="W49" s="2" t="inlineStr"/>
-      <c r="X49" s="2" t="inlineStr"/>
-      <c r="Y49" s="2" t="inlineStr"/>
-      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>Kansas City homepage concept for Renovating KC</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steven,
+Heads up: the 'Learn More' button for Full Home Remodels on your home page points to /fullhomeremodels, and that page returned a 404 when it was checked on October 17.
+I designed a free homepage concept for Renovating KC from your own project photos and Google reviews. It opens with 'Kitchen Remodeling in Kansas City', puts (913) 481-1236 in the header as tap-to-call, and moves your 5.0 rating from 88 reviews, the REMY Gold award and the 12-month warranty into the hero. Every service link works. It's a private preview, not indexed and not on renokc.com.
+https://renokc.thecreativezohaib.com/
+Reply if you'd like to see more, or grab 10 minutes with me this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steven, one more note. Your site scored 38 on Google's mobile PageSpeed test, and the testimonials are set as all-caps headings. The concept quotes real Google reviews as normal text and keeps one clean heading per section, with every service button linking to a live page. https://renokc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>Steven, this is my last follow-up. The Renovating KC concept is still at this private link for you and the team: https://renokc.thecreativezohaib.com/ Thanks either way. The page stays private until you decide what to do with it.</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steven, I made a free homepage concept for Renovating KC from your own kitchens and Google reviews, with your REMY award and 5.0 rating up top. Private preview: https://renokc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>Broken link (Full Home Remodels button to /fullhomeremodels returned 404 on 2026-10-17) from current_site_defects / outreach_hook; PSI 38 from measured_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>The email mentions a 404 on their Full Home Remodels button (seen 2026-10-17). Re-check before sending.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -5508,12 +7266,49 @@
           <t>mobile performance score below 60: PSI mobile performance 53; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/649f0b20ab5e727b6fa66e9f/84a96315-de27-45e7-bf13-c15f001acad6/portland%2Bhome%2Bremodeler.webp?format=2500w = 1,609,722 bytes; https://images.squarespace-cdn.com/content/v1/649f0b20ab5e727b6fa66e9f/1689178764950-CGWMFMWFW0ZRI44QU17B/Alameda1.png?format=1500w = 1,319,464 bytes; https://images.squarespace-cdn.com/content/v1/649f0b20ab5e727b6fa66e9f/1690321849550-OH169RN64XI2GF27ZKRI/IMG_5515-HDR.png?format=1500w = 1,125,460 bytes; https://images.squarespace-cdn.com/content/v1/649f0b20ab5e727b6fa66e9f/1689181524030-BCO0R0EY12M7NG97YEMZ/IMG_6508-HDR+copy.png?format=1500w = 1,694,146 bytes | re-measured 2026-10-14 (full download): 7b6fa66e9f/84a96315-de27-45e7-bf13-c15f001acad6/portland%2Bh = 1,609,722 bytes (browser Accept) / 1,609,722 bytes (curl); 7b6fa66e9f/1689178764950-CGWMFMWFW0ZRI44QU17B/Alameda1.png?f = 1,319,464 bytes (browser Accept) / 1,319,464 bytes (curl); 7b6fa66e9f/1690321849550-OH169RN64XI2GF27ZKRI/IMG_5515-HDR.p = 1,508,188 bytes (browser Accept) / 1,508,188 bytes (curl); 7b6fa66e9f/1689181524030-BCO0R0EY12M7NG97YEMZ/IMG_6508-HDR+c = 1,694,146 bytes (browser Accept) / 1,694,146 bytes (curl)</t>
         </is>
       </c>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="inlineStr"/>
-      <c r="X50" s="2" t="inlineStr"/>
-      <c r="Y50" s="2" t="inlineStr"/>
-      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Lake Oswego homepage idea for Straight Line</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt,
+On straightlinedr.com, (503) 244-5463 appears only as plain text in the footer. There's no tappable phone link on any page, so a phone visitor has to copy the number by hand.
+I made a free homepage concept for Straight Line from your own project photos and Google reviews. The number is a tap-to-call link in the header and the hero, and your 4.9 rating, CCB number and 2026 NARI Remodeler of the Year award sit in the first screen. Think of it as a private draft: it isn't indexed and it isn't live on straightlinedr.com.
+https://straightlinedr.thecreativezohaib.com/
+Would a 10-minute call this week work to go over it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, a short follow-up. The hero image on your current home page is 1,609,722 bytes, about 1.6MB, on its own. The concept uses town-labeled gallery photos from Bull Mountain to West Linn and shows reviews as real text instead of images. https://straightlinedr.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, last one from me. The Straight Line concept will stay up as a private preview at https://straightlinedr.thecreativezohaib.com/ if you want to look later. It's yours to forward to anyone on the team. Thanks for your time.</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, I put together a free homepage concept for Straight Line from your own projects and reviews. Your number is tap-to-call up top, next to your 2026 NARI award: https://straightlinedr.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>No tel: link anywhere, phone only as footer text, from current_site_defects / outreach_hook; 1.6MB hero image from measured_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>The only email is jennifer@ but the email greets Matt; consider the contact form or a call to reach Matt directly.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -5614,12 +7409,45 @@
           <t>horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 440px, i.e. 65px wider than the screen; elements past the right edge: ['DIV.swiper-slide.swiper-slide-next right=755', 'DIV.CarouselItem__CarouselItemContainer-sc-b0242df4-0.es-carousel-item right=755', 'DIV.ReviewContainer__Inner-sc-4342da43-0.koGojx right=755']</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" s="2" t="inlineStr"/>
-      <c r="W51" s="2" t="inlineStr"/>
-      <c r="X51" s="2" t="inlineStr"/>
-      <c r="Y51" s="2" t="inlineStr"/>
-      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for The Bath Remodeling Center</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nicole,
+Every page of thebathremodelingcenter.com shows (919) 636-6958, but your Google Business Profile lists (919) 914-0684. Calls end up split between two numbers, and the listing and site don't match.
+I made a free homepage concept for The Bath Remodeling Center, built from your own bathroom photos and Google reviews. It uses the Google number as tap-to-call (easy to switch if the other line is the one you want) and puts your 2,000+ remodels and license #86537 under the headline. The preview is private, hidden from search engines and separate from your domain.
+https://thebathremodelingcenter.thecreativezohaib.com/
+If you have 10 minutes this week, I'd be glad to walk you through it.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nicole, one more detail. On a 375px phone screen your home page renders 440px wide because the review carousel runs off the edge, so it scrolls sideways. The concept also uses one install timeline, 12 to 14 business days, where your site currently gives two. https://thebathremodelingcenter.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nicole, I'll stop here. The concept is still up as a private preview if it ever helps: https://thebathremodelingcenter.thecreativezohaib.com/ If you decide which phone line should lead, I can update the concept to match. Congrats on the Maggy Awards.</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nicole! I designed a free homepage concept for The Bath Remodeling Center from your own bath photos and reviews, with your 2,000+ remodels up top. Private preview: https://thebathremodelingcenter.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>Phone mismatch (site 636-6958 vs Google 914-0684) from current_site_defects / outreach_hook; 375px overflow (440px wide) from measured_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -5716,12 +7544,45 @@
           <t>gallery images over 1MB each: https://thrivehomeconstruction.com/wp-content/uploads/2026/07/Foxworth-Kitchen-105.png = 2,615,204 bytes; https://thrivehomeconstruction.com/wp-content/uploads/2026/07/Foxworth-Kitchen-105-1536x1024.png = 1,357,999 bytes; https://thrivehomeconstruction.com/wp-content/uploads/2026/07/Foxworth-Kitchen-171.png = 2,609,352 bytes | re-measured 2026-10-18 (full download): tion.com/wp-content/uploads/2026/07/Foxworth-Kitchen-105.png = 2,615,204 bytes (browser Accept) / 2,615,204 bytes (curl); p-content/uploads/2026/07/Foxworth-Kitchen-105-1536x1024.png = 1,357,999 bytes (browser Accept) / 1,357,999 bytes (curl); tion.com/wp-content/uploads/2026/07/Foxworth-Kitchen-171.png = 2,609,352 bytes (browser Accept) / 2,609,352 bytes (curl)</t>
         </is>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" s="2" t="inlineStr"/>
-      <c r="W52" s="2" t="inlineStr"/>
-      <c r="X52" s="2" t="inlineStr"/>
-      <c r="Y52" s="2" t="inlineStr"/>
-      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>Thrive homepage idea: On-Time Promise up top</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrey,
+When I loaded thrivehomeconstruction.com, a few kitchen gallery images came through as 2.6MB PNG files each, which is heavy for a phone on a cell connection.
+Your On-Time Promise deserves a better spot, so I made a free homepage concept for Thrive from your own project photos and Google reviews. The hero leads with the $100-per-late-day promise, the 3-year warranty and your 5.0 rating, with (916) 308-4575 as tap-to-call. Your story as a dad of six is front and center. It lives on a private, unindexed link, not on thrivehomeconstruction.com.
+https://thrivehomeconstruction.thecreativezohaib.com/
+Reply if you'd like to chat, or we can set up 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrey, following up with one more find. Your Fair Oaks service-area page returns a 404, and the Davis page's description mentions Antelope. The concept answers the hard-water and timeline questions in plain FAQ text, using your own project photos throughout. https://thrivehomeconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>Andrey, last note from me. The Thrive concept stays at this private link if you want it later: https://thrivehomeconstruction.thecreativezohaib.com/ No reply needed unless it's helpful. Thanks for your time and good luck this season.</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrey, I built a free homepage concept for Thrive that leads with your $100-a-day On-Time Promise and 5.0 Google rating, using your own bathroom photos. Preview: https://thrivehomeconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>Blank stat counters and 'SACRAMETNO' typo from current_site_defects / outreach_hook; Fair Oaks 404 and Davis meta description from current_site_defects in follow_up_1. | Revised: counter claims removed after a browser check showed they were animation or crawl artifacts.</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -5816,12 +7677,45 @@
           <t>gallery images over 1MB each: https://cdn.prod.website-files.com/6984b8ec6defb469d1874ad1/69f3caef41138dfa7ce28454_69f3bc90b21ed48b5a85d712_4_hutchinson_st_milton-040826%2520-%252008.jpeg = 1,263,636 bytes; https://cdn.prod.website-files.com/6984b8ec6defb469d1874ad1/69f3c3f752664c749091e5c6_69f3ac60dc4c590a702c46bf_4_124woodst_milton_202600228_17.jpeg = 1,936,620 bytes; https://cdn.prod.website-files.com/6984b8ec6defb469d1874ad1/69f3caef41138dfa7ce28485_69f3b5849048496a60f73b56_2_318prospectst_norwell_ma-02.jpeg = 2,107,408 bytes | re-measured 2026-10-18 (full download): 49c5e918a17/69729df11c9aae86ff087b66_1203Ferry_batch1-53.jpg = 2,429,154 bytes (browser Accept) / 2,429,154 bytes (curl); bde49c5e918a17/69794815639331fd46037e25_6Polk_Kitchen-17.jpg = 2,240,019 bytes (browser Accept) / 2,240,019 bytes (curl); c97bde49c5e918a17/69794c96c5babfc6db28b7fc_6HeatherDr-15.jpg = 1,727,898 bytes (browser Accept) / 1,727,898 bytes (curl); 7/69936c52de000ba1d5a74937_3_318prospectst_norwell_ma-01.jpg = 2,190,097 bytes (browser Accept) / 2,190,097 bytes (curl); 7/69c2c738b7a8ed615b306ca4_7_318prospectst_norwell_ma-07.jpg = 1,883,820 bytes (browser Accept) / 1,883,820 bytes (curl); e918a17/69cad35f8676a744340f6395_Bathroomphotos_print-27.jpg = 2,156,490 bytes (browser Accept) / 2,156,490 bytes (curl); 9f3ac60dc4c590a702c46bf_4_124woodst_milton_202600228_17.jpeg = 1,936,620 bytes (browser Accept) / 1,936,620 bytes (curl); d48b5a85d712_4_hutchinson_st_milton-040826%2520-%252008.jpeg = 1,263,636 bytes (browser Accept) / 1,263,636 bytes (curl); 1874ad1/6a0b590b7c769ad59a84b14b_hingham_260513%20-%2001.jpg = 1,273,393 bytes (browser Accept) / 1,273,393 bytes (curl); 569ae9fc641b_5_416-john-mahar-hwy%203105_260622%20-%2004.jpg = 1,940,267 bytes (browser Accept) / 1,940,267 bytes (curl); 74ad1/6a4bd93296e81b137a10fd46_tamburini_260626%20-%2002.jpg = 1,985,524 bytes (browser Accept) / 1,985,524 bytes (curl)</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" s="2" t="inlineStr"/>
-      <c r="W53" s="2" t="inlineStr"/>
-      <c r="X53" s="2" t="inlineStr"/>
-      <c r="Y53" s="2" t="inlineStr"/>
-      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>Norwell homepage concept for Transitions</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Craig,
+Your Norwell and Milton project photos are excellent, but several on transitionskbr.com download at over 2MB each. 1203Ferry_batch1-53.jpg alone is 2,429,154 bytes, which is a lot for a phone on cell data.
+I built a free homepage concept for Transitions from your own project photos and Google reviews. It opens with 'Kitchen Remodeling in Norwell, MA', puts (781) 871-0881 in the header as tap-to-call, and features your 800+ kitchens and the free visit, measure and first design. Search engines are blocked from it, and it isn't on your domain, so it's purely a private preview.
+https://transitionskbr.thecreativezohaib.com/
+Open to a 10-minute look together this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Craig, one more observation. Your home page says '1200+ customers served' up top and '1600+ projects completed' further down, and shows a 4.6 rating while Google shows 4.5. The concept uses the per-service counts and the real 4.5 from 55 reviews. https://transitionskbr.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Craig, I'll close the loop here. If the Transitions concept is useful down the road, it's at https://transitionskbr.thecreativezohaib.com/ Your showroom visit and line-item budget already sell the work; the page just puts them first. Appreciate you reading.</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Craig, I made a free homepage concept for Transitions using your own South Shore project photos and reviews, with tap-to-call and your 800+ kitchens up top. Private link: https://transitionskbr.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>Gallery images over 2MB (1203Ferry_batch1-53.jpg 2,429,154 bytes) from measured_defects / outreach_hook; conflicting totals and 4.6 vs 4.5 rating from current_site_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5921,12 +7815,45 @@
           <t>mobile performance score below 60: PSI mobile performance 47</t>
         </is>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
-      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>St. Paul kitchen homepage idea for Wise Design</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Hi Philip,
+The St. Clair kitchen is the first photo on wisedesignremodel.com, but it has empty alt text, and the home page H1 never mentions kitchens. Your Google reviewers bring up kitchen remodels 17 times.
+I created a free homepage concept for Wise Design &amp; Remodel from your own photos and Google reviews. The St. Clair kitchen is the hero, the headline reads 'Kitchen Remodeling in St. Paul for Homes With Character', and your 4.9 rating and License # BC738242 sit in the first screen with (612) 849-2515 as tap-to-call. It is not live anywhere public: the preview isn't indexed and isn't on your domain.
+https://wisedesignremodel.thecreativezohaib.com/
+If you'd like a 10-minute call this week, just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>Hi Philip, a follow-up on the concept. Your home page FAQ answers are collapsed, so a crawl only sees the questions, and there's no process page yet. The concept writes out a five-step process and five plain-text FAQ answers from your own pages. https://wisedesignremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>Philip, my last note. The concept for Wise Design &amp; Remodel stays here as a private preview: https://wisedesignremodel.thecreativezohaib.com/ Glad to share it whenever it's useful. If you prefer a different hero photo, that's an easy swap.</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>Hi Philip, I built a free homepage concept for Wise Design &amp; Remodel around your St. Clair kitchen and 4.9 Google rating, using your own photos. Private preview: https://wisedesignremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>St. Clair kitchen hero with empty alt text and H1 without 'kitchen' (17 kitchen mentions in reviews) from current_site_defects / outreach_hook; collapsed FAQ and no process page in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -6011,12 +7938,45 @@
           <t>mobile performance score below 60: PSI mobile performance 52; gallery images over 1MB each: https://wrights-renovations.com/wp-content/uploads/2026/06/basement-design-c-1.jpg = 1,493,526 bytes (HTTP Content-Length); https://wrights-renovations.com/wp-content/uploads/2026/06/basement-design-1-1.jpg = 1,326,867 bytes (HTTP Content-Length) | re-measured 2026-10-14 (full download): tions.com/wp-content/uploads/2026/06/basement-design-c-1.jpg = 1,493,526 bytes (browser Accept) / 1,493,526 bytes (curl); tions.com/wp-content/uploads/2026/06/basement-design-1-1.jpg = 1,326,867 bytes (browser Accept) / 1,326,867 bytes (curl)</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" s="2" t="inlineStr"/>
-      <c r="W55" s="2" t="inlineStr"/>
-      <c r="X55" s="2" t="inlineStr"/>
-      <c r="Y55" s="2" t="inlineStr"/>
-      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Wright's Renovations</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Hi Connor,
+Your kitchen remodeling page uses eight Pexels stock photos, while your own navy and Ann Arbor kitchens aren't shown there. The site also uses (734) 251-4187, but Google lists (734) 540-0347.
+I made a free homepage concept for Wright's Renovations from your own project photos and Google reviews. It uses only your work, one tap-to-call number that matches Google, and your 4.9 rating, 550+ projects and Inc. 5000 rank in the hero. Your 'renovation without the runaround' line stays. Only people with the link can see it, since it isn't indexed or hosted on your domain.
+https://wrights-renovations.thecreativezohaib.com/
+Reply, or let me show you around on a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>Hi Connor, one more thing. Your site says '5.0 rating on Google · 50+ reviews', but Google currently shows 4.9 from 54. The concept uses the live Google figure, and its FAQ answers cost, timeline, hidden-damage and historic-district questions in plain text. https://wrights-renovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>Hi Connor, last follow-up from me. The concept is still at this private link: https://wrights-renovations.thecreativezohaib.com/ If now isn't the time, no problem at all. Should the Inc. 5000 badge or project count need updating, a one-line reply covers it.</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>Hey Connor, I put together a free homepage concept for Wright's Renovations using only your own kitchens and baths, plus your 4.9 rating and Inc. 5000 rank. See it: https://wrights-renovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>Pexels stock photos on kitchen page and phone mismatch (251-4187 vs Google 540-0347) from current_site_defects / outreach_hook; 5.0 vs 4.9 rating claim in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -6101,12 +8061,45 @@
           <t>gallery images over 1MB each: https://yourdreamremodeling.com/wp-content/uploads/2024/06/5202-Devon-Green-1.jpg = 1,928,717 bytes; https://yourdreamremodeling.com/wp-content/uploads/2024/06/5202-Devon-Green-2.jpg = 1,918,990 bytes; https://yourdreamremodeling.com/wp-content/uploads/2024/06/5202-Devon-Green-6.jpg = 1,841,095 bytes; https://yourdreamremodeling.com/wp-content/uploads/2024/06/5202-Devon-Green-8.jpg = 1,685,329 bytes | re-measured 2026-10-14 (full download): deling.com/wp-content/uploads/2024/06/5202-Devon-Green-1.jpg = 1,928,717 bytes (browser Accept) / 1,928,717 bytes (curl); deling.com/wp-content/uploads/2024/06/5202-Devon-Green-2.jpg = 1,918,990 bytes (browser Accept) / 1,918,990 bytes (curl); deling.com/wp-content/uploads/2024/06/5202-Devon-Green-6.jpg = 1,841,095 bytes (browser Accept) / 1,841,095 bytes (curl); deling.com/wp-content/uploads/2024/06/5202-Devon-Green-8.jpg = 1,685,329 bytes (browser Accept) / 1,685,329 bytes (curl)</t>
         </is>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
-      <c r="V56" s="2" t="inlineStr"/>
-      <c r="W56" s="2" t="inlineStr"/>
-      <c r="X56" s="2" t="inlineStr"/>
-      <c r="Y56" s="2" t="inlineStr"/>
-      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>Houston homepage idea for Your Dream Remodeling</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ike,
+Four of your Devon Green bathroom photos on yourdreamremodeling.com load at full size, between 1.7 MB and 1.9 MB each. I also noticed the About page says 2010 while the contact page says 'Remodeling since 2014'.
+I made a free homepage concept for Your Dream Remodeling from your own project photos and Google reviews. It leads with the N Fry Rd showroom, the free home visit, the 1-year warranty and your 4.9 rating, and every call button uses (281) 550-8900. It's a private preview, kept off search engines and off your domain.
+https://yourdreamremodeling.thecreativezohaib.com/
+Reply anytime, or let's find 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ike, following up. Phone links on your site point to three numbers: 281-550-8900, 281-392-8740 and 281-550-8509. The concept uses one, matching Google, so every caller reaches the same line, and adds your published price ranges and aging-in-place work to the FAQ. https://yourdreamremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>Ike, a final note. The concept is parked at this private link if you'd like it later: https://yourdreamremodeling.thecreativezohaib.com/ If 2014 is the right founding year rather than 2010, tell me and I'll change it. Have a good week.</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ike, I designed a free homepage concept for Your Dream Remodeling from your own bathrooms and reviews, leading with your N Fry Rd showroom and 4.9 rating. Preview: https://yourdreamremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>Devon Green photos 1.7 to 1.9 MB from measured_defects and 2010 vs 2014 founding year from current_site_defects / outreach_hook; three phone numbers in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -6157,11 +8150,7 @@
           <t>info@alphageneralconstructionwtx.com</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>stephanie.hecke@primelending.com</t>
-        </is>
-      </c>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>https://alphagenco.com/contact</t>
@@ -6203,12 +8192,45 @@
           <t>mobile performance score below 60: PSI mobile performance 47</t>
         </is>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
-      <c r="V57" s="2" t="inlineStr"/>
-      <c r="W57" s="2" t="inlineStr"/>
-      <c r="X57" s="2" t="inlineStr"/>
-      <c r="Y57" s="2" t="inlineStr"/>
-      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>Midland bathroom homepage concept for Alpha</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel,
+Your blog post on flood-tested pans and RedGard waterproofing is one of the clearest shower explanations I've read from a contractor. Right now it's buried in the blog, and the home page header has no phone number.
+I built a free homepage concept for Alpha General Construction from your own Midland project photos and Google reviews. It moves the waterproofing method onto the home page, puts (432) 250-7940 in the header as tap-to-call, and shows your 5.0 rating and BBB A+ under 'Bathroom Remodeling in Midland, TX'. The page is a private preview, unindexed and separate from your own site.
+https://alphagenco.thecreativezohaib.com/
+Could we take 10 minutes this week to go through it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, one more note. Your home page scored 47 on Google's mobile PageSpeed test, and the FAQ answers sit in collapsed accordions. The concept writes those answers out in plain text, including how you keep a new shower from leaking. https://alphagenco.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, I'll leave it here. The Alpha concept stays up privately at https://alphagenco.thecreativezohaib.com/ in case it's useful later. If Odessa should be in the service area along with Midland, that's a quick addition. Take care.</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, I made a free homepage concept for Alpha that puts your flood-tested, waterproofed showers front and center, using your own Midland photos. Private preview: https://alphagenco.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>Waterproofing proof buried in blog post and no header phone from current_site_defects / outreach_hook; PSI 47 from measured_defects and collapsed FAQ in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -6308,12 +8330,49 @@
           <t>mobile performance score below 60: PSI mobile performance 44; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 435px, i.e. 60px wider than the screen; elements past the right edge: ['svg right=895', 'path right=895']; gallery images over 1MB each: https://ccfauxfinishes.com/wp-content/uploads/2024/09/Screenshot-2024-09-11-at-9.26.18%E2%80%AFAM.png = 5,526,684 bytes; https://ccfauxfinishes.com/wp-content/uploads/2024/11/Screenshot-2024-11-14-at-9.51.25%E2%80%AFAM.png = 4,248,283 bytes</t>
         </is>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" s="2" t="inlineStr"/>
-      <c r="W58" s="2" t="inlineStr"/>
-      <c r="X58" s="2" t="inlineStr"/>
-      <c r="Y58" s="2" t="inlineStr"/>
-      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Creative Cabinets</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Hi Evan,
+On ccfauxfinishes.com, the header shows (770) 693-1896, your Google number. But the only tap-to-call link, and the footer, use (678) 324-3913. So a phone visitor who taps sees one number and dials another.
+I built a free homepage concept for Creative Cabinets and Fine Finishes from your own project photos and Google reviews. It uses (770) 693-1896 everywhere, shows 4.9 stars from 309 reviews, and explains refinish vs reface vs remodel in plain words, with your paint booth and CNC shop as the reason. It's a private mockup on a preview address, blocked from search and not on your domain.
+https://ccfauxfinishes.thecreativezohaib.com/
+Reply if it's interesting, or I can do a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>Hi Evan, a follow-up. On a 375px iPhone screen your home page is 435px wide, so it scrolls sideways by 60px. The concept also quotes three named Google reviews instead of the two one-line quotes on the current site. https://ccfauxfinishes.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>Hi Evan, last note. The CCFF concept will stay available at this private link: https://ccfauxfinishes.thecreativezohaib.com/ Happy to hand it over anytime. It could also be a starting point if you're already planning a site refresh.</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>Hi Evan! I made a free homepage concept for CCFF from your own projects and 309 Google reviews, with one phone number and a clear refinish, reface or remodel guide: https://ccfauxfinishes.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>Header number vs tel: link mismatch (693-1896 shown, 324-3913 dialed) from current_site_defects / outreach_hook; 60px overflow at 375px from measured_defects in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>The new concept shows a 'Women-owned business' badge; the owner on record is Evan Hill. Confirm or remove the badge on the concept before sending.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -6411,12 +8470,49 @@
           <t>gallery images over 1MB each: https://kitchenconceptsinoregon.com/wp-content/uploads/2026/08/20260805_151803.jpg = 1,317,779 bytes (HTTP Content-Length); https://kitchenconceptsinoregon.com/wp-content/uploads/2026/04/20260325_090738.jpg = 1,363,702 bytes (HTTP Content-Length); https://kitchenconceptsinoregon.com/wp-content/uploads/2025/11/20251008_100644.jpg = 1,473,773 bytes (HTTP Content-Length); https://kitchenconceptsinoregon.com/wp-content/uploads/2025/06/Screen-Shot-2025-06-03-at-11.25.14-AM.png = 2,998,378 bytes (HTTP Content-Length) | re-measured 2026-10-17 (full download): sinoregon.com/wp-content/uploads/2026/08/20260805_151803.jpg = 1,317,779 bytes (browser Accept) / 1,317,779 bytes (curl); sinoregon.com/wp-content/uploads/2026/04/20260325_090738.jpg = 1,363,702 bytes (browser Accept) / 1,363,702 bytes (curl); sinoregon.com/wp-content/uploads/2025/11/20251008_100644.jpg = 1,473,773 bytes (browser Accept) / 1,473,773 bytes (curl); nt/uploads/2025/06/Screen-Shot-2025-06-03-at-11.25.14-AM.png = 2,998,378 bytes (browser Accept) / 2,998,378 bytes (curl)</t>
         </is>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" s="2" t="inlineStr"/>
-      <c r="W59" s="2" t="inlineStr"/>
-      <c r="X59" s="2" t="inlineStr"/>
-      <c r="Y59" s="2" t="inlineStr"/>
-      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>Gresham homepage concept for Kitchen Concepts</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dave,
+The home page of kitchenconceptsinoregon.com has no H1 heading. The main heading, 'Trusted Remodeling. Exceptional Results. Since 1989', is an H2, and the rest of the page is a blog feed.
+I made a free homepage concept for Kitchen Concepts NW from your own project photos and Google reviews. It has one H1, 'Kitchen Remodeling in Gresham, OR', a tap-to-call number in the header, and your free consultation and 1989 founding above the fold. Your posted price brackets are in readable text. You're seeing a private preview: it isn't indexed and it isn't on kitchenconceptsinoregon.com.
+https://kitchenconceptsinoregon.thecreativezohaib.com/
+Would you be up for a 10-minute call this week? Or just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dave, one more detail. The Oregon City Tupper post uses a PNG screenshot that weighs 2,998,378 bytes, close to 3MB. The concept also shows your 5.0 Google rating right under the headline; today it doesn't appear anywhere on the site. https://kitchenconceptsinoregon.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>Dave, final note from me. Your concept is still at this private link: https://kitchenconceptsinoregon.thecreativezohaib.com/ One small tip: your Google profile lists the category as 'Home goods store', which may be worth a look.</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dave, I built a free homepage concept for Kitchen Concepts NW from your own kitchens and reviews, with a clear Gresham headline and your 1989 story up top: https://kitchenconceptsinoregon.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>No H1 (main heading is an H2, rest is a blog feed) from current_site_defects / outreach_hook; 2,998,378-byte screenshot from measured_defects and missing rating in follow_up_1.</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>Their Google profile category is 'Home goods store' and the address starts with 'Parking lot'; follow-up 2 mentions this gently.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -6516,12 +8612,45 @@
           <t>mobile performance score below 60: PSI mobile performance 50</t>
         </is>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
-      <c r="V60" s="2" t="inlineStr"/>
-      <c r="W60" s="2" t="inlineStr"/>
-      <c r="X60" s="2" t="inlineStr"/>
-      <c r="Y60" s="2" t="inlineStr"/>
-      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>Wilmington homepage concept for Newberry</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Hi Barry,
+You have a 5.0 rating from 242 Google reviews, but the homepage at newberryhome.com doesn't show it. The header has no phone number either, only 'Request Pricing', and the first heading is a sale banner.
+I built a free homepage concept for Newberry Home Improvement from your own project photos and Google reviews. It leads with 'Cabinet Refacing in Wilmington, NC, Done in as Little as 2 Days', your rating, the WECT award and the 7-year warranty, with 910-500-6811 as tap-to-call at the top. For now it's a private preview that search engines can't index, and it isn't on your domain.
+https://newberryhome.thecreativezohaib.com/
+Reply if you'd like 10 minutes together this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>Hi Barry, a quick follow-up. Your home, bath and kitchen pages carry dozens of identical 'View Pictures Of Job' links. The concept swaps those for named photos like Shaker Fashion Grey and the Calcutta stone shower, and explains the 2-day bath with its overnight water test. https://newberryhome.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>Hi Barry, my last note. The Newberry concept is at this private link whenever it's convenient: https://newberryhome.thecreativezohaib.com/ It stays evergreen, with no dated sale banners. If you want a seasonal promo strip, I can add one that expires on its own.</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>Hi Barry, I made a free homepage concept for Newberry built around your 5.0 rating from 242 Google reviews and your own refacing photos. Tap-to-call up top. Take a look: https://newberryhome.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>Rating not on home page and no header phone (only 'Request Pricing') from current_site_defects / outreach_hook; 'View Pictures Of Job' links in follow_up_1. Sale end date deliberately not used to avoid urgency.</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -6568,11 +8697,7 @@
           <t>pacificremodelingllc@gmail.com</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>planning@puyallupwa.gov</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
           <t>https://pacificremodelingllc.com/contact-us/</t>
@@ -6610,12 +8735,45 @@
           <t>horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 397px, i.e. 22px wider than the screen; elements past the right edge: ['BUTTON#mobile-menu-close.mobile-menu__close right=770', 'UL.mobile-menu__links right=778', 'LI right=778']</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
-      <c r="V61" s="2" t="inlineStr"/>
-      <c r="W61" s="2" t="inlineStr"/>
-      <c r="X61" s="2" t="inlineStr"/>
-      <c r="Y61" s="2" t="inlineStr"/>
-      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>Puyallup homepage idea for Pacific Remodeling</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad,
+On a 375px phone screen, the pacificremodelingllc.com home page measures 397px wide, so it scrolls 22px sideways. The mobile menu's close button and links sit past the right edge.
+I built a free homepage concept for Pacific Remodeling from your own before-and-after photos and Google reviews. Your real portfolio shots replace the generated renders, (253) 392-9266 is tap-to-call at the top and bottom, and the hero shows 5.0 from 21 reviews, as Google lists it. It also leads with your waterproofing approach. It's a private preview on its own address, not indexed and not live on your domain.
+https://pacificremodelingllc.thecreativezohaib.com/
+Interested? Reply here, or let's do 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad, one more idea. Your site shows '4.9 · 63 customer reviews' while Google shows 5.0 from 21, which can look inconsistent to a careful shopper. The concept uses the Google figure and lists your hall bath and master bath price ranges and timelines in the services. https://pacificremodelingllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>Brad, last note from me. The concept stays live as a private preview here: https://pacificremodelingllc.thecreativezohaib.com/ If you'd rather lead with a different shower photo, just tell me which one. Good luck with the next bathroom.</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad, I designed a free homepage concept for Pacific Remodeling using your real shower photos instead of renders, with your 5.0 rating and prices up front: https://pacificremodelingllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>Measured 22px horizontal overflow at 375px from measured_defects / outreach_hook; AI renders vs portfolio photos and 4.9/63 vs 5.0/21 rating from current_site_defects.</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -6713,12 +8871,50 @@
           <t>mobile performance score below 60: PSI mobile performance 49; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/680a2dec919f817da2379e91/7d368e67-8252-4c25-a983-2b0cee76bdf0/Interior-4.jpg?format=2500w = 1,072,612 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/680a2dec919f817da2379e91/225f4391-f5ff-4e31-b51a-d7d1636fe505/Exterior-18.jpg?format=2500w = 1,264,137 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/680a2dec919f817da2379e91/2b44eb41-39e7-497b-8da1-5ff4bb3d0f0f/Interior-5.jpg = 1,172,521 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" s="2" t="inlineStr"/>
-      <c r="W62" s="2" t="inlineStr"/>
-      <c r="X62" s="2" t="inlineStr"/>
-      <c r="Y62" s="2" t="inlineStr"/>
-      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for RenoDB</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey,
+Your site does something most remodelers won't: it posts real bathroom prices. On the homepage, though, (540) 418-2130 only shows up in the footer, and Google's PageSpeed test gave the mobile version a 49.
+I put together a free homepage concept using your own project photos and Google reviews. It puts call or text at the top, shows the $12,500 small bath starting price early, and answers five common questions in plain text. It's a private preview, not indexed and not on your domain.
+https://renodb.thecreativezohaib.com/
+If it's useful, just reply, or we can do a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey, one more detail on the concept. Each project photo is labeled by town, like the Riner soaking tub and the Christiansburg vanity, and the discovery call form takes three short steps. Your 5.0 rating from 14 Google reviews sits in the first screen.
+https://renodb.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey, last note from me on this. The RenoDB concept stays up as a private preview if you want to look later:
+https://renodb.thecreativezohaib.com/
+No reply needed if the timing is wrong.
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joey! I built a free homepage concept for RenoDB from your own photos and reviews, with your number and posted bath prices up top. It's a private preview, not live: https://renodb.thecreativezohaib.com/ Happy to hear what you think.</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>Used phone only in footer plus PSI mobile 49 (conversion_notes.current_site_defects, measured_defects); concept features (call or text, $12,500 price, 5 FAQs, 3-step form) checked on live page.</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -6815,12 +9011,50 @@
           <t>mobile performance score below 60: PSI mobile performance 40</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
-      <c r="V63" s="2" t="inlineStr"/>
-      <c r="W63" s="2" t="inlineStr"/>
-      <c r="X63" s="2" t="inlineStr"/>
-      <c r="Y63" s="2" t="inlineStr"/>
-      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>A Sarasota homepage idea for S&amp;W Kitchens</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe,
+On your Sarasota showroom page, the header number is the statewide 877.400.0237. The local (941) 274-3552 only appears further down in the body text, and Google's mobile speed test scored the site 40.
+I mocked up a free Sarasota-first homepage built from S&amp;W's own project photos and Google reviews. The local number is tap-to-call at the top, the 5th Street address sits in the hero, and the 96% on-budget figure and your license number are in the first screen. Search engines can't index it, and it isn't on your domain; it's a private preview.
+https://sandwkitchens.thecreativezohaib.com/
+Would you be open to a quick reply or a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe, a quick follow-up. Your site says 'By Appointment Only!' on one page and 'Walk-Ins Welcome!' on another, so the concept simply answers when the showroom is open. It also features Peter N.'s Google review about his bathroom.
+https://sandwkitchens.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe, I'll leave it here so I don't crowd your inbox. If a Sarasota-first homepage is ever on your list, the preview is still waiting at this link:
+https://sandwkitchens.thecreativezohaib.com/
+Thanks for reading,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joe, I made a free Sarasota homepage concept for S&amp;W using your own photos and reviews, with (941) 274-3552 tappable at the top. Private preview here: https://sandwkitchens.thecreativezohaib.com/ Would love your take.</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>Used header showing statewide 877 number instead of the Sarasota (941) number, plus PSI 40 (conversion_notes.current_site_defects, measured_defects); concept checked for hero address, 96% stat, license, showroom-hours FAQ, Peter N. review.</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -6914,12 +9148,50 @@
           <t>mobile performance score below 60: PSI mobile performance 17</t>
         </is>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
-      <c r="V64" s="2" t="inlineStr"/>
-      <c r="W64" s="2" t="inlineStr"/>
-      <c r="X64" s="2" t="inlineStr"/>
-      <c r="Y64" s="2" t="inlineStr"/>
-      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Guthrie Kitchen &amp; Bath</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mike,
+Google's PageSpeed Insights gave your site a mobile score of 17 out of 100. I also spotted a small mismatch: the footer and FAQ say the company started in 2012, while the home page says January 2013.
+So I built a free homepage concept from your own project photos and Google reviews. The hero names Pleasant View, gives the Industrial Drive address and puts (615) 247-5091 one tap away. Questions like buying just cabinets or countertops are answered in plain text, and I left the founding year out until you confirm it. This is a private preview, unindexed and off your domain.
+https://guthriekitchenandbath.thecreativezohaib.com/
+Worth a 10-minute call this week? A reply works too.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mike, one more piece I think works well: the concept leads with your 7,000 sq ft showroom and your years in construction since 1982. The gallery shows real Clarksville, Springfield and Pleasant View jobs. Have a look when you get a minute.
+https://guthriekitchenandbath.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mike, final note on the Guthrie concept. It stays private, so there's no pressure to act on it, and you're welcome to share it with your team:
+https://guthriekitchenandbath.thecreativezohaib.com/
+If now isn't the time, no problem at all.
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mike, I built a free homepage concept for Guthrie Kitchen &amp; Bath using your own photos and reviews, centered on the Pleasant View showroom. Not live, just a private preview: https://guthriekitchenandbath.thecreativezohaib.com/ Curious what you think!</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>Used PSI mobile 17 and the 2012 vs January 2013 founding conflict (measured_defects, conversion_notes.current_site_defects); concept checked for Pleasant View hero, address, tap-to-call, cabinets-only FAQ.</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -7016,12 +9288,50 @@
           <t>Likely heavy page: Google PageSpeed Insights timed out twice on the homepage, and the crawl supports that. The homepage loads 14 images and backgrounds totaling about 15.4MB, led by a 7.1MB bathroom photo (Stacey Goldberg bathroom/2434.jpg, 5244x3544), a 3.3MB 3024x4032 kitchen JPEG (Prager-kitchen), a 1.8MB 'ChatGPT Image Mar 4, 2026' PNG background and two Unsplash backgrounds of 1.25MB and 0.79MB</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
-      <c r="V65" s="2" t="inlineStr"/>
-      <c r="W65" s="2" t="inlineStr"/>
-      <c r="X65" s="2" t="inlineStr"/>
-      <c r="Y65" s="2" t="inlineStr"/>
-      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>A lighter homepage for B&amp;B Associates</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael,
+Google's PageSpeed test timed out twice on your homepage. Looking at the page, it loads 14 images totaling about 15.4MB, including a 7.1MB bathroom photo, which is a lot for a phone to download.
+I built a free concept that uses only your own watermarked project photos at web size, plus real Google reviews. Your 5.0 rating from 68 reviews sits next to the headline, and the Pipersville and Doylestown projects lead the gallery. It sits on a private preview link, hidden from indexing and separate from your domain.
+https://bbassociatesco.thecreativezohaib.com/
+Happy to walk you through it on a 10-minute call this week, or just reply with thoughts.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, one more detail. Your site lists projects completed as 1,200+, 1,113+, 600+ and 500+ on different pages. The concept sticks to numbers anyone can check: 5.0 from 68 Google reviews, family-owned since 2013 and PA HIC #PA104189.
+https://bbassociatesco.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, this is my last nudge. The B&amp;B preview is still private if you or Laurentiu would like to look it over later, and I'm happy to adjust anything:
+https://bbassociatesco.thecreativezohaib.com/
+Wishing you a busy winter,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I made a free homepage concept for B&amp;B from your own project photos and Google reviews, built light for phones with your 5.0 from 68 up top. Private preview, not live: https://bbassociatesco.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>Used PSI timeout plus 15.4MB homepage images led by a 7.1MB photo (conversion_notes.current_site_defects; measured_defects is empty, pagespeed_mobile=PSI_TIMEOUT); FU1 uses conflicting project counts; concept checked for 5.0/68 hero, Pipersville/Doylestown gallery.</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -7111,12 +9421,50 @@
           <t>gallery images over 1MB each: https://cdn.prod.website-files.com/5ea6e14e5dd63e2936d44574/64821a44672c590c8f946932_01_Main%20Image%20.jpg = 1,006,481 bytes; https://cdn.prod.website-files.com/5ea6e14e5dd63e2936d44574/65f50d8c3c5b6a554fc6c224_20240215_Aptitude_Bathroom_1803BuckinghamGreenCt._0123%20copy%202.jpg = 1,194,731 bytes; dead phone or email link: tel: hrefs [] mailto: hrefs ['314-713-1989']</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
-      <c r="V66" s="2" t="inlineStr"/>
-      <c r="W66" s="2" t="inlineStr"/>
-      <c r="X66" s="2" t="inlineStr"/>
-      <c r="Y66" s="2" t="inlineStr"/>
-      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>A St. Charles homepage idea for Aptitude</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt,
+Quick heads-up from testing your site: the phone number is coded as a mailto: link, so tapping 314-713-1989 on a phone opens an email instead of dialing. Only the contact page has a working call link.
+I built a free homepage concept with your own project photos and Google reviews where the call button actually dials, in the hero and again at the bottom. It also shows your 4.9 from 72 reviews up top and answers the 'can you take out a wall' question in plain text. Think of it as a private preview: it isn't indexed and it isn't on your domain.
+https://aptitudedesignandbuild.thecreativezohaib.com/
+Up for a 10-minute call this week? Or just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, following up with one more piece. The concept spells out typical timelines, 8 to 12 weeks for kitchens and 4 to 8 for baths, so people know what to expect. It also uses Aptitude Design &amp; Build throughout, matching your Google profile.
+https://aptitudedesignandbuild.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, I won't keep filling your inbox. The St. Charles concept is here whenever you want it, and if the timing is off this season, that's completely fine:
+https://aptitudedesignandbuild.thecreativezohaib.com/
+Thanks either way,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>Hi Matt, heads-up: on phones, tapping the number on your site opens an email instead of a call. I built a free concept from your photos and reviews where it dials. Private preview: https://aptitudedesignandbuild.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>Used phone coded as mailto:314-713-1989 (measured_defects dead phone link, conversion_notes.current_site_defects); concept checked for tel: links, 4.9/72, wall-removal FAQ.</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -7207,12 +9555,50 @@
           <t>gallery images over 1MB each: https://bigbuildconstruction.net/yardsign.jpg = 1,906,028 bytes; https://bigbuildconstruction.net/bathroom-hero.jpg = 2,458,264 bytes; https://bigbuildconstruction.net/hero-van.jpg = 2,404,063 bytes; https://bigbuildconstruction.net/home-hero1.jpg = 6,900,497 bytes</t>
         </is>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
-      <c r="V67" s="2" t="inlineStr"/>
-      <c r="W67" s="2" t="inlineStr"/>
-      <c r="X67" s="2" t="inlineStr"/>
-      <c r="Y67" s="2" t="inlineStr"/>
-      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Big Build Construction</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oleg,
+Your site already scores a solid 90 on Google's mobile speed test. The gap I noticed is the homepage headline, 'Full-Service Remodeling, Done Right the First Time', which never says bathroom or Kent, even though Google lists you as a bathroom remodeler in Kent.
+I built a free concept around that from your own project photos and Google reviews. The H1 reads 'Bathroom Remodeling in Kent, WA, With a Price Locked in Writing', and your 5.0 from 38 reviews and licence number sit right under it. Nothing is live on your domain; it's a private preview that search engines don't index.
+https://bigbuildconstruction.thecreativezohaib.com/
+Would a 10-minute call this week work, or would you rather reply?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oleg, a mobile detail I left out: your home hero photo, home-hero1.jpg, is 6.9MB on its own. The concept lists one service area, Kent plus the 11 cities with their own pages, and answers what Kent bathroom remodels usually run.
+https://bigbuildconstruction.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oleg, last one from me. If you ever want to see a Kent-first homepage that leads with your tile work, the preview stays at this link:
+https://bigbuildconstruction.thecreativezohaib.com/
+All the best with the season,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oleg, I put together a free homepage concept for Big Build that leads with bathroom remodeling in Kent and your 5.0 from 38 Google reviews. Built from your own photos, it's a private preview: https://bigbuildconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>Used H1 without 'bathroom' or 'Kent' vs Google category (conversion_notes.current_site_defects), acknowledged PSI 90; FU1 uses 6.9MB home-hero1.jpg (measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -7301,12 +9687,50 @@
           <t>mobile performance score below 60: PSI mobile performance 54; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/59e7d1e0fe54ef21b756fd1e/1712853297953-Z5CZNCTGKW46ZA5FT3DW/002A7265.jpg = 1,729,768 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/59e7d1e0fe54ef21b756fd1e/1712853313312-I7CCHC1BXHQOEZXOI08C/002A7278.jpg = 1,801,822 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/59e7d1e0fe54ef21b756fd1e/1712853335065-KDJ4DJY70BMHCC86NX50/002A7282.jpg = 1,659,771 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/59e7d1e0fe54ef21b756fd1e/1712853335546-QHETPYR33ZHQ5PW2412Y/002A7286.jpg = 1,857,568 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
-      <c r="V68" s="2" t="inlineStr"/>
-      <c r="W68" s="2" t="inlineStr"/>
-      <c r="X68" s="2" t="inlineStr"/>
-      <c r="Y68" s="2" t="inlineStr"/>
-      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Completely Kitchens</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Hi Becky,
+Your Ames showroom has been open since 1985, but the homepage says very little about it. The headline is 'Our Services', the page has about 80 words, and (515) 233-1470 is plain text, so it can't be tapped on a phone.
+I made a free homepage concept from your own kitchen and bath photos and Google reviews. It introduces you and Russ by name, leads with seeing materials in the showroom, and puts a tap-to-call number at the top and bottom. It's an unindexed private preview, kept off your domain.
+https://completelykitchens.thecreativezohaib.com/
+If you'd like, reply with thoughts or pick a time for a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>Hi Becky, one more idea from the concept. Your countertop blog posts already answer good questions about timelines and materials, so I turned them into a short homepage FAQ, including 'Which countertop material should I choose?'. Photos are captioned with Ames and Cambridge.
+https://completelykitchens.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>Hi Becky, just closing the loop. The concept will stay private if you or Russ want a look later on, and I can change any wording or photos you'd like:
+https://completelykitchens.thecreativezohaib.com/
+Take care,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>Hi Becky, I built a free homepage concept for Completely Kitchens that puts your Ames showroom and a tap-to-call number front and center, using your own photos. Private preview link: https://completelykitchens.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>Used thin homepage (H1 'Our Services', ~80 words) and non-tappable phone (conversion_notes.current_site_defects). Did not mention the 3.6 Google rating, per what_this_homepage_fixes.</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -7392,12 +9816,50 @@
           <t>gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/56b8fc0a60b5e9ab3bc1088a/19ddceb4-6df3-40ba-869d-3abe531a0978/CKI-Team+Photo+Adjusted+10-7-25.jpg?format=2500w = 1,296,369 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/56b8fc0a60b5e9ab3bc1088a/1763070185522-0J5PM490NUG69RHBNSYX/CKI+Mizell+Office-01-adjusted-05122025.jpg = 1,202,159 bytes (HTTP Content-Length); https://images.squarespace-cdn.com/content/v1/56b8fc0a60b5e9ab3bc1088a/1763070484587-1MJOGB46O4UQP3PKLZKW/CKI+Kuzel+Kitchen+06-04172025.jpg = 1,150,587 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
-      <c r="V69" s="2" t="inlineStr"/>
-      <c r="W69" s="2" t="inlineStr"/>
-      <c r="X69" s="2" t="inlineStr"/>
-      <c r="Y69" s="2" t="inlineStr"/>
-      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Custom Kitchens</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Hi Richard,
+On your home page, the meta description says 'over 55 years', while the page copy says 'over 65 years'. The page also has no tap-to-call link, so on a phone the number is only footer text.
+I built a free homepage concept from your own project photos and Google reviews that tells the Hendrick family story with one figure, 65+ years. Your 4.5 from 39 reviews is in the hero, (804) 288-7247 is one tap away, and the planning, design and installation steps are written out as text. It's a private preview, unindexed and separate from your domain.
+https://customkitchensinc.thecreativezohaib.com/
+Could I get your reaction by reply, or over a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Hi Richard, I wanted to mention the gallery. It uses your real project names, like Stratford Hills, Behind Monument and Near Wellesley. The FAQ also covers when the deposit is due and whether clients keep a working kitchen.
+https://customkitchensinc.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>Hi Richard, my last note on this. The Custom Kitchens preview remains private, and there's nothing you need to do unless you'd like to talk about it:
+https://customkitchensinc.thecreativezohaib.com/
+Thank you for your time,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>Hi Richard, I made a free homepage concept for Custom Kitchens from your own photos and reviews. It tells the Hendrick family story and keeps your number one tap away. Private preview: https://customkitchensinc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>Used 55 vs 65 years conflict and missing tap-to-call (conversion_notes.current_site_defects; no PSI score recorded, pagespeed_mobile=None); concept checked for 4.5/39 hero, project names, deposit and temporary kitchen FAQs.</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -7493,12 +9955,50 @@
           <t>mobile performance score below 60: PSI mobile performance 52</t>
         </is>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
-      <c r="V70" s="2" t="inlineStr"/>
-      <c r="W70" s="2" t="inlineStr"/>
-      <c r="X70" s="2" t="inlineStr"/>
-      <c r="Y70" s="2" t="inlineStr"/>
-      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Modern Kitchen in Elkhart</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mark,
+I couldn't find a tap-to-call link anywhere on your site; (574) 674-9989 appears only as plain footer text. The six testimonials on the site are also all dated July 15, 2016.
+Since your family has built kitchens since 1946, I made a free homepage concept that opens with that story. It uses your own project photos, shows your 4.4 from 22 Google reviews with real reviewer quotes, and puts a call button at the top and bottom. This is a private preview: not live on your domain and not indexed.
+https://modernkitchen.thecreativezohaib.com/
+If you're curious, reply here or let's set up a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mark, one detail customers may appreciate: the concept states one set of showroom hours, Saturday 9 to noon and evenings by appointment, where the site currently gives two versions. The FAQ also covers cabinet brands and seeing a countertop in your own kitchen first.
+https://modernkitchen.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mark, I'll stop here. The Modern Kitchen preview is still up whenever you have five minutes, and I'd be glad to hear what the family thinks of it:
+https://modernkitchen.thecreativezohaib.com/
+Best,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mark, I built a free homepage concept for Modern Kitchen that leads with your family story since 1946 and a tap-to-call button. Made from your own photos and reviews, private preview: https://modernkitchen.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>Used no tel: link anywhere and testimonials all dated July 15, 2016 (conversion_notes.current_site_defects); concept checked for 1946 story, 4.4/22, Harold R./Randy H./Melissa H. Google quotes, hours.</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -7583,12 +10083,50 @@
           <t>mobile performance score below 60: PSI mobile performance 44; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 447px, i.e. 72px wider than the screen; elements past the right edge: ['ARIA-HIDDEN="TRUE" right=447', 'SPAN.content-link right=447', 'A right=447']</t>
         </is>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
-      <c r="V71" s="2" t="inlineStr"/>
-      <c r="W71" s="2" t="inlineStr"/>
-      <c r="X71" s="2" t="inlineStr"/>
-      <c r="Y71" s="2" t="inlineStr"/>
-      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Mountaineer Kitchens &amp; Baths</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ben,
+On a 375px iPhone screen, your homepage renders 447px wide, so it scrolls sideways by 72px. Your 4.7 rating from 138 Google reviews also isn't shown anywhere as text, just a 'Reviews On Google' link in the footer.
+I built a free concept using your own project photos and reviews that puts those 138 reviews in the hero. It leads with the 5,000 sq. ft. showroom on Rock Cliff Drive and tells your story, from a summer job at 16 to owner. The page is a private preview, blocked from indexing and not connected to your domain.
+https://mountaineerkitchensandbaths.thecreativezohaib.com/
+Open to a reply, or a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ben, a small detail worth fixing either way: your site footer lists ZIP 25403, while your Google profile shows 25401. The concept uses 25401 and gives every project photo alt text that names the room and town.
+https://mountaineerkitchensandbaths.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ben, last note from me. The Mountaineer preview stays private if you'd like it for later, and no reply is needed if the timing isn't right:
+https://mountaineerkitchensandbaths.thecreativezohaib.com/
+Congrats again on taking over the business,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ben, I made a free homepage concept for Mountaineer that leads with your showroom and your 4.7 from 138 Google reviews. Built from your own photos, and it's a private preview: https://mountaineerkitchensandbaths.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>Used 375px horizontal overflow (447px wide) and 138 reviews not shown (measured_defects, conversion_notes.current_site_defects); FU1 uses ZIP 25403 vs 25401.</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -7673,12 +10211,54 @@
           <t>mobile performance score below 60: PSI mobile performance 55</t>
         </is>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
-      <c r="V72" s="2" t="inlineStr"/>
-      <c r="W72" s="2" t="inlineStr"/>
-      <c r="X72" s="2" t="inlineStr"/>
-      <c r="Y72" s="2" t="inlineStr"/>
-      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>Phone number mismatch on OKC Kitchen &amp; Bath</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan,
+Your Google Business Profile lists (405) 693-4737, but every page of your website shows and links (405) 830-1184. Callers comparing the two may not know which to use.
+I built a free homepage concept from your own Stone Gate Lodge photos and Google reviews. For now it uses the Google number as a tap-to-call button at the top and bottom, and you can tell me which one is right. It also shows your 5.0 from 21 reviews and answers the $40,000 starting point and design questions up front. Nothing goes live anywhere; this private preview is unindexed and kept off your domain.
+https://okckitchenandbath.thecreativezohaib.com/
+Would you reply, or grab 10 minutes this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan, one more thing I noticed while building the concept. Your Google profile shows no address, no hours and just 3 photos, even though your site has a Midtown office and dozens of projects. That part is quick to update on Google.
+https://okckitchenandbath.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan, this is my final follow-up. The OKC Kitchen &amp; Bath concept remains a private preview, and the phone number question is worth settling either way:
+https://okckitchenandbath.thecreativezohaib.com/
+Thanks for your time,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan, heads-up: your Google profile number and your website number don't match. I built a free homepage concept from your photos and reviews that uses one number. Private preview: https://okckitchenandbath.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>Used phone mismatch, Google (405) 693-4737 vs site (405) 830-1184 (conversion_notes.current_site_defects). Unsure which number is the real main line; concept uses the Google number, email asks Ryan to confirm.</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>Google and their site show different phone numbers; the concept uses Google's and the email asks which is right.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -7765,12 +10345,50 @@
           <t>mobile performance score below 60: PSI mobile performance 49; gallery images over 1MB each: https://www.specialtykitchensandbaths.com/wp-content/uploads/2015/10/bathroom-remodeling-before-after-1-1500x1125.png = 2,229,704 bytes; https://www.specialtykitchensandbaths.com/wp-content/uploads/2016/12/kitchen-remodeling-contractor-michigan.png = 1,100,334 bytes</t>
         </is>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
-      <c r="V73" s="2" t="inlineStr"/>
-      <c r="W73" s="2" t="inlineStr"/>
-      <c r="X73" s="2" t="inlineStr"/>
-      <c r="Y73" s="2" t="inlineStr"/>
-      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Specialty Kitchens and Baths</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Hi Howard,
+Google knows your business as Specialty Kitchens and Baths, LLC, but every page title on the site says Designs In Glass. I also found one call button with an empty tel: link, so tapping it does nothing.
+I built a free homepage concept from your own project photos and Google reviews that uses the Google name first and keeps Designs in Glass as the second brand. It puts you, the 2-year warranty, BBB A+ and your 5.0 from 32 reviews in the first screen, with (248) 798-1000 as tap-to-call. Nobody else can find it: the preview is private, unindexed and separate from your domain.
+https://specialtykitchensandbaths.thecreativezohaib.com/
+Would you want to talk for 10 minutes this week, or just reply?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Hi Howard, a quick add. Your 2.2MB before-and-after PNG is one of the heavy files on a site that scores 49 on mobile. The concept also answers 'Do you only install glass?' on the homepage, since your work goes well beyond shower doors.
+https://specialtykitchensandbaths.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Hi Howard, I'll leave this with you. The preview remains private, and I'm glad to change anything, from the wording to the gallery photos I picked for it:
+https://specialtykitchensandbaths.thecreativezohaib.com/
+All the best,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>Hi Howard, I made a free homepage concept for Specialty Kitchens and Baths using your own photos and reviews. It leads with you, your 2-year warranty and a tap-to-call number. Private preview: https://specialtykitchensandbaths.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>Used brand split (Google name vs 'Designs In Glass' titles) and empty tel: link (conversion_notes.current_site_defects); FU1 uses 2.2MB PNG and PSI 49 (measured_defects).</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -7873,12 +10491,54 @@
           <t>mobile performance score below 60: PSI mobile performance 47; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 525px, i.e. 150px wider than the screen; elements past the right edge: ['SPAN.uael-slide-block. right=614', 'SPAN.uael-slide_text right=614', 'DIV.slick-track right=5984']; gallery images over 1MB each: https://ironwoodremodels.com/wp-content/uploads/2023/08/8L4A2282_3_4_web.webp = 1,267,292 bytes; https://ironwoodremodels.com/wp-content/uploads/2026/04/DSC08819-HDRtest-scaled.png = 3,653,809 bytes; https://ironwoodremodels.com/wp-content/uploads/2025/05/5O8A2074-1.jpg = 1,061,227 bytes; https://ironwoodremodels.com/wp-content/uploads/2023/03/1-1.jpg = 1,239,536 bytes</t>
         </is>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
-      <c r="V74" s="2" t="inlineStr"/>
-      <c r="W74" s="2" t="inlineStr"/>
-      <c r="X74" s="2" t="inlineStr"/>
-      <c r="Y74" s="2" t="inlineStr"/>
-      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>One phone number for Ironwood Custom Remodels</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ethan,
+Your Google profile lists (760) 642-6051, but the site shows other numbers: 919-289-5462 in the header and footer, 919-823-3819 on the contact page, plus two more in the page code. That makes it hard to know which line to call.
+I built a free homepage concept from your own project photos and Google reviews that uses one number throughout. It uses the Google one for now; I can swap it. It leads with your Marine Corps service, your 4.9 from 40 reviews and the Hope Valley and Hurdle Mills kitchens. This private preview is unindexed and has no connection to your domain.
+https://ironwoodremodels.thecreativezohaib.com/
+Reply anytime, or let's do a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ethan, a phone detail: at a 375px iPhone width your homepage is 525px wide, because the slider runs past the right edge. The concept drops the slider and shows each review once instead of repeating them.
+https://ironwoodremodels.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ethan, one last note and then I'll stop. The Ironwood preview is still private whenever you have a minute:
+https://ironwoodremodels.thecreativezohaib.com/
+Thank you for your service, and good luck with the Triangle projects.
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ethan, I built a free homepage concept for Ironwood from your own photos and reviews, with one phone number and your Hope Valley kitchen up front. Take a look at the private preview: https://ironwoodremodels.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>Used four site numbers vs Google (760) 642-6051 (conversion_notes.current_site_defects); FU1 uses 375px overflow (measured_defects). Unsure: the Google number is a 760 (California) area code for a Durham firm, so the main line should be confirmed.</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>The concept uses Google's (760) 642-6051, a California number, for a Durham NC firm; their site header shows (919) 289-5462. Confirm the main line.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -7963,12 +10623,50 @@
           <t>mobile performance score below 60: PSI mobile performance 48</t>
         </is>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
-      <c r="V75" s="2" t="inlineStr"/>
-      <c r="W75" s="2" t="inlineStr"/>
-      <c r="X75" s="2" t="inlineStr"/>
-      <c r="Y75" s="2" t="inlineStr"/>
-      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>A stray phone number on Your New Baths</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brandon,
+While looking through your site, I found a Kansas City number, (816) 622-3393, set up as a call link on the home, offer and service pages, right next to your real 330-980-8398.
+I put together a free homepage concept with your own shower and tub photos and your Google reviews, and it uses one number only. It shows your 5.0 from 46 reviews, quotes real reviewers by name and says plainly which jobs take one day and which take longer. There are no countdown banners. It lives on a private preview link that isn't indexed or tied to your domain.
+https://yournewbaths.thecreativezohaib.com/
+Reply if you'd like, or we can talk for 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brandon, one more thing. Your Google profile's website link points to the /offer/ landing page instead of your home page, which is an easy setting to change. The concept names Boardman as your base and lists Niles, Lowellville and Southington from your reviews.
+https://yournewbaths.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brandon, this will be my last email about it. The concept stays private here, and you can forward it to anyone you'd like a second opinion from:
+https://yournewbaths.thecreativezohaib.com/
+Good luck with the next shower install,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brandon, quick heads-up: a Kansas City number is linked on several pages of your site. I made a free homepage concept from your photos and reviews with just 330-980-8398. Private preview: https://yournewbaths.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>Used stray Kansas City tel: link (816) 622-3393 (conversion_notes.current_site_defects); FU1 uses Google profile linking to /offer/; concept checked for one number, 5.0/46, named Google reviewers, no countdown.</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -8045,12 +10743,54 @@
           <t>gallery images over 1MB each: https://affordableremodelingsolutions.com/wp-content/uploads/2024/10/IMG_4654.jpeg = 1,022,167 bytes; https://affordableremodelingsolutions.com/wp-content/uploads/2025/07/IMG_5342.jpeg = 1,073,331 bytes; https://affordableremodelingsolutions.com/wp-content/uploads/2024/02/IMG_3045.jpeg = 1,870,565 bytes</t>
         </is>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
-      <c r="V76" s="2" t="inlineStr"/>
-      <c r="W76" s="2" t="inlineStr"/>
-      <c r="X76" s="2" t="inlineStr"/>
-      <c r="Y76" s="2" t="inlineStr"/>
-      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Affordable Remodeling</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan,
+Your number, 919.607.5467, shows in the header, but I couldn't find a tel: link, so it can't be tapped on a phone. The home page also has no H1 at the top; the only one reads 'Our Work'.
+I built a free homepage concept from your own gallery photos and Google reviews. It has call or text buttons at the top and bottom, puts your 4.9 from 54 reviews beside the headline, and introduces you by name, since right now you appear only on the contact page. It's only a private preview, with no indexing and nothing on your domain.
+https://affordableremodelingsolutions.thecreativezohaib.com/
+If it looks useful, reply or book a 10-minute call this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, another detail: your gallery serves full-size phone photos, one of them 1.9MB. The concept also answers 'Who will I talk to when I call?' up front, since you walk each house and build the estimate yourself.
+https://affordableremodelingsolutions.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, last check-in from me. If you'd like to see it later, the ARS preview is private and will stay at the same link for now:
+https://affordableremodelingsolutions.thecreativezohaib.com/
+Appreciate your time,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>Hi Jonathan, I made a free homepage concept for Affordable Remodeling Solutions from your own photos and reviews, with call or text one tap away. It's a private preview: https://affordableremodelingsolutions.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>Used header phone with no tel: link and missing top H1 (conversion_notes.current_site_defects); FU1 uses 1.9MB gallery photo. No email on file (verified_email is null), so this needs the contact form or a DM.</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -8142,12 +10882,54 @@
           <t>mobile performance score below 60: PSI mobile performance 28</t>
         </is>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
-      <c r="V77" s="2" t="inlineStr"/>
-      <c r="W77" s="2" t="inlineStr"/>
-      <c r="X77" s="2" t="inlineStr"/>
-      <c r="Y77" s="2" t="inlineStr"/>
-      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Callen's Delafield center</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael,
+Congrats on the new Delafield Design Center. The homepage hasn't caught up yet: the title tag doesn't mention Delafield, and Google's PageSpeed test scored the mobile version 28.
+I built a free homepage concept around the Design Center, using your own project photos and Google reviews. The headline names kitchen remodeling in Delafield, and the hero shows your lifetime workmanship warranty, the 1986 founding and your Infinity by Marvin Platinum Dealer status. Five FAQs are answered in plain text, including financing. It's a private preview: unindexed, not on your domain.
+https://callenconstruction.thecreativezohaib.com/
+Is there a day this week that suits a quick 10-minute look together? A reply is fine too.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, one more angle. All 7 of your Google reviews mention windows or doors, so the concept leads with kitchens and baths and keeps windows second. Every project photo also gets descriptive alt text, which none of the current site images have.
+https://callenconstruction.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, final note. The Callen concept stays private for whenever you have a minute, and I'm happy to answer any questions about how it was put together:
+https://callenconstruction.thecreativezohaib.com/
+Best of luck with the new space,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I made a free homepage concept for Callen around the new Delafield Design Center, using your own photos and reviews. It's a private preview, not live: https://callenconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>Used PSI mobile 28 and title tag without Delafield (measured_defects, conversion_notes.current_site_defects). Owner field says Michael Wood; confirm he is the right contact after the ownership change.</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>Owner on record is Michael Wood under new ownership since 2023; confirm he is the right contact.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -8226,12 +11008,54 @@
           <t>mobile performance score below 60: PSI mobile performance 54</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
-      <c r="V78" s="2" t="inlineStr"/>
-      <c r="W78" s="2" t="inlineStr"/>
-      <c r="X78" s="2" t="inlineStr"/>
-      <c r="Y78" s="2" t="inlineStr"/>
-      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for JC Custom Cabinets</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel,
+Your reviews are strong, so I want to flag a mix-up. The home page mentions a perfect 5-star record from '43 homeowners', the About and Kitchen pages say 'all 34' clients, and Google shows 4.8 from 24 reviews.
+I made a free homepage concept from your own project photos and Google reviews that states the rating once, accurately. It opens with the Meadowview Estates kitchen, puts (951) 816-7809 one tap away and offers the free in-home consultation. You're seeing a private preview that is not indexed and does not touch your domain.
+https://cervantescabinets.thecreativezohaib.com/
+Reply when you can, or let's talk for 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, one thing I liked writing for you: the FAQ says families can plan the whole project in Spanish, and it explains that you build the cabinets yourself rather than installing stock ones. The towns you serve get their own section too.
+https://cervantescabinets.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, I'll wrap up here. The Temecula concept is still private, and a short reply is all it takes if you'd like to go over it together:
+https://cervantescabinets.thecreativezohaib.com/
+Have a good week,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>Hi Joel, I made a free homepage concept for JC Custom Cabinets from your own photos and reviews, opening with the Meadowview kitchen and a tap-to-call number. Private preview: https://cervantescabinets.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>Used conflicting rating claims ('43 homeowners' vs 'all 34' vs Google 4.8/24) (conversion_notes.current_site_defects). No email on file (verified_email is null), so send via form or DM.</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>The observation (conflicting review counts on their site vs 24 on Google) is factual but the most sensitive; read it once before sending. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -8316,12 +11140,50 @@
           <t>mobile performance score below 60: PSI mobile performance 59</t>
         </is>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
-      <c r="V79" s="2" t="inlineStr"/>
-      <c r="W79" s="2" t="inlineStr"/>
-      <c r="X79" s="2" t="inlineStr"/>
-      <c r="Y79" s="2" t="inlineStr"/>
-      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Schock Construction</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve,
+Your kitchen page publishes real price ranges and a fixed bid, which is rare. The home page mentions neither, and there's no phone number in the header; visitors see 'Book a Call' instead.
+I built a free homepage concept from your own project photos and Google reviews that puts the fixed bid in the headline. It answers cost and timeline questions on the home page, shows your licence number, 8x Best of Houzz and 5.0 from 21 reviews, and makes (425) 620-6318 tap-to-call at the top. It runs as a private preview that is not indexed, and your domain is untouched.
+https://schockinc.thecreativezohaib.com/
+Got 10 minutes this week? I'd like your thoughts, or just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, one small consistency note. The Modern Moment photo alt text says Sammamish, while the case study says Issaquah. The concept keeps project locations consistent and answers 'What happens if you find something behind a wall?' plainly.
+https://schockinc.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, a last note before I let it go. The Schock preview stays private, and I'd still value even a one-line opinion on leading with the fixed bid:
+https://schockinc.thecreativezohaib.com/
+Thanks,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, I made a free homepage concept for Schock that leads with your fixed bid and posted prices, built from your own photos and reviews. Here's the private preview: https://schockinc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>Used prices and fixed bid absent from home page plus no header phone (conversion_notes.current_site_defects); FU1 uses Sammamish vs Issaquah label.</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -8420,12 +11282,50 @@
           <t>mobile performance score below 60: PSI mobile performance 11</t>
         </is>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
-      <c r="V80" s="2" t="inlineStr"/>
-      <c r="W80" s="2" t="inlineStr"/>
-      <c r="X80" s="2" t="inlineStr"/>
-      <c r="Y80" s="2" t="inlineStr"/>
-      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Stebnitz Builders</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris,
+Google's PageSpeed Insights scored your homepage 11 out of 100 on mobile. Your 4.8 rating from 26 Google reviews also isn't shown anywhere on the site.
+I made a free homepage concept with your own project photos and Google reviews. The first screen shows the five-year warranty, the 1972 founding and your 4.8 from 26 reviews. Lake-home projects are named, and (262) 723-7232 is tap-to-call at the top and bottom. As a private preview, it isn't indexed and doesn't replace anything on your domain.
+https://stebnitzbuilders.thecreativezohaib.com/
+Feel free to reply, or we can find 10 minutes this week.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, one detail from your About page: the timeline says you bought the business in 2006, while the paragraph above says 2008. Worth a quick fix either way. The concept also explains why planning takes 60 to 120 days.
+https://stebnitzbuilders.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, closing out my notes on this. The Stebnitz preview is private and ready whenever you are, and I'm glad to adjust it if the family has ideas:
+https://stebnitzbuilders.thecreativezohaib.com/
+Best regards,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris, I built a free homepage concept for Stebnitz Builders that leads with your five-year warranty and 1972 roots, made from your own photos and reviews. Private preview: https://stebnitzbuilders.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>Used PSI mobile 11 and stats counters rendering as zero (measured_defects, conversion_notes.current_site_defects); FU1 uses 2006 vs 2008 ownership date. | Revised: counter claims removed after a browser check showed they were animation or crawl artifacts.</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -8523,12 +11423,50 @@
           <t>mobile performance score below 60: PSI mobile performance 51; horizontal overflow at 375px: 375px-wide mobile viewport (iPhone UA, DPR 3): document width 395px, i.e. 20px wider than the screen; elements past the right edge: ['DIV.swiper-slide right=720', 'DIV.swiper-slide-inner right=720', 'DIV.elementskit-single-testimonial-slider.elementskit-testimonial-slider-block-s right=720']</t>
         </is>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
-      <c r="V81" s="2" t="inlineStr"/>
-      <c r="W81" s="2" t="inlineStr"/>
-      <c r="X81" s="2" t="inlineStr"/>
-      <c r="Y81" s="2" t="inlineStr"/>
-      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for USA Home Remodeling</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>Hi Isaac,
+Your site sends calls to toll-free 888-872-5082 on some pages and 888-803-9490 on others, while your Google profile lists (949) 762-8025. On a phone, the homepage also scrolls sideways because the testimonial slider runs 20px past the screen.
+I built a free homepage concept from your own project photos and Google reviews with one number, the Irvine line, as tap-to-call. It leads with your 3D design process, shows your CSLB licence and 4.9 from 52 reviews above the fold, and writes out FAQ answers, including HOA approval. This private preview is not indexed and is separate from your domain.
+https://usahomeremodeling.thecreativezohaib.com/
+Can I get your take by reply, or on a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Hi Isaac, one mobile detail: a lead form sits above the headline on every page, so on a phone the H1 and photos start below the fold. The concept opens with the headline and a call button instead.
+https://usahomeremodeling.thecreativezohaib.com/
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>Hi Isaac, last message from me on this. The USA Home Remodeling preview is private, and I can walk you through the changes in a few minutes if that helps:
+https://usahomeremodeling.thecreativezohaib.com/
+All the best,
+[Your Name]</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>Hi Isaac, I made a free homepage concept for USA Home Remodeling with one phone number and your 3D design process up front, built from your own photos and reviews. Private preview: https://usahomeremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>Used two 888 numbers vs Google (949) 762-8025 and 375px overflow (conversion_notes.current_site_defects, measured_defects); FU1 uses lead form above H1.</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -8611,12 +11549,52 @@
           <t>mobile performance score below 60: PSI mobile performance 52; gallery images over 1MB each: https://whitebirchdesignllc.com/wp-content/uploads/2026/08/White-Birch-Design-Jackpine-Trail-008.jpg = 1,958,349 bytes; https://whitebirchdesignllc.com/wp-content/uploads/2024/07/White-Birch-Deerwood-Eagan_015.jpg = 1,748,997 bytes; https://whitebirchdesignllc.com/wp-content/uploads/2026/06/The-19th-Hole-Img-3.jpg = 2,037,449 bytes; https://whitebirchdesignllc.com/wp-content/uploads/2020/06/2020WhiteBirch_001.jpg = 1,943,713 bytes</t>
         </is>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
-      <c r="V82" s="2" t="inlineStr"/>
-      <c r="W82" s="2" t="inlineStr"/>
-      <c r="X82" s="2" t="inlineStr"/>
-      <c r="Y82" s="2" t="inlineStr"/>
-      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for White Birch Design</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve,
+On whitebirchdesignllc.com, your 2025 NARI RotY awards appear only as logo images, so there is no text a visitor or Google can read. The home page H1, "Creating spaces people," also never mentions kitchens or Lakeville.
+I built a free homepage concept for White Birch from your own project photos and Google reviews. It opens with "Kitchen Remodeling in Lakeville," lists the awards and your 5.0 rating from 30 reviews as readable text, and puts tap-to-call 952-686-8443 in the header. It is a private preview, so it is not indexed and not on your domain:
+https://whitebirchdesignllc.thecreativezohaib.com/
+If you would like a quick tour, just reply and I will send a couple of times.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, a quick follow-up on the White Birch concept. On a phone, the call button sits in the first screen, and the project form takes three short steps: what to remodel, your town and a start window. The Eagan and Lakeville projects are labeled by town too. Here is the link again:
+https://whitebirchdesignllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, last note from me on this. The White Birch concept stays up as a private preview if you or Angela want to look later:
+https://whitebirchdesignllc.thecreativezohaib.com/
+Thanks for your time either way.</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, I made a free homepage concept for White Birch Design using your own photos and reviews. Your NARI awards and 5.0 rating are up top as text. Private preview: https://whitebirchdesignllc.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>Used the NARI RotY awards shown only as logo images and the H1 without Lakeville (conversion_notes.current_site_defects, echoed in outreach_hook); call bar, 3-step form and town-labeled photos checked on the live concept.</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -8698,12 +11676,52 @@
           <t>mobile performance score below 60: PSI mobile performance 37</t>
         </is>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
-      <c r="V83" s="2" t="inlineStr"/>
-      <c r="W83" s="2" t="inlineStr"/>
-      <c r="X83" s="2" t="inlineStr"/>
-      <c r="Y83" s="2" t="inlineStr"/>
-      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>A homepage idea for Woodsman Kitchens</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad,
+In a recent check of the Woodsman home page, the hero video showed the message "Video is not available or format is not supported." Google PageSpeed also scored the page 37 on mobile.
+So I made a free homepage concept for Woodsman, using your own project photos and reviews. A still Ponte Vedra kitchen replaces the video, the hero shows 4.5 stars from 286 Google reviews, and the employee-owned story and in-house countertop shop come first. Tap-to-call (904) 641-8336 sits at the top and bottom. This is a private preview only. It is not indexed or live on woodsman.biz:
+https://woodsman.thecreativezohaib.com/
+Could we walk through it together on a short call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad, one more thought. Your FAQ answers on financing, consultations and service areas are collapsed on the current site. In the concept they are written out, including that Woodsman is not a general contractor and where the countertops are cut. Showroom hours are listed plainly too. Link:
+https://woodsman.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>Brad, I will leave it here. The Woodsman concept stays private and unindexed, so look whenever it suits you:
+https://woodsman.thecreativezohaib.com/
+If it is not a fit, no problem at all.</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>Hi Brad, I built a free homepage concept for Woodsman from your own photos and reviews. It leads with the employee-owned story and your 286 Google reviews, with no video to fail. Private link: https://woodsman.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>Used the failing hero video text from conversion_notes.current_site_defects plus PSI mobile 37 from measured_defects/pagespeed_mobile.</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>The failing hero video was seen in a crawl and may play in a normal browser; the email words it as 'in a recent check'. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -8794,12 +11812,48 @@
           <t>mobile performance score below 60: PSI mobile performance 41</t>
         </is>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
-      <c r="V84" s="2" t="inlineStr"/>
-      <c r="W84" s="2" t="inlineStr"/>
-      <c r="X84" s="2" t="inlineStr"/>
-      <c r="Y84" s="2" t="inlineStr"/>
-      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>Kitchen-first homepage for Bennett</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrew,
+Your testimonials page still shows "4.9/5, 148 Reviews" for Google, while the profile now shows 4.8 from 330 reviews. The older number actually undersells how many clients have vouched for you.
+As an example, I drafted a free kitchen-first homepage for Bennett, made from your photos and the reviews clients left on Google. It opens on kitchen remodeling in Albany, shows the current rating and your CRBRA Remodeler of the Year wins, and puts tap-to-call (518) 462-6731 in the hero. It stays private: an unindexed preview, separate from bennettcontracting.com.
+https://bennettcontracting.thecreativezohaib.com/
+Glad to walk you and Kevin through it on a short call this week if that helps.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrew, a second detail worth a look. The current home page has no H1 and leads with storm door posts. The concept opens on an Albany kitchen, writes out the five-phase process and financing, and labels photos from Niskayuna, Castleton and Delmar. On phones, the call button is in the first screen and again at the end. Link again:
+https://bennettcontracting.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>Andrew, just closing the loop. If the timing is wrong, no worries at all. The Bennett concept will stay up as a private preview for a while, so you and Kevin can look whenever it suits you:
+https://bennettcontracting.thecreativezohaib.com/
+Reply anytime if you want to talk it through.</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>Hi Andrew, I made a free kitchen-first homepage concept for Bennett from your own photos and Google reviews, with your current 4.8 rating from 330 reviews up top. Private preview: https://bennettcontracting.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>Used the outdated '4.9/5, 148 Reviews' testimonials figure vs Google 4.8 (330) from conversion_notes.current_site_defects; follow-up uses the missing H1 / storm door posts defect.</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -8881,12 +11935,48 @@
           <t>mobile performance score below 60: PSI mobile performance 50</t>
         </is>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
-      <c r="V85" s="2" t="inlineStr"/>
-      <c r="W85" s="2" t="inlineStr"/>
-      <c r="X85" s="2" t="inlineStr"/>
-      <c r="Y85" s="2" t="inlineStr"/>
-      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Elevate Remodeling</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael,
+I noticed elevate-remodeling.com never lists a street address. The footer says only "COLUMBUS, OHIO," while your Google profile shows 1538 Pemberton Dr. The home page hero photo also has an empty alt attribute.
+I designed a free homepage concept for Elevate with your own kitchen photos and Google reviews. It shows 4.9 stars with the real 15-review count, puts your Amish-built cabinets and 3D design step near the top, and adds Pemberton Drive to the footer. It lives on a private, unindexed link, not on your domain:
+https://elevate-remodeling.thecreativezohaib.com/
+If you have 10 minutes this week, I would be glad to show you how it works.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, one more piece. Your kitchen page hides the cost and timeline answers in collapsed boxes. The concept answers them in plain text, including whether the price changes after work starts. On phones, "Call Michael" is one tap from the top of the page. Here it is:
+https://elevate-remodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>Michael, last note from me. The Elevate concept is still there if you want a look later, private and unindexed, and nothing on your current site has been touched:
+https://elevate-remodeling.thecreativezohaib.com/
+Thanks for reading, and good luck with the next kitchen.</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I made a free homepage concept for Elevate Remodeling from your own photos and reviews. It puts your 4.9 rating, Amish cabinets and Pemberton Dr address up front. Private preview: https://elevate-remodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>Used the missing street address (footer says only COLUMBUS, OHIO vs Google 1538 Pemberton Dr) and empty hero alt from conversion_notes.current_site_defects.</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -8977,12 +12067,48 @@
           <t>mobile performance score below 60: PSI mobile performance 46</t>
         </is>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
-      <c r="V86" s="2" t="inlineStr"/>
-      <c r="W86" s="2" t="inlineStr"/>
-      <c r="X86" s="2" t="inlineStr"/>
-      <c r="Y86" s="2" t="inlineStr"/>
-      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Elite Construction</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Hi Eric,
+Two of your pages, About and Get an Estimate, carry the title "General 1" plus the brand name, and that is the title Google shows for them. Your pricing page, on the other hand, is more open than almost any remodeler's.
+My free homepage concept for Elite leans on that openness, using only your project photos and client reviews. It shows your 4.9 rating and license number in the hero and answers cost questions with your published tiers. Tap-to-call (831) 234-5052 is at the top and bottom. Search engines cannot see this private preview, and it is not connected to discoverelite.com:
+https://discoverelite.thecreativezohaib.com/
+Send a reply if you want me to walk you through it.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>Hi Eric, a mobile detail on the Elite concept. Your current estimate form makes phone visitors scroll a full country list before the address fields. The concept uses a short three-step form instead, with a call button right beside it. Alison's design work is quoted in the reviews too. Link:
+https://discoverelite.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>Eric, I will stop here. The Elite concept remains a private preview whenever you or Craig have a minute:
+https://discoverelite.thecreativezohaib.com/
+Thanks for taking a look, and no reply needed if it is not for you.</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>Hi Eric, I put together a free homepage concept for Elite Construction using your own photos and reviews, with your price tiers and 4.9 Google rating up top. Private, unindexed preview: https://discoverelite.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>Used the 'General 1' page titles from conversion_notes.current_site_defects / outreach_hook; follow-up uses the country-list estimate form defect.</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -9051,12 +12177,52 @@
           <t>gallery images over 1MB each: https://static.wixstatic.com/media/60158a_5c5e0e71de0d4f15b2bc4fca196d470f~mv2.png/v1/fit/w_1440,h_959,q_90,enc_avif,quality_auto/60158a_5c5e0e71de0d4f15b2bc4fca196d470f~mv2.png = 3,394,544 bytes (HTTP Content-Length); https://static.wixstatic.com/media/d233dc_1e70e28f85fe4f06b784a8cdb48835ac~mv2.png/v1/fit/w_1440,h_900,q_90,enc_avif,quality_auto/d233dc_1e70e28f85fe4f06b784a8cdb48835ac~mv2.png = 1,259,919 bytes (HTTP Content-Length); https://static.wixstatic.com/media/60158a_c62256680a244f27a6cb47fac5c4c23e~mv2.png/v1/fit/w_1200,h_800,q_90,enc_avif,quality_auto/60158a_c62256680a244f27a6cb47fac5c4c23e~mv2.png = 2,174,489 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
-      <c r="V87" s="2" t="inlineStr"/>
-      <c r="W87" s="2" t="inlineStr"/>
-      <c r="X87" s="2" t="inlineStr"/>
-      <c r="Y87" s="2" t="inlineStr"/>
-      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>Tap-to-call homepage for Halco</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tyler,
+I could not find a phone number anywhere on halcokb.com. There is no tel link and no number in the text, while Google lists (781) 324-6462. Three gallery images also weigh 1.3MB to 3.4MB each.
+Using your portfolio shots and Google reviews, I made Halco a free homepage concept. Tap-to-call (781) 324-6462 sits in the hero and closing section, 650 Broadway is in the footer, and the 5-year warranty and 5 to 7 week timelines are written out instead of baked into images. It sits on a private address Google does not index:
+https://halcokb.thecreativezohaib.com/
+Would you be open to a 10-minute call this week?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tyler, one more thing I liked building. The concept shows your 4.4 rating and three Google reviews, including Danielle's note about pulling into Halco on a whim and meeting you and Jarod. Your Melrose, Wakefield and Beverly kitchens are labeled by town. Here is the link once more:
+https://halcokb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>Tyler, last message from me. The Halco concept stays private and unindexed if you want it later, and the phone number fix is worth doing on your current site either way:
+https://halcokb.thecreativezohaib.com/
+If now is not the right time, I understand.</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tyler, I noticed halcokb.com has no phone number on it, so I made a free homepage concept with tap-to-call, your 5-year warranty and your own photos and reviews. Private preview: https://halcokb.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>Used 'no phone number anywhere on the site' from conversion_notes.current_site_defects plus the 1.3MB to 3.4MB images from measured_defects.</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -9141,12 +12307,48 @@
           <t>mobile performance score below 60: PSI mobile performance 56</t>
         </is>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
-      <c r="V88" s="2" t="inlineStr"/>
-      <c r="W88" s="2" t="inlineStr"/>
-      <c r="X88" s="2" t="inlineStr"/>
-      <c r="Y88" s="2" t="inlineStr"/>
-      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>Bathroom-first homepage for Integral</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taylor,
+You have 71 five-star Google reviews, yet the newest review your site shows is from August 2025, and the widget cuts each one off mid-sentence. Almost all of your project photos also have empty alt text.
+I mocked up a free homepage for Integral Renovations with your real bathroom photos and reviews. Bathroom remodeling in Buford is the headline, the 5.0 rating and three full reviews appear as text, and the free design consultation and 3D renderings sit near the top. It is a private preview only, not indexed or on integralrenovations.co:
+https://integralrenovations.thecreativezohaib.com/
+If you want, reply and I will send a few times for a quick call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taylor, a phone detail on the Integral concept. The call button is in the first screen on a phone, and the free consultation request is three short steps. Albert's review about you, Carlos and Juan finishing the bathroom and backsplash on time is one of the quotes shown. Link:
+https://integralrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>Taylor, final note from me. The Integral concept will stay up privately for now, so there is no rush to look at it this week:
+https://integralrenovations.thecreativezohaib.com/
+Feel free to reply whenever, or not at all if it is not useful.</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>Hi Taylor, I made a free bathroom-first homepage for Integral Renovations from your own photos and reviews, with your 5.0 rating from 71 Google reviews shown in full. Private link: https://integralrenovations.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>Used the stale August 2025 review widget and empty alt text from conversion_notes.current_site_defects (also outreach_hook).</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -9223,12 +12425,48 @@
           <t>gallery images over 1MB each: https://static.wixstatic.com/media/d92212_1a7b27db28fb44a0bf2ebc32fed25973~mv2.png/v1/fit/w_960,h_848,q_90,enc_avif,quality_auto/d92212_1a7b27db28fb44a0bf2ebc32fed25973~mv2.png = 1,219,955 bytes (HTTP Content-Length); https://static.wixstatic.com/media/d92212_4b489be0564b43f29321bcd22d850957~mv2.png/v1/fit/w_960,h_848,q_90,enc_avif,quality_auto/d92212_4b489be0564b43f29321bcd22d850957~mv2.png = 1,248,396 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
-      <c r="V89" s="2" t="inlineStr"/>
-      <c r="W89" s="2" t="inlineStr"/>
-      <c r="X89" s="2" t="inlineStr"/>
-      <c r="Y89" s="2" t="inlineStr"/>
-      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Laplante Cabinetry</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan,
+A small thing on laplantecabinetry.com: the footer still reads "© 2035 by Laplante Cabinetry. Powered and secured by Wix," which looks like it came with the template. Your two 5-star Google reviews also do not appear anywhere on the site.
+I built a free homepage concept for Laplante from your own kitchen photos and those reviews. It names you as the builder and Kevin as the designer, quotes Jocelyne and Bruce, and adds tap-to-call 207-513-8440 plus your Sunrise Trail address. Your current site is untouched; the concept is a private, unindexed preview:
+https://laplantecabinetry.thecreativezohaib.com/
+If it looks useful, just reply and we can set up a short call.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan, one more idea from the concept. It explains your refresh options, from new doors to refinishing to fully custom, for people who are not ready to replace every cabinet. Eight of your own kitchens are in the gallery with real descriptions instead of camera file names. Link again:
+https://laplantecabinetry.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>Ryan, I will leave this with you. The Laplante concept stays private and unindexed, and you are welcome to share it with Kevin if he wants a look:
+https://laplantecabinetry.thecreativezohaib.com/
+Thanks for your time, and nice work on those kitchens.</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ryan, I made a free homepage concept for Laplante Cabinetry using your own kitchen photos and both Google reviews. It puts you and Kevin front and center. Private preview: https://laplantecabinetry.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>Used the '© 2035 ... Powered and secured by Wix' footer and the missing Google reviews from conversion_notes.current_site_defects / outreach_hook.</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -9322,12 +12560,52 @@
           <t>mobile performance score below 60: PSI mobile performance 55</t>
         </is>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
-      <c r="V90" s="2" t="inlineStr"/>
-      <c r="W90" s="2" t="inlineStr"/>
-      <c r="X90" s="2" t="inlineStr"/>
-      <c r="Y90" s="2" t="inlineStr"/>
-      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for North2South</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>Hi Colby,
+On north2southflo.com, the bathroom, kitchen and city pages show FAQ questions with no visible answers. The home page also has no H1, and the hero reads "South Florida's Finest" without naming a service or city.
+I made a free sample homepage for North2South, pulled from your project gallery and Google reviews. Its H1 targets bathroom remodeling in Delray Beach, license CBC1269429 and 5.0 from 84 reviews appear as badges, and every FAQ gets a real answer. Tap-to-call (561) 664-3256 is in the hero. It is a private preview, hidden from search engines and not on your domain:
+https://north2southflo.thecreativezohaib.com/
+Could we find 10 minutes this week to talk it through?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>Hi Colby, one more note. Your reviewers name you personally, so the concept quotes Jessica and Renee on your communication from consultation to walkthrough. It also adds your Albatross Road address to the footer, which the current site leaves out. Here is the link:
+https://north2southflo.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>Colby, last follow-up from me. The North2South concept is still there as a private preview, and you can look at it on your phone in about a minute:
+https://north2southflo.thecreativezohaib.com/
+If the timing is off, no problem.</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>Hi Colby, I made a free homepage concept for North2South from your own photos and reviews. It leads with bathroom remodeling in Delray Beach, your license and 84 five-star reviews. Private preview: https://north2southflo.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>Used FAQ questions with no visible answers and the missing H1 from conversion_notes.current_site_defects; business_name on Google is keyword-stuffed, so the shorter 'North2South' is used.</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>Their Google business name is keyword-stuffed; the drafts use 'North2South'.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -9422,12 +12700,48 @@
           <t>mobile performance score below 60: PSI mobile performance 54</t>
         </is>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
-      <c r="V91" s="2" t="inlineStr"/>
-      <c r="W91" s="2" t="inlineStr"/>
-      <c r="X91" s="2" t="inlineStr"/>
-      <c r="Y91" s="2" t="inlineStr"/>
-      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>Real reviews on the Palmhouse homepage</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oscar,
+The testimonials on your home page are credited to names like "Guy Hawkins" and "Jenny Wilson," which read like theme placeholders. Meanwhile, 44 real five-star Google reviews go unused on the site.
+I designed a free homepage concept for Palmhouse with your own project photos and those Google reviews. It quotes Ronni, Shannon and Dean, shows the 5.0 rating in the hero, and states the line-by-line estimate and two-year warranty in plain text. Tap-to-call (561) 831-4170 is at the top and bottom. You are seeing a private preview; it is unindexed and not live on palmhousedesign.com:
+https://palmhousedesign.thecreativezohaib.com/
+Reply if you would like a quick walkthrough.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oscar, one angle I thought you would like. The concept's FAQ covers work in gated and golf communities and managing a remodel while the owner is out of state, both points from your own pitch. Only Palmhouse project photos are used, no stock images. Link:
+https://palmhousedesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>Oscar, I will leave it here. The Palmhouse concept is still a private preview whenever you have a minute, and the placeholder names are worth swapping out on your current site either way:
+https://palmhousedesign.thecreativezohaib.com/
+Thanks for considering it.</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>Hi Oscar, I made a free homepage concept for Palmhouse Design &amp; Build that swaps the placeholder testimonials for your real Google reviews and your own photos. Private preview: https://palmhousedesign.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>Used the placeholder-looking testimonial names (Guy Hawkins, Jenny Wilson) vs 44 unused Google reviews from conversion_notes.current_site_defects / outreach_hook.</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -9511,12 +12825,48 @@
           <t>mobile performance score below 60: PSI mobile performance 57</t>
         </is>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
-      <c r="V92" s="2" t="inlineStr"/>
-      <c r="W92" s="2" t="inlineStr"/>
-      <c r="X92" s="2" t="inlineStr"/>
-      <c r="Y92" s="2" t="inlineStr"/>
-      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>Your reviews page and a homepage idea</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>Hi Adolph,
+Your reviews page currently prints a raw shortcode, "[brb_collection id=1891]", instead of the reviews themselves. It is an easy thing to miss, but it hides a 5.0 Google rating from 20 reviews.
+There is now a free homepage concept for Rohrer For Construction, built with your job photos and client reviews. It shows that rating and three real reviews as text, opens with the father-and-son story, and lists the towns you cover. Tap-to-call (847) 668-7183 is at the top and bottom. It is a private preview, kept off Google and off your domain:
+https://rohrerforconstruction.thecreativezohaib.com/
+Happy to walk through it with you and Austin if you reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>Hi Adolph, a phone detail on the Rohrer concept. The call button shows in the first screen on a phone, and the free quote form is three quick steps. The FAQ also answers cost, permits and financing in plain words. Same link as before:
+https://rohrerforconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>Adolph, one last note. The Rohrer For Construction concept stays private and unindexed if you or Austin want to look later. The reviews shortcode is worth fixing on your current site regardless:
+https://rohrerforconstruction.thecreativezohaib.com/
+Thanks either way.</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>Hi Adolph, your reviews page shows a code snippet instead of reviews, so I made a free homepage concept that shows your 5.0 Google rating, your crew and your own photos. Private preview: https://rohrerforconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>Used the raw '[brb_collection id=1891]' shortcode on the reviews page from conversion_notes.current_site_defects / outreach_hook.</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -9606,12 +12956,48 @@
           <t>mobile performance score below 60: PSI mobile performance 45</t>
         </is>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
-      <c r="V93" s="2" t="inlineStr"/>
-      <c r="W93" s="2" t="inlineStr"/>
-      <c r="X93" s="2" t="inlineStr"/>
-      <c r="Y93" s="2" t="inlineStr"/>
-      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>Contact link on stevenskitchens.com</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve,
+The email link on your contact page points to info@mysite.com, a leftover template address, so a tap there does not reach you. There is also no H1 on the home page, and the footer still says © 2021.
+Here is a free homepage concept I drafted for Stevens Kitchens, made from your project photos plus your Google reviews. It tells your story from cabinet technician to licensed contractor since 2003, shows 4.7 stars from 88 reviews with your CRC license, and lists the working reception@ address. Tap-to-call (407) 359-0302 is in the hero. It is only a preview: private, unindexed and not on stevenskitchens.com.
+https://stevenskitchens.thecreativezohaib.com/
+Would a short call this week be worth it?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, one more angle. Wendy's review mentions Reem redesigning the kitchen and Dylan staying responsive, and it sits right on the concept page. The FAQ also answers budget, weeks of work and financing, and the showroom hours are listed. Link:
+https://stevenskitchens.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>Steve, final note from me on this. The Stevens Kitchens concept stays up privately, and the info@mysite.com link is a quick fix worth making on your current site:
+https://stevenskitchens.thecreativezohaib.com/
+If it is not a priority now, that is completely fine.</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, quick heads-up: the email link on your contact page goes to info@mysite.com. I also made a free homepage concept from your own photos and reviews: https://stevenskitchens.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>Used the info@mysite.com placeholder email link from conversion_notes.current_site_defects / outreach_hook, plus no H1 and the 2021 footer.</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -9688,12 +13074,48 @@
           <t>mobile performance score below 60: PSI mobile performance 49; gallery images over 1MB each: https://images.squarespace-cdn.com/content/v1/5a6ebdc12aeba59754f635bd/b4946eae-99ec-440f-bf31-647aea83e776/IMG_1243.png?format=1500w = 1,997,480 bytes; https://images.squarespace-cdn.com/content/v1/5a6ebdc12aeba59754f635bd/f24538ce-25ab-4772-a90f-c94e3b98796f/IMG_1245.png?format=1500w = 1,479,660 bytes</t>
         </is>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
-      <c r="V94" s="2" t="inlineStr"/>
-      <c r="W94" s="2" t="inlineStr"/>
-      <c r="X94" s="2" t="inlineStr"/>
-      <c r="Y94" s="2" t="inlineStr"/>
-      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>Caldwell homepage for TVRR</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael,
+Google shows Treasure Valley Redesign &amp; Remodel at 3425 E Chicago St in Caldwell, but your website lists only a PO Box in Star. Your 4.6 rating from 18 Google reviews also does not appear on the home page.
+I created a free sample homepage for TVRR with your own kitchen and bath photos and what clients wrote on Google. It uses the Caldwell address throughout, quotes three reviews, introduces your 35+ years of building, and groups the ten process steps into five stages. The page is private and blocked from search, and it does not replace anything on tvremodel.com:
+https://tvremodel.thecreativezohaib.com/
+Just reply if you want a quick tour.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, a phone detail I wanted to mention. The call button is in the first screen on a phone, and the free estimate request takes three short steps. The FAQ also explains why your bid might differ from another contractor's and whether you can work with an outside designer. Link:
+https://tvremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>Michael, last message on this. The TVRR concept stays private and unindexed for whenever you have a moment, and matching your site address to Google is worth doing either way:
+https://tvremodel.thecreativezohaib.com/
+Thanks for reading it.</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael, I made a free homepage concept for Treasure Valley Redesign &amp; Remodel from your own photos and reviews, with your Caldwell address and Google reviews up front. Private preview: https://tvremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>Used the NAP mismatch (PO Box in Star on site vs 3425 E Chicago St, Caldwell on Google) and the missing rating from conversion_notes.current_site_defects / outreach_hook.</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -9778,12 +13200,52 @@
           <t>mobile performance score below 60: PSI mobile performance 38</t>
         </is>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
-      <c r="V95" s="2" t="inlineStr"/>
-      <c r="W95" s="2" t="inlineStr"/>
-      <c r="X95" s="2" t="inlineStr"/>
-      <c r="Y95" s="2" t="inlineStr"/>
-      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for APlus Remodeling</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex,
+Your service-area page title renders as "Area We Serve - Aplus % %," and the home page H1, "Leading Home Remodeling Experts," does not mention kitchens or Anaheim.
+Your own photos and reviews went into a free homepage concept I built for APlus. The hero is about kitchens in Anaheim and the cabinets from your factory, with 4.9 stars from 57 reviews and tap-to-call (949) 458-2108. Eric's note about cabinets he still loves after 13 years is quoted. Think of it as a private draft. It is not indexed, and your real site stays as is:
+https://aplushomeimprovements.thecreativezohaib.com/
+I can go over it on a 10-minute call if you are interested.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex, one more detail. Your portfolio photos are hotlinked from Google Photos with empty alt text. In the concept they carry town names like Coto de Caza, Dana Point and Tustin, and the page ends with an invitation to tour the Anaheim shop. Link again:
+https://aplushomeimprovements.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>Alex, I will close the loop here. The APlus concept stays up as a private preview, and the page title showing "% %" is a quick fix on your current site either way:
+https://aplushomeimprovements.thecreativezohaib.com/
+Thanks, and reply anytime if you want to talk.</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>Hi Alex, I made a free homepage concept for APlus that leads with your Anaheim cabinet factory and 4.9 Google rating, built from your own photos and reviews. Private preview: https://aplushomeimprovements.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>Used the 'Area We Serve - Aplus % %' page title and the H1 without kitchens or Anaheim from conversion_notes.current_site_defects; follow-up uses hotlinked Google Photos with empty alt.</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -9871,12 +13333,52 @@
           <t>mobile performance score below 60: PSI mobile performance 51; gallery images over 1MB each: https://gmh-remodeling.com/wp-content/uploads/2026/08/Sussex-Kitchen-Remodel-2048x1365.jpg = 1,901,190 bytes (HTTP Content-Length); https://gmh-remodeling.com/wp-content/uploads/2026/08/Sussex-Kitchen-Remodel-GMH-2048x1365.jpg = 2,110,224 bytes (HTTP Content-Length); https://gmh-remodeling.com/wp-content/uploads/2026/08/GMH-Kitchen-Remodel-Sussex-scaled.jpg = 2,937,832 bytes (HTTP Content-Length)</t>
         </is>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
-      <c r="V96" s="2" t="inlineStr"/>
-      <c r="W96" s="2" t="inlineStr"/>
-      <c r="X96" s="2" t="inlineStr"/>
-      <c r="Y96" s="2" t="inlineStr"/>
-      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>Waukesha homepage idea for GMH</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg,
+Your site gives the office address as Pewaukee, WI 53186, while your Google profile lists Waukesha, WI 53186. The site also carries two extra phone numbers, 262-364-6969 and 262-490-8222, beside the main 262-696-8131.
+I drafted a free homepage concept for GMH, using nothing but your project photos and reviews. It matches the Google address exactly, uses one tap-to-call number at the top and bottom, and moves your published price ranges and fixed-price contracts onto the home page. It runs on a private preview address, unindexed and apart from gmh-remodeling.com:
+https://gmh-remodeling.thecreativezohaib.com/
+If it's useful, I'm happy to take you through it in about 10 minutes.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, a thought on photos. One Sussex kitchen image on the current site is about 2.9MB, and the full-size original downloaded at around 14MB. The concept labels your Sussex, Waukesha and Brookfield work by town, and on phones the call button is in the first screen. The preview again:
+https://gmh-remodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>Greg, last note from me. The GMH concept will stay private and unindexed if you or Dane want to look later:
+https://gmh-remodeling.thecreativezohaib.com/
+No reply needed if it is not a fit.</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>Hi Greg, I made a free homepage concept for GMH Construction from your own photos and reviews, with your Waukesha address, one phone number and your fixed pricing up front. Private preview: https://gmh-remodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>Used the Pewaukee vs Waukesha NAP mismatch and extra tel links from conversion_notes.current_site_defects; follow-up uses measured image sizes from measured_defects.</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -9953,12 +13455,52 @@
           <t>broken quote or estimate form: form on https://upscaleremodeling.com/ posts to https://upscaleremodeling.com/wp-json/ws-form/v1/submit: GET form action -&gt; HTTP 404; dead phone or email link: tel: hrefs ['123456789'] mailto: hrefs []</t>
         </is>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
-      <c r="V97" s="2" t="inlineStr"/>
-      <c r="W97" s="2" t="inlineStr"/>
-      <c r="X97" s="2" t="inlineStr"/>
-      <c r="Y97" s="2" t="inlineStr"/>
-      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>Call link on upscaleremodeling.com</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve,
+One of the tap-to-call links on your home page dials "123456789" instead of your number. Also, when I checked the address your estimate form submits to, it returned a 404. It may still work for real submissions, but a test request would confirm it.
+To show an alternative, I built Upscale a free homepage concept from your portfolio and Google reviews. It has a working tap-to-call to (607) 539-6014, shows 5.0 from 40 Google reviews, and puts your fixed price before construction and 5-year warranty first. The preview is private and noindexed, separate from your live domain:
+https://upscaleremodeling.thecreativezohaib.com/
+A quick reply is all it takes if you want to talk it over.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, one more piece. Your FAQ answers on hours, warranty and timelines are collapsed today. The concept writes them out, including what to expect with an older house, and labels photos from Cayuga Heights, Fall Creek and Trumansburg. Here it is again:
+https://upscaleremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>Steve, final note from me. The Upscale concept stays up privately for whenever you want it, and the 123456789 call link is worth fixing on your current site either way:
+https://upscaleremodeling.thecreativezohaib.com/
+Thanks for your time.</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>Hi Steve, heads-up: a call button on upscaleremodeling.com dials 123456789. I also built a free homepage concept from your own photos and reviews with a working call button. Private preview: https://upscaleremodeling.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>Used the placeholder tel:123456789 link and the form endpoint 404 from measured_defects; the 404 came from a GET to the form action, so the email hedges it and suggests a test submission.</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>Leads with a call link that dials 123456789 (verified). The contact form 404 may only affect GET requests, so the email suggests a test instead of claiming it is broken. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -10043,12 +13585,52 @@
           <t>mobile performance score below 60: PSI mobile performance 44</t>
         </is>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
-      <c r="V98" s="2" t="inlineStr"/>
-      <c r="W98" s="2" t="inlineStr"/>
-      <c r="X98" s="2" t="inlineStr"/>
-      <c r="Y98" s="2" t="inlineStr"/>
-      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for VanderBeken Remodel</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron,
+On your kitchen services page, the testimonial box still shows template text: "Your content goes here. Edit or remove this text inline." The home page also has no H1; its first heading is an H3 about interior remodeling since 2007.
+I sketched out a free homepage for VanderBeken with your own project photography and Google reviews. The first line says kitchen remodeling in Marysville, and the fixed investment price, two-year warranty and 2025 REX award sit in the first screen beside tap-to-call (425) 870-8123. The link below is a private preview that search engines skip:
+https://vanderbekenremodel.thecreativezohaib.com/
+If you and Jennifer want a quick walkthrough, just reply.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron, one more detail. Brian's review about having three months to gut and remodel a new house before moving in is quoted on the concept, and the FAQ explains accessible bathrooms that do not look institutional. Photos are captioned by town, from Snohomish to Lake Stevens. Link:
+https://vanderbekenremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>Ron, last note from me. The VanderBeken concept stays private and unindexed, and the "Your content goes here" text on the kitchen page is an easy fix either way:
+https://vanderbekenremodel.thecreativezohaib.com/
+If now is not the time, I understand completely.</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron, I made a free homepage concept for VanderBeken Remodel from your own photos and reviews. It leads with your fixed price, two-year warranty and REX award. Private preview: https://vanderbekenremodel.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>Used the 'Your content goes here' placeholder testimonial and missing H1 from conversion_notes.current_site_defects / outreach_hook.</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -10132,12 +13714,52 @@
           <t>mobile performance score below 60: PSI mobile performance 36</t>
         </is>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
-      <c r="V99" s="2" t="inlineStr"/>
-      <c r="W99" s="2" t="inlineStr"/>
-      <c r="X99" s="2" t="inlineStr"/>
-      <c r="Y99" s="2" t="inlineStr"/>
-      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>Homepage concept for Clar Construction</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dan,
+On clarconstruction.com, the Stowe kitchen photo carries the alt text "Architect reviewing blueprints in front of a 19th-century home." Google PageSpeed also scored the home page 36 on mobile.
+Working from your own photos and client reviews, I made a free homepage concept for Clar. It describes each photo as it actually is, shows 4.5 stars from 43 reviews next to "since 2004" and fixed-price contracts, and explains the Project Development step plainly. Tap-to-call (802) 223-3447 is in the hero. Only you have the link to this private preview. It is unindexed and not on your domain:
+https://clarconstruction.thecreativezohaib.com/
+Would a 10-minute call sometime this week suit you?
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dan, one more angle. The concept tells the millwork shop story, cabinets built in Montpelier's old clothespin factory, near the top. Diane's review about you and Robyn guiding the planning is quoted, and on phones the call button is in the first screen. Here it is:
+https://clarconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>Dan, I will leave it here. The Clar concept stays a private preview if you or Robyn want to come back to it, and the photo captions are worth fixing on the current site either way:
+https://clarconstruction.thecreativezohaib.com/
+Thank you for your time.</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dan, I built a free homepage concept for Clar Construction from your own photos and reviews, with your fixed-price process and clothespin-factory millwork shop up front. Private preview: https://clarconstruction.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>Used the mismatched alt text on the Stowe kitchen photo from conversion_notes.current_site_defects plus PSI mobile 36 from measured_defects.</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -10222,12 +13844,52 @@
           <t>mobile performance score below 60: PSI mobile performance 56</t>
         </is>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
-      <c r="V100" s="2" t="inlineStr"/>
-      <c r="W100" s="2" t="inlineStr"/>
-      <c r="X100" s="2" t="inlineStr"/>
-      <c r="Y100" s="2" t="inlineStr"/>
-      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Pereira Construction</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Hi Robert,
+You have 50 five-star Google reviews and six Nextdoor Neighborhood Fave awards, but neither appears on your site. The phone number shows once as plain text near the bottom, with no button to call or text from a phone.
+I put your project photos and Google reviews into a free homepage concept for Pereira Construction. It puts bathroom remodeling in Lake Worth first, shows your CGC license since 2007 and the Nextdoor award up top, and adds a call-or-text button for (561) 248-9957 in the hero and footer. It is a private preview only, kept out of search and off your domain:
+https://pereiraconstructionsouthfl.thecreativezohaib.com/
+Reply here and I can show you around the page.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Hi Robert, one more detail. The concept quotes Pru and Kristen, including the shower with mold and water damage that now looks brand new, and the FAQ covers tub-to-shower conversions. Your seven-day hours and the Nextdoor award are listed as well. Link:
+https://pereiraconstructionsouthfl.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>Robert, last note from me. The Pereira concept stays private and unindexed for whenever you have a minute:
+https://pereiraconstructionsouthfl.thecreativezohaib.com/
+Thanks, and no reply needed if it is not for you.</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>Hi Robert, I made a free homepage concept for Pereira Construction from your own photos and reviews, with your 50 five-star reviews and a call-or-text button up top. Private preview: https://pereiraconstructionsouthfl.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>Used the missing Google rating / Nextdoor awards and the lack of a tap-to-call link from conversion_notes.current_site_defects / outreach_hook. Note id is pcsouthflorida.com but the live site and concept use the pereiraconstructionsouthfl name.</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>Concept subdomain is pereiraconstructionsouthfl (their live domain); the record id is pcsouthflorida.com. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -10308,15 +13970,55 @@
           <t>mobile performance score below 60: PSI mobile performance 39</t>
         </is>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
-      <c r="V101" s="2" t="inlineStr"/>
-      <c r="W101" s="2" t="inlineStr"/>
-      <c r="X101" s="2" t="inlineStr"/>
-      <c r="Y101" s="2" t="inlineStr"/>
-      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>Homepage idea for Sicora Design / Build</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron,
+The Facebook icon on sicora.com links to facebook.com/profile.php with no profile ID, so it does not reach the Sicora page. The home page also has five separate H1 headings and scored 39 on mobile in Google PageSpeed.
+Using your project gallery and Google reviews, I designed a free homepage concept for Sicora. The headline targets kitchen remodeling in Minneapolis, and the three design options, under 3% budget variance, 10-year structural warranty and 4.9 stars from 54 reviews all sit above the fold. The link is a private, unindexed preview, not your live site:
+https://sicora.thecreativezohaib.com/
+If it is worth a look, a reply or a 10-minute call works.
+[Your Name]
+[Your Company] | [Your Phone / WhatsApp]
+[Your Business Address]
+Not interested? Just reply "no thanks" and I will not follow up.</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron, one more note. Your site footer says St. Louis Park while Google says Minneapolis for the same 55416 address. The concept uses the Google version. Cassie's review about you and Darcy keeping design and budget in check is quoted too. Link:
+https://sicora.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>Ron, last follow-up from me. The Sicora concept will stay private and unindexed for a while, and the Facebook link fix takes a minute on your current site either way:
+https://sicora.thecreativezohaib.com/
+Appreciate you reading this far.</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>Hi Ron, I made a free homepage concept for Sicora Design / Build from your own photos and reviews, leading with your three design options and 4.9 Google rating. Private preview: https://sicora.thecreativezohaib.com/</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>Used the broken Facebook profile.php link and five H1s from conversion_notes.current_site_defects plus PSI mobile 39 from measured_defects; follow-up uses the St. Louis Park vs Minneapolis NAP mismatch.</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z101"/>
+  <autoFilter ref="A1:AA101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/OUTREACH_100.xlsx
+++ b/output/OUTREACH_100.xlsx
@@ -8368,11 +8368,7 @@
           <t>Header number vs tel: link mismatch (693-1896 shown, 324-3913 dialed) from current_site_defects / outreach_hook; 60px overflow at 375px from measured_defects in follow_up_1.</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>The new concept shows a 'Women-owned business' badge; the owner on record is Evan Hill. Confirm or remove the badge on the concept before sending.</t>
-        </is>
-      </c>
+      <c r="AA58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">

--- a/output/OUTREACH_100.xlsx
+++ b/output/OUTREACH_100.xlsx
@@ -1579,20 +1579,20 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>info@assemblysquad.com</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+          <t>info@assemblyserviceil.com</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>assemblysquadcustomerservice@gmail.com</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.assemblyserviceil.com/privacy-policy.html</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.assemblyserviceil.com/contact.html</t>
-        </is>
-      </c>
+          <t>https://www.assemblyserviceil.com/contact.html (page meta and JSON-LD on about 400 of their pages); Gmail address in JSON-LD and on facebook.com/assemblysquad</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/assemblysquad
@@ -1674,7 +1674,11 @@
           <t>Wicker Park slider Before image returns HTTP 404, plus PSI mobile 48 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>Replaces info@assemblysquad.com, which bounced (that domain has a Null MX). assemblyserviceil.com has a working mail server.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2126,13 +2130,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>info@mcdonaldremodeling.com</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>ajants@mcdonaldremodeling.com</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>galsterlund@mcdonaldremodeling.com</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcdonaldremodeling.com/</t>
+          <t>https://www.mcdonaldremodeling.com/remodel-reveal ('To RSVP: email ajants@mcdonaldremodeling.com'); galsterlund@ from a 2023 archive of their contact page</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -2221,7 +2229,11 @@
           <t>Phone only as plain footer text with no tap-to-call on 16 crawled pages, PSI 41 (conversion_notes.current_site_defects, pagespeed_mobile).</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>ajants@ is Amy Jants, designer and project manager; the email greets Chris, so ask her to pass it on or change the greeting. info@ was blocked by their Barracuda filter, which often blocks the sending mailbox, so send from a different warmed-up mailbox. galsterlund@ belongs to the former president and may be dead.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -11500,14 +11512,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>https://whitebirchdesignllc.com/contact/</t>
-        </is>
-      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>steve@whitebirchdesignllc.com</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>info@whitebirchdesignllc.com</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>City of Eagan permit EA188724 signed by Steve McDonald, Jan 2024 (https://eagandocs.cityofeagan.com/WebLink/DocView.aspx?id=2733565&amp;dbid=0&amp;repo=CityofEagan); info@ on facebook.com/whitebirchdesignllc</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/whitebirchdesignllc</t>
@@ -11588,7 +11608,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>On the permit scan the box cuts the address at 'whitebirchdesignllc.c'; the domain is theirs (Google Workspace MX). For zero risk send to info@ first.</t>
         </is>
       </c>
     </row>
@@ -11628,14 +11648,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.woodsman.biz/contact-us</t>
-        </is>
-      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>info@woodsman.biz</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>careers@woodsman.biz</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/woodsmankitchensandfloors contact info; also hoorayfor904day.com and threebestrated.com; careers@ on woodsman.biz/openings-at-woodsman</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>http://www.facebook.com/2008/fbml
@@ -11715,7 +11743,7 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>The failing hero video was seen in a crawl and may play in a normal browser; the email words it as 'in a recent check'. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>woodsman.biz mail runs on their own Exchange server (outlook.woodsman.biz). If it fails again, their server is likely down; use the phone or the short message on Facebook. The failing hero video was seen in a crawl and may play in a normal browser; the email words it as 'in a recent check'.</t>
         </is>
       </c>
     </row>
@@ -12142,14 +12170,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.halcokb.com/contact</t>
-        </is>
-      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>halco@halcokb.com</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>tim@halcoshowroom.com, tyler@tproplumbing.com</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/halcokb and Crunchbase (halco@); tim@ from a 2020 archive of halcoshowroom.com (Tim Procopio, President per BBB); tyler@ from federal DOT record 3038634 for HALCO SHOWROOM</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr"/>
@@ -12216,7 +12252,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>halco@ is the safest current address (Microsoft 365). tim@ is the president's but from 2020; tyler@ is Tyler Procopio's address at his plumbing company. Socials found: facebook.com/halcokb, instagram.com/halcokitchenandbath, linkedin.com/company/halco-kb.</t>
         </is>
       </c>
     </row>
@@ -13923,14 +13959,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>https://sicora.com/contact/</t>
-        </is>
-      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>rsonnek@sicora.com</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>contactus@sicora.com</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>mn.gov resource listing, Nextdoor and a Houzz comment by Ron Sonnek; contactus@ on sicora.com case study pages ('Email us at: contactus@sicora.com')</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php</t>
@@ -14009,7 +14053,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>sicora.com does accept mail (Microsoft 365; its MX starts with priority 0, which some checkers misread as no mail).</t>
         </is>
       </c>
     </row>

--- a/output/OUTREACH_100.xlsx
+++ b/output/OUTREACH_100.xlsx
@@ -10712,14 +10712,18 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>jonathan@affordableremodelingsolutions.com</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>https://affordableremodelingsolutions.com/contact/</t>
-        </is>
-      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>nextdoor.com/pages/affordable-remodeling-solutions-llc-1 (mailto) and the JSON-LD on every page of their site</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/affordableremodsolutions</t>
@@ -10796,7 +10800,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Owner Jonathan Doering's own inbox and the only address published anywhere (Proofpoint MX, valid).</t>
         </is>
       </c>
     </row>
@@ -10975,14 +10979,18 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>info@cervantescabinets.com</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>https://cervantescabinets.com/contact</t>
-        </is>
-      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>cervantescabinets.com/contact, in the page's JSON-LD (not visible text)</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>http://www.facebook.com/2008/fbml</t>
@@ -11061,7 +11069,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>The observation (conflicting review counts on their site vs 24 on Google) is factual but the most sensitive; read it once before sending. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Shared inbox (Microsoft 365 MX, valid). No personal email for Joel is published; the Instagram DM is the second channel. The observation (conflicting review counts on their site vs 24 on Google) is factual but the most sensitive; read it once before sending.</t>
         </is>
       </c>
     </row>
@@ -13185,14 +13193,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.aplushomeimprovements.com/</t>
-        </is>
-      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>alex.t@apluskitchen.com</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>sales@apluskitchen.com, admin@apluskitchen.com, info@apluskitchen.com</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>aplushomeimprovements.com consultation form recipients (wp-json page 230394, modified 2026-08-12); sales@ in their Facebook intro; admin@ on Trustindex; info@ on Manta</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/apluskitchens</t>
@@ -13275,7 +13291,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Their mail runs on apluskitchen.com (Google Workspace), not the website domain, which has no mailbox. alex.t@ is owner Alex Tabrizi's address taken from a hidden form recipient list; sales@ is the public one.</t>
         </is>
       </c>
     </row>
@@ -13319,14 +13335,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>https://gmh-remodeling.com/services/</t>
-        </is>
-      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>greg@gmh-remodeling.com</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>info@gmh-remodeling.com</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>NARI Milwaukee 'Renovate 2026' directory (issuu.com/narimilwaukee/docs/nari_renovate_2026); also their 2020 referral certificate PDF; info@ on gmh-remodeling.com/referral-program</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/GMH-Construction-Inc-193174987380536</t>
@@ -13408,7 +13432,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Owner Greg Perkins (Google Workspace MX, valid).</t>
         </is>
       </c>
     </row>
@@ -13448,14 +13472,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>https://upscaleremodeling.com/</t>
-        </is>
-      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>steve@upscaleremodeling.com</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>hello@upscaleremodeling.com, info@upscaleremodeling.com</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Builders Exchange of the Southern Tier member directory, May 2025 (bxstier.com/wp-content/uploads/STBA_2025_P2.pdf); hello@ in their own checklist PDFs (July 2025); info@ in Facebook contact info</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/UpscaleRemodelingCorp</t>
@@ -13530,7 +13562,7 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>Leads with a call link that dials 123456789 (verified). The contact form 404 may only affect GET requests, so the email suggests a test instead of claiming it is broken. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Owner Stephen Nash (Microsoft 365 MX, valid). Leads with a call link that dials 123456789 (verified). The contact form 404 may only affect GET requests, so the email suggests a test instead of claiming it is broken.</t>
         </is>
       </c>
     </row>
@@ -13570,14 +13602,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>https://vanderbekenremodel.com/</t>
-        </is>
-      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@vanderbekenremodel.com</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>info@vanderbekenremodel.com</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>n49.com business listing ('Email jennifer@vanderbekenremodel.com'); also bizthistown.com; info@ in Facebook contact info</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/vanderbekenremodel</t>
@@ -13660,7 +13700,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Washington L&amp;I lists the owners as Jennifer Elin and Ronald Dean VanderBeken, so Jennifer is an owner; the email greets Ron, so greet both or change the greeting.</t>
         </is>
       </c>
     </row>
@@ -13700,14 +13740,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>https://clarconstruction.com/</t>
-        </is>
-      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>dan@clarconstruction.com</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>info@clarconstruction.com</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>greenlight-realestate.com/resources/preferred-providers ('Dan Clar ... dan@clarconstruction.com'); also City of Montpelier contractor list; info@ in Facebook contact info</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/clarconstruction</t>
@@ -13789,7 +13837,7 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>Owner Dan Clar (Google Workspace MX, valid).</t>
         </is>
       </c>
     </row>
@@ -13829,14 +13877,22 @@
           <t>Not listed on their site (try the phone number on WhatsApp)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pereiraconstructionsouthfl.com/</t>
-        </is>
-      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>info@pcsouthflorida.com</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>robert@pereiraconstructionsouthfl.com</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>nextdoor.com/pages/pereira-construction-of-south-fl-inc-lake-worth-fl, their Facebook page and 2026 posts; robert@ in the Facebook contact info of sister business 561 Soft Wash</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/PCsouthFlorida
@@ -13919,7 +13975,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>Concept subdomain is pereiraconstructionsouthfl (their live domain); the record id is pcsouthflorida.com. No email on file: use the contact form, then the short message on Facebook or Instagram.</t>
+          <t>info@ is the clearly current address (Google Workspace MX, valid); robert@ is the owner's but from a sister business listing. Concept subdomain is pereiraconstructionsouthfl (their live domain); the record id is pcsouthflorida.com.</t>
         </is>
       </c>
     </row>
